--- a/excel/04_Modelo_Financiero_Embudo_Webinar_Pago.xlsx
+++ b/excel/04_Modelo_Financiero_Embudo_Webinar_Pago.xlsx
@@ -169,9 +169,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -995,7 +995,7 @@
           <t>&gt;3,5 %</t>
         </is>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
@@ -1031,7 +1031,7 @@
           <t>&lt;8</t>
         </is>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="19">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
@@ -1067,7 +1067,7 @@
           <t>&gt;65 %</t>
         </is>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <f>'Supuestos'!$C$20</f>
         <v/>
       </c>
@@ -1103,7 +1103,7 @@
           <t>&lt;10</t>
         </is>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="19">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
@@ -1139,7 +1139,7 @@
           <t>&gt;22 %</t>
         </is>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <f>'Supuestos'!$C$25</f>
         <v/>
       </c>
@@ -1175,7 +1175,7 @@
           <t>&lt;80</t>
         </is>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="19">
         <f>'Modelo'!$C$26</f>
         <v/>
       </c>
@@ -1211,7 +1211,7 @@
           <t>&gt;65 %</t>
         </is>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="17">
         <f>'Supuestos'!$C$27</f>
         <v/>
       </c>
@@ -1247,7 +1247,7 @@
           <t>&gt;10 %</t>
         </is>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="18">
         <f>'Modelo'!$C$28</f>
         <v/>
       </c>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="C7" s="35">
-        <f>IF(ISERROR(SUM('Embudo'!C5:I60)),"REVISAR","OK")</f>
+        <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2944,7 +2944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J25"/>
+  <dimension ref="B2:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2952,24 +2952,23 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Embudo: todos los pasos, cuántos, qué porcentaje pasa y cuánto cuesta cada uno</t>
+          <t>Embudo: todos los pasos, cuántos pasan y, por cada uno, qué pagás, qué te queda y hasta cuánto podrías pagar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cada fila es un paso del embudo en orden. '% que pasa' compara con el paso anterior (o con el que dice la nota). El costo por paso es inversión ÷ cantidad; el techo por paso es lo máximo que podrías pagar por él si lo demás se mantiene. Los pasos sin costo propio ya se pagaron con el CPA: mejoran el AOV.</t>
+          <t>Cada fila es un paso del embudo en orden. '% que pasa' compara con el paso anterior (o con el que dice la nota). Tres números por paso: lo que pagás hoy por cada uno (inversión ÷ cantidad), lo que te queda por cada uno (ganancia ÷ cantidad) y lo máximo que podrías pagar (el techo: lo que cada uno genera en cash neto). Techo = costo + ganancia + fijos repartidos.</t>
         </is>
       </c>
     </row>
@@ -2991,30 +2990,25 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>% que se pierde</t>
+          <t>% acumulado</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>% acumulado</t>
+          <t>Costo por paso (pagás hoy)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Costo por paso</t>
+          <t>Ganancia por paso (te queda)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Techo por paso</t>
+          <t>Techo por paso (máximo a pagar)</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Ganancia por paso</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Qué se paga acá / cómo se lee</t>
         </is>
@@ -3040,24 +3034,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F6" s="12">
+        <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$7)</f>
+        <v/>
       </c>
       <c r="G6" s="12">
-        <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$7)</f>
-        <v/>
-      </c>
-      <c r="H6" s="17">
+        <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$44*1/'Modelo'!$C$7)</f>
+        <v/>
+      </c>
+      <c r="H6" s="12">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="I6" s="12">
-        <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$44*1/'Modelo'!$C$7)</f>
-        <v/>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Costo por visita.</t>
         </is>
@@ -3073,31 +3062,27 @@
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$9/'Modelo'!$C$7)</f>
         <v/>
       </c>
       <c r="E7" s="18">
-        <f>IF('Modelo'!$C$7=0,0,1-'Modelo'!$C$9/'Modelo'!$C$7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$9/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F7" s="12">
+        <f>IF('Modelo'!$C$9=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$9)</f>
+        <v/>
+      </c>
       <c r="G7" s="12">
-        <f>IF('Modelo'!$C$9=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="H7" s="17">
+        <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$44*1/'Modelo'!$C$9)</f>
+        <v/>
+      </c>
+      <c r="H7" s="12">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="I7" s="12">
-        <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$44*1/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Costo por entrada. La unidad de este embudo: acá los leads ya son compradores.</t>
         </is>
@@ -3113,21 +3098,22 @@
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$11/'Modelo'!$C$9)</f>
         <v/>
       </c>
       <c r="E8" s="18">
-        <f>IF('Modelo'!$C$9=0,0,1-'Modelo'!$C$11/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="F8" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$11/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3135,12 +3121,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Sobre compradores de entrada. Suma al ROAS del front.</t>
         </is>
@@ -3156,31 +3137,27 @@
         <f>'Modelo'!$C$16</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$16/'Modelo'!$C$9)</f>
         <v/>
       </c>
       <c r="E9" s="18">
-        <f>IF('Modelo'!$C$9=0,0,1-'Modelo'!$C$16/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$16/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F9" s="12">
+        <f>IF('Modelo'!$C$16=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$16)</f>
+        <v/>
+      </c>
       <c r="G9" s="12">
-        <f>IF('Modelo'!$C$16=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$16)</f>
-        <v/>
-      </c>
-      <c r="H9" s="17">
+        <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$44*1/'Modelo'!$C$16)</f>
+        <v/>
+      </c>
+      <c r="H9" s="12">
         <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="I9" s="12">
-        <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$44*1/'Modelo'!$C$16)</f>
-        <v/>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Costo por persona en el grupo.</t>
         </is>
@@ -3196,31 +3173,27 @@
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$18/'Modelo'!$C$9)</f>
         <v/>
       </c>
       <c r="E10" s="18">
-        <f>IF('Modelo'!$C$9=0,0,1-'Modelo'!$C$18/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$18/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F10" s="12">
+        <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$18)</f>
+        <v/>
+      </c>
       <c r="G10" s="12">
-        <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$18)</f>
-        <v/>
-      </c>
-      <c r="H10" s="17">
+        <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$44*1/'Modelo'!$C$18)</f>
+        <v/>
+      </c>
+      <c r="H10" s="12">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="I10" s="12">
-        <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$44*1/'Modelo'!$C$18)</f>
-        <v/>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Costo por asistente en vivo. Sobre compradores de entrada.</t>
         </is>
@@ -3236,31 +3209,27 @@
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$19/'Modelo'!$C$9)</f>
         <v/>
       </c>
       <c r="E11" s="18">
-        <f>IF('Modelo'!$C$9=0,0,1-'Modelo'!$C$19/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="F11" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$19/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F11" s="12">
+        <f>IF('Modelo'!$C$19=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$19)</f>
+        <v/>
+      </c>
       <c r="G11" s="12">
-        <f>IF('Modelo'!$C$19=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$19)</f>
-        <v/>
-      </c>
-      <c r="H11" s="17">
+        <f>IF('Modelo'!$C$19=0,0,'Modelo'!$C$44*1/'Modelo'!$C$19)</f>
+        <v/>
+      </c>
+      <c r="H11" s="12">
         <f>IF('Modelo'!$C$19=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$19)</f>
         <v/>
       </c>
-      <c r="I11" s="12">
-        <f>IF('Modelo'!$C$19=0,0,'Modelo'!$C$44*1/'Modelo'!$C$19)</f>
-        <v/>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Sobre compradores de entrada.</t>
         </is>
@@ -3276,31 +3245,27 @@
         <f>'Modelo'!$C$22</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$22/'Modelo'!$C$18)</f>
         <v/>
       </c>
       <c r="E12" s="18">
-        <f>IF('Modelo'!$C$18=0,0,1-'Modelo'!$C$22/'Modelo'!$C$18)</f>
-        <v/>
-      </c>
-      <c r="F12" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$22/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F12" s="12">
+        <f>IF('Modelo'!$C$22=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$22)</f>
+        <v/>
+      </c>
       <c r="G12" s="12">
-        <f>IF('Modelo'!$C$22=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$22)</f>
-        <v/>
-      </c>
-      <c r="H12" s="17">
+        <f>IF('Modelo'!$C$22=0,0,'Modelo'!$C$44*1/'Modelo'!$C$22)</f>
+        <v/>
+      </c>
+      <c r="H12" s="12">
         <f>IF('Modelo'!$C$22=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$22)</f>
         <v/>
       </c>
-      <c r="I12" s="12">
-        <f>IF('Modelo'!$C$22=0,0,'Modelo'!$C$44*1/'Modelo'!$C$22)</f>
-        <v/>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Formulario de compra, aplicación o vendedor. Sobre asistentes en vivo.</t>
         </is>
@@ -3316,31 +3281,27 @@
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <f>IF('Modelo'!$C$19=0,0,'Modelo'!$C$23/'Modelo'!$C$19)</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>IF('Modelo'!$C$19=0,0,1-'Modelo'!$C$23/'Modelo'!$C$19)</f>
-        <v/>
-      </c>
-      <c r="F13" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$23/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F13" s="12">
+        <f>IF('Modelo'!$C$23=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$23)</f>
+        <v/>
+      </c>
       <c r="G13" s="12">
-        <f>IF('Modelo'!$C$23=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$23)</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
+        <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$44*1/'Modelo'!$C$23)</f>
+        <v/>
+      </c>
+      <c r="H13" s="12">
         <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="I13" s="12">
-        <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$44*1/'Modelo'!$C$23)</f>
-        <v/>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Sobre los que vieron el replay.</t>
         </is>
@@ -3356,31 +3317,27 @@
         <f>'Modelo'!$C$24</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$24/'Modelo'!$C$9)</f>
         <v/>
       </c>
       <c r="E14" s="18">
-        <f>IF('Modelo'!$C$9=0,0,1-'Modelo'!$C$24/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="F14" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$24/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F14" s="12">
+        <f>IF('Modelo'!$C$24=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$24)</f>
+        <v/>
+      </c>
       <c r="G14" s="12">
-        <f>IF('Modelo'!$C$24=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$24)</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
+        <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$44*1/'Modelo'!$C$24)</f>
+        <v/>
+      </c>
+      <c r="H14" s="12">
         <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$24)</f>
         <v/>
       </c>
-      <c r="I14" s="12">
-        <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$44*1/'Modelo'!$C$24)</f>
-        <v/>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Costo por solicitud. Sobre compradores de entrada.</t>
         </is>
@@ -3396,31 +3353,27 @@
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="17">
         <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$27/'Modelo'!$C$24)</f>
         <v/>
       </c>
       <c r="E15" s="18">
-        <f>IF('Modelo'!$C$24=0,0,1-'Modelo'!$C$27/'Modelo'!$C$24)</f>
-        <v/>
-      </c>
-      <c r="F15" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$27/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F15" s="12">
+        <f>IF('Modelo'!$C$27=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$27)</f>
+        <v/>
+      </c>
       <c r="G15" s="12">
-        <f>IF('Modelo'!$C$27=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$27)</f>
-        <v/>
-      </c>
-      <c r="H15" s="17">
+        <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$44*1/'Modelo'!$C$27)</f>
+        <v/>
+      </c>
+      <c r="H15" s="12">
         <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="I15" s="12">
-        <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$44*1/'Modelo'!$C$27)</f>
-        <v/>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Costo por comprador de la oferta. Sobre solicitudes (cierre).</t>
         </is>
@@ -3436,21 +3389,22 @@
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="17">
         <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$31/'Modelo'!$C$27)</f>
         <v/>
       </c>
       <c r="E16" s="18">
-        <f>IF('Modelo'!$C$27=0,0,1-'Modelo'!$C$31/'Modelo'!$C$27)</f>
-        <v/>
-      </c>
-      <c r="F16" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$31/'Modelo'!$C$9)</f>
         <v/>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3458,12 +3412,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Sobre compradores de la oferta.</t>
         </is>
@@ -3472,53 +3421,70 @@
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>Comprobalo con la fila de la unidad: costo + ganancia + fijos repartidos = techo</t>
+        </is>
+      </c>
+      <c r="F18" s="19">
+        <f>F7</f>
+        <v/>
+      </c>
+      <c r="G18" s="19">
+        <f>G7</f>
+        <v/>
+      </c>
+      <c r="H18" s="12">
+        <f>F7+G7+'Supuestos'!$C$36/'Modelo'!$C$9</f>
+        <v/>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Techo = costo + ganancia + fijos ÷ unidades. Lo que falta entre (costo + ganancia) y el techo son los costos fijos repartidos entre las unidades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Cómo se lee</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Cantidad: cuántas acciones o personas hubo en ese paso con los supuestos del escenario en uso.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>% que pasa: de los que estaban en el paso anterior (o en el paso que indica la nota), cuántos llegan a este. % que se pierde es el complemento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>% acumulado: cuántos llegan a este paso por cada 100 unidades que compra la pauta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
+          <t>% que pasa: de los que estaban en el paso anterior (o en el paso que indica la nota), cuántos llegan a este. % acumulado: cuántos llegan a este paso por cada 100 unidades que compra la pauta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Costo por paso: inversión ÷ cantidad. Es lo que te está costando hoy cada persona que llega a ese paso.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="26" customHeight="1">
+    <row r="23" ht="28" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Techo por paso: lo máximo que podrías pagar por ese paso sin perder plata, si lo demás se mantiene. Comparalo con el costo por paso: si el costo está por encima del techo, ese paso está caro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
+          <t>Ganancia por paso: ganancia del período ÷ cantidad. Lo que te queda por cada persona de ese paso después de pagar la pauta, las comisiones, los reembolsos y los fijos. La ganancia por visita es la métrica más valiosa del embudo: resume todo lo que pasa después.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Ganancia por paso: la ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo: cuánto te queda por cada visita, por cada lead, por cada comprador. La ganancia por visita es la métrica más valiosa del embudo: resume todo lo que pasa después.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
+          <t>Techo por paso: lo que cada persona de ese paso genera en cash neto (cash neto menos costos por unidad, dividido por la cantidad). Es lo máximo que podrías pagar por ese paso antes de que la ganancia llegue a cero, si lo demás se mantiene. Por eso siempre es mayor que la ganancia: techo = costo + ganancia + fijos repartidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Los bumps, las OTOs y la ascensión no tienen costo propio: se pagan con el CPA del comprador principal y se miden por lo que suman al AOV.</t>
@@ -3526,14 +3492,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="B20:J20"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B21:J21"/>
+  <mergeCells count="6">
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -3696,7 +3661,7 @@
           <t>Costo por visita a la página de ventas de la entrada</t>
         </is>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="19">
         <f>IF('Supuestos'!$C$6=1,D10,IF('Supuestos'!$C$6=2,E10,F10))</f>
         <v/>
       </c>
@@ -3739,7 +3704,7 @@
           <t>% de visitas que compran la entrada</t>
         </is>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <f>IF('Supuestos'!$C$6=1,D13,IF('Supuestos'!$C$6=2,E13,F13))</f>
         <v/>
       </c>
@@ -3809,7 +3774,7 @@
           <t>Bump: % de compradores de entrada que lo toman</t>
         </is>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="17">
         <f>IF('Supuestos'!$C$6=1,D16,IF('Supuestos'!$C$6=2,E16,F16))</f>
         <v/>
       </c>
@@ -3848,7 +3813,7 @@
           <t>% que entra al grupo de WhatsApp</t>
         </is>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="17">
         <f>IF('Supuestos'!$C$6=1,D19,IF('Supuestos'!$C$6=2,E19,F19))</f>
         <v/>
       </c>
@@ -3878,7 +3843,7 @@
           <t>% que asiste en vivo</t>
         </is>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="17">
         <f>IF('Supuestos'!$C$6=1,D20,IF('Supuestos'!$C$6=2,E20,F20))</f>
         <v/>
       </c>
@@ -3908,7 +3873,7 @@
           <t>% que ve el replay (sin contar los que fueron en vivo)</t>
         </is>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="17">
         <f>IF('Supuestos'!$C$6=1,D21,IF('Supuestos'!$C$6=2,E21,F21))</f>
         <v/>
       </c>
@@ -3967,7 +3932,7 @@
           <t>% de asistentes en vivo que solicitan (formulario de compra, de aplicación o hablar con un vendedor)</t>
         </is>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="17">
         <f>IF('Supuestos'!$C$6=1,D25,IF('Supuestos'!$C$6=2,E25,F25))</f>
         <v/>
       </c>
@@ -3997,7 +3962,7 @@
           <t>% de los que ven el replay que solicitan</t>
         </is>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="17">
         <f>IF('Supuestos'!$C$6=1,D26,IF('Supuestos'!$C$6=2,E26,F26))</f>
         <v/>
       </c>
@@ -4023,7 +3988,7 @@
           <t>% de solicitudes que terminan en compra</t>
         </is>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="17">
         <f>IF('Supuestos'!$C$6=1,D27,IF('Supuestos'!$C$6=2,E27,F27))</f>
         <v/>
       </c>
@@ -4073,7 +4038,7 @@
           <t>Programa superior: % de compradores de la oferta que lo toman</t>
         </is>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="17">
         <f>IF('Supuestos'!$C$6=1,D29,IF('Supuestos'!$C$6=2,E29,F29))</f>
         <v/>
       </c>
@@ -4667,7 +4632,7 @@
           <t>Costo por asistente en vivo</t>
         </is>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="19">
         <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8/'Modelo'!$C$18)</f>
         <v/>
       </c>
@@ -4740,7 +4705,7 @@
           <t>% de compradores de entrada que solicitan</t>
         </is>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$24/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -4788,7 +4753,7 @@
           <t>% de compradores de entrada que compran la oferta</t>
         </is>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$27/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -4884,7 +4849,7 @@
           <t>Facturado por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="19">
         <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$33/'Modelo'!$C$27)</f>
         <v/>
       </c>
@@ -4900,7 +4865,7 @@
           <t>Ventas de la oferta por entrada (para la proyección)</t>
         </is>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$27/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -4916,7 +4881,7 @@
           <t>Facturado por entrada</t>
         </is>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$33/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -5085,7 +5050,7 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C47" s="18">
+      <c r="C47" s="17">
         <f>IF('Modelo'!$C$38=0,0,'Modelo'!$C$44/'Modelo'!$C$38)</f>
         <v/>
       </c>
@@ -5174,7 +5139,7 @@
           <t>Techo de costo por visita a la página</t>
         </is>
       </c>
-      <c r="C53" s="17">
+      <c r="C53" s="19">
         <f>'Modelo'!$C$50*'Supuestos'!$C$13</f>
         <v/>
       </c>
@@ -5190,7 +5155,7 @@
           <t>Techo de costo por asistente en vivo</t>
         </is>
       </c>
-      <c r="C54" s="17">
+      <c r="C54" s="19">
         <f>IF('Supuestos'!$C$20=0,0,'Modelo'!$C$50/'Supuestos'!$C$20)</f>
         <v/>
       </c>
@@ -5222,7 +5187,7 @@
           <t>Techo de costo por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C56" s="17">
+      <c r="C56" s="19">
         <f>IF('Modelo'!$C$28=0,0,'Modelo'!$C$50/'Modelo'!$C$28)</f>
         <v/>
       </c>
@@ -5238,7 +5203,7 @@
           <t>Objetivo de costo por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C57" s="17">
+      <c r="C57" s="19">
         <f>'Modelo'!$C$56/(1+'Supuestos'!$C$45)</f>
         <v/>
       </c>
@@ -5368,7 +5333,7 @@
           <t>Ganancia por asistente en vivo</t>
         </is>
       </c>
-      <c r="C66" s="17">
+      <c r="C66" s="19">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$44/'Modelo'!$C$18)</f>
         <v/>
       </c>
@@ -5384,7 +5349,7 @@
           <t>Ganancia por solicitud</t>
         </is>
       </c>
-      <c r="C67" s="17">
+      <c r="C67" s="19">
         <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$44/'Modelo'!$C$24)</f>
         <v/>
       </c>
@@ -6076,23 +6041,23 @@
           <t>Costo máximo (facturado por unidad ÷ ROAS)</t>
         </is>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="19">
         <f>IF(C44=0,0,'Modelo'!$C$36/C44)</f>
         <v/>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="19">
         <f>IF(D44=0,0,'Modelo'!$C$36/D44)</f>
         <v/>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="19">
         <f>IF(E44=0,0,'Modelo'!$C$36/E44)</f>
         <v/>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="19">
         <f>IF(F44=0,0,'Modelo'!$C$36/F44)</f>
         <v/>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="19">
         <f>IF(G44=0,0,'Modelo'!$C$36/G44)</f>
         <v/>
       </c>
@@ -6366,7 +6331,7 @@
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
@@ -6394,7 +6359,7 @@
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
@@ -6422,7 +6387,7 @@
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
@@ -6450,7 +6415,7 @@
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
@@ -6478,7 +6443,7 @@
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
@@ -6506,7 +6471,7 @@
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
@@ -6534,7 +6499,7 @@
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
@@ -6562,7 +6527,7 @@
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
@@ -6590,7 +6555,7 @@
         <f>D15-$D$6</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <f>IF($D$6=0,0,E15/ABS($D$6))</f>
         <v/>
       </c>
@@ -8083,15 +8048,15 @@
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N9=0,0,N7/N9))</f>
         <v/>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="19">
         <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
         <v/>
       </c>
-      <c r="P20" s="17">
+      <c r="P20" s="19">
         <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
         <v/>
       </c>
-      <c r="Q20" s="17">
+      <c r="Q20" s="19">
         <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
         <v/>
       </c>
@@ -8102,63 +8067,63 @@
           <t>% visita → entrada</t>
         </is>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="17">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C8=0,0,C9/C8))</f>
         <v/>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="17">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D8=0,0,D9/D8))</f>
         <v/>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="17">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E8=0,0,E9/E8))</f>
         <v/>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="17">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F8=0,0,F9/F8))</f>
         <v/>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="17">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G8=0,0,G9/G8))</f>
         <v/>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="17">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H8=0,0,H9/H8))</f>
         <v/>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="17">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I8=0,0,I9/I8))</f>
         <v/>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="17">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J8=0,0,J9/J8))</f>
         <v/>
       </c>
-      <c r="K21" s="18">
+      <c r="K21" s="17">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K8=0,0,K9/K8))</f>
         <v/>
       </c>
-      <c r="L21" s="18">
+      <c r="L21" s="17">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L8=0,0,L9/L8))</f>
         <v/>
       </c>
-      <c r="M21" s="18">
+      <c r="M21" s="17">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M8=0,0,M9/M8))</f>
         <v/>
       </c>
-      <c r="N21" s="18">
+      <c r="N21" s="17">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N8=0,0,N9/N8))</f>
         <v/>
       </c>
-      <c r="O21" s="18">
+      <c r="O21" s="17">
         <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
         <v/>
       </c>
-      <c r="P21" s="18">
+      <c r="P21" s="17">
         <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
         <v/>
       </c>
-      <c r="Q21" s="18">
+      <c r="Q21" s="17">
         <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
         <v/>
       </c>
@@ -8236,63 +8201,63 @@
           <t>% entrada → en vivo</t>
         </is>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="17">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C9=0,0,C12/C9))</f>
         <v/>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="17">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D9=0,0,D12/D9))</f>
         <v/>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="17">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E9=0,0,E12/E9))</f>
         <v/>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="17">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F9=0,0,F12/F9))</f>
         <v/>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="17">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G9=0,0,G12/G9))</f>
         <v/>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="17">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H9=0,0,H12/H9))</f>
         <v/>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="17">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I9=0,0,I12/I9))</f>
         <v/>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="17">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J9=0,0,J12/J9))</f>
         <v/>
       </c>
-      <c r="K23" s="18">
+      <c r="K23" s="17">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K9=0,0,K12/K9))</f>
         <v/>
       </c>
-      <c r="L23" s="18">
+      <c r="L23" s="17">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L9=0,0,L12/L9))</f>
         <v/>
       </c>
-      <c r="M23" s="18">
+      <c r="M23" s="17">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M9=0,0,M12/M9))</f>
         <v/>
       </c>
-      <c r="N23" s="18">
+      <c r="N23" s="17">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N9=0,0,N12/N9))</f>
         <v/>
       </c>
-      <c r="O23" s="18">
+      <c r="O23" s="17">
         <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
         <v/>
       </c>
-      <c r="P23" s="18">
+      <c r="P23" s="17">
         <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
         <v/>
       </c>
-      <c r="Q23" s="18">
+      <c r="Q23" s="17">
         <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
         <v/>
       </c>
@@ -8303,63 +8268,63 @@
           <t>Ventas ÷ asistentes en vivo</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="17">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C12=0,0,C15/C12))</f>
         <v/>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="17">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D12=0,0,D15/D12))</f>
         <v/>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="17">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E12=0,0,E15/E12))</f>
         <v/>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="17">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F12=0,0,F15/F12))</f>
         <v/>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="17">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G12=0,0,G15/G12))</f>
         <v/>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="17">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H12=0,0,H15/H12))</f>
         <v/>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="17">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I12=0,0,I15/I12))</f>
         <v/>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="17">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J12=0,0,J15/J12))</f>
         <v/>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="17">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K12=0,0,K15/K12))</f>
         <v/>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="17">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L12=0,0,L15/L12))</f>
         <v/>
       </c>
-      <c r="M24" s="18">
+      <c r="M24" s="17">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M12=0,0,M15/M12))</f>
         <v/>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="17">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N12=0,0,N15/N12))</f>
         <v/>
       </c>
-      <c r="O24" s="18">
+      <c r="O24" s="17">
         <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
         <v/>
       </c>
-      <c r="P24" s="18">
+      <c r="P24" s="17">
         <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
         <v/>
       </c>
-      <c r="Q24" s="18">
+      <c r="Q24" s="17">
         <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
         <v/>
       </c>
@@ -8370,63 +8335,63 @@
           <t>Costo por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="19">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C15=0,0,C7/C15))</f>
         <v/>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="19">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D15=0,0,D7/D15))</f>
         <v/>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="19">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E15=0,0,E7/E15))</f>
         <v/>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="19">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F15=0,0,F7/F15))</f>
         <v/>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="19">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G15=0,0,G7/G15))</f>
         <v/>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="19">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H15=0,0,H7/H15))</f>
         <v/>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="19">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I15=0,0,I7/I15))</f>
         <v/>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="19">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J15=0,0,J7/J15))</f>
         <v/>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="19">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K15=0,0,K7/K15))</f>
         <v/>
       </c>
-      <c r="L25" s="17">
+      <c r="L25" s="19">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L15=0,0,L7/L15))</f>
         <v/>
       </c>
-      <c r="M25" s="17">
+      <c r="M25" s="19">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M15=0,0,M7/M15))</f>
         <v/>
       </c>
-      <c r="N25" s="17">
+      <c r="N25" s="19">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N15=0,0,N7/N15))</f>
         <v/>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="19">
         <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
         <v/>
       </c>
-      <c r="P25" s="17">
+      <c r="P25" s="19">
         <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
         <v/>
       </c>
-      <c r="Q25" s="17">
+      <c r="Q25" s="19">
         <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
         <v/>
       </c>
@@ -8437,63 +8402,63 @@
           <t>Costo por persona en el grupo</t>
         </is>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="19">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C11=0,0,C7/C11))</f>
         <v/>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="19">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D11=0,0,D7/D11))</f>
         <v/>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="19">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E11=0,0,E7/E11))</f>
         <v/>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="19">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F11=0,0,F7/F11))</f>
         <v/>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="19">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G11=0,0,G7/G11))</f>
         <v/>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="19">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H11=0,0,H7/H11))</f>
         <v/>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="19">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I11=0,0,I7/I11))</f>
         <v/>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="19">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J11=0,0,J7/J11))</f>
         <v/>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="19">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K11=0,0,K7/K11))</f>
         <v/>
       </c>
-      <c r="L26" s="17">
+      <c r="L26" s="19">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L11=0,0,L7/L11))</f>
         <v/>
       </c>
-      <c r="M26" s="17">
+      <c r="M26" s="19">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M11=0,0,M7/M11))</f>
         <v/>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="19">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N11=0,0,N7/N11))</f>
         <v/>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="19">
         <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
         <v/>
       </c>
-      <c r="P26" s="17">
+      <c r="P26" s="19">
         <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
         <v/>
       </c>
-      <c r="Q26" s="17">
+      <c r="Q26" s="19">
         <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
         <v/>
       </c>
@@ -8504,63 +8469,63 @@
           <t>% en vivo → solicitud</t>
         </is>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="17">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C12=0,0,C14/C12))</f>
         <v/>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="17">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D12=0,0,D14/D12))</f>
         <v/>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="17">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E12=0,0,E14/E12))</f>
         <v/>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="17">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F12=0,0,F14/F12))</f>
         <v/>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="17">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G12=0,0,G14/G12))</f>
         <v/>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="17">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H12=0,0,H14/H12))</f>
         <v/>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="17">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I12=0,0,I14/I12))</f>
         <v/>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="17">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J12=0,0,J14/J12))</f>
         <v/>
       </c>
-      <c r="K27" s="18">
+      <c r="K27" s="17">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K12=0,0,K14/K12))</f>
         <v/>
       </c>
-      <c r="L27" s="18">
+      <c r="L27" s="17">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L12=0,0,L14/L12))</f>
         <v/>
       </c>
-      <c r="M27" s="18">
+      <c r="M27" s="17">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M12=0,0,M14/M12))</f>
         <v/>
       </c>
-      <c r="N27" s="18">
+      <c r="N27" s="17">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N12=0,0,N14/N12))</f>
         <v/>
       </c>
-      <c r="O27" s="18">
+      <c r="O27" s="17">
         <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
         <v/>
       </c>
-      <c r="P27" s="18">
+      <c r="P27" s="17">
         <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
         <v/>
       </c>
-      <c r="Q27" s="18">
+      <c r="Q27" s="17">
         <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
         <v/>
       </c>
@@ -8619,15 +8584,15 @@
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N14=0,0,N7/N14))</f>
         <v/>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="19">
         <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
         <v/>
       </c>
-      <c r="P28" s="17">
+      <c r="P28" s="19">
         <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
         <v/>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q28" s="19">
         <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
         <v/>
       </c>
@@ -8638,63 +8603,63 @@
           <t>% solicitud → compra</t>
         </is>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="17">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C14=0,0,C15/C14))</f>
         <v/>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="17">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D14=0,0,D15/D14))</f>
         <v/>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="17">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E14=0,0,E15/E14))</f>
         <v/>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="17">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F14=0,0,F15/F14))</f>
         <v/>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="17">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G14=0,0,G15/G14))</f>
         <v/>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="17">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H14=0,0,H15/H14))</f>
         <v/>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="17">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I14=0,0,I15/I14))</f>
         <v/>
       </c>
-      <c r="J29" s="18">
+      <c r="J29" s="17">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J14=0,0,J15/J14))</f>
         <v/>
       </c>
-      <c r="K29" s="18">
+      <c r="K29" s="17">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K14=0,0,K15/K14))</f>
         <v/>
       </c>
-      <c r="L29" s="18">
+      <c r="L29" s="17">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L14=0,0,L15/L14))</f>
         <v/>
       </c>
-      <c r="M29" s="18">
+      <c r="M29" s="17">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M14=0,0,M15/M14))</f>
         <v/>
       </c>
-      <c r="N29" s="18">
+      <c r="N29" s="17">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N14=0,0,N15/N14))</f>
         <v/>
       </c>
-      <c r="O29" s="18">
+      <c r="O29" s="17">
         <f>IF(COUNT(C29:N29)=0,"",AVERAGE(C29:N29))</f>
         <v/>
       </c>
-      <c r="P29" s="18">
+      <c r="P29" s="17">
         <f>IF(COUNT(C29:N29)=0,"",MAX(C29:N29))</f>
         <v/>
       </c>
-      <c r="Q29" s="18">
+      <c r="Q29" s="17">
         <f>IF(COUNT(C29:N29)=0,"",MIN(C29:N29))</f>
         <v/>
       </c>
@@ -8753,15 +8718,15 @@
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N9=0,0,(N17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-N9*'Supuestos'!$C$35)/N9))</f>
         <v/>
       </c>
-      <c r="O30" s="17">
+      <c r="O30" s="19">
         <f>IF(COUNT(C30:N30)=0,"",AVERAGE(C30:N30))</f>
         <v/>
       </c>
-      <c r="P30" s="17">
+      <c r="P30" s="19">
         <f>IF(COUNT(C30:N30)=0,"",MAX(C30:N30))</f>
         <v/>
       </c>
-      <c r="Q30" s="17">
+      <c r="Q30" s="19">
         <f>IF(COUNT(C30:N30)=0,"",MIN(C30:N30))</f>
         <v/>
       </c>
@@ -8954,15 +8919,15 @@
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N9=0,0,(N17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-N9*'Supuestos'!$C$35-'Supuestos'!$C$36-N7)/N9))</f>
         <v/>
       </c>
-      <c r="O33" s="17">
+      <c r="O33" s="19">
         <f>IF(COUNT(C33:N33)=0,"",AVERAGE(C33:N33))</f>
         <v/>
       </c>
-      <c r="P33" s="17">
+      <c r="P33" s="19">
         <f>IF(COUNT(C33:N33)=0,"",MAX(C33:N33))</f>
         <v/>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q33" s="19">
         <f>IF(COUNT(C33:N33)=0,"",MIN(C33:N33))</f>
         <v/>
       </c>
@@ -9107,63 +9072,63 @@
           <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
         </is>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="19">
         <f>IF(COUNT(C7:C18)&lt;12,"",'Modelo'!$C$51)</f>
         <v/>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="19">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(COUNT(C30:C30)&gt;0,MEDIAN(C30:C30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="19">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(COUNT(C30:D30)&gt;0,MEDIAN(C30:D30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="19">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(COUNT(C30:E30)&gt;0,MEDIAN(C30:E30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="19">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(COUNT(C30:F30)&gt;0,MEDIAN(C30:F30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="19">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(COUNT(D30:G30)&gt;0,MEDIAN(D30:G30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="I36" s="17">
+      <c r="I36" s="19">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(COUNT(E30:H30)&gt;0,MEDIAN(E30:H30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="J36" s="17">
+      <c r="J36" s="19">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(COUNT(F30:I30)&gt;0,MEDIAN(F30:I30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="K36" s="17">
+      <c r="K36" s="19">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(COUNT(G30:J30)&gt;0,MEDIAN(G30:J30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="L36" s="17">
+      <c r="L36" s="19">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(COUNT(H30:K30)&gt;0,MEDIAN(H30:K30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="M36" s="17">
+      <c r="M36" s="19">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(COUNT(I30:L30)&gt;0,MEDIAN(I30:L30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="N36" s="17">
+      <c r="N36" s="19">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(COUNT(J30:M30)&gt;0,MEDIAN(J30:M30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="O36" s="17">
+      <c r="O36" s="19">
         <f>IF(COUNT(C36:N36)=0,"",AVERAGE(C36:N36))</f>
         <v/>
       </c>
-      <c r="P36" s="17">
+      <c r="P36" s="19">
         <f>IF(COUNT(C36:N36)=0,"",MAX(C36:N36))</f>
         <v/>
       </c>
-      <c r="Q36" s="17">
+      <c r="Q36" s="19">
         <f>IF(COUNT(C36:N36)=0,"",MIN(C36:N36))</f>
         <v/>
       </c>

--- a/excel/04_Modelo_Financiero_Embudo_Webinar_Pago.xlsx
+++ b/excel/04_Modelo_Financiero_Embudo_Webinar_Pago.xlsx
@@ -19,8 +19,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chequeos" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licencia" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="Autor_Jesus_Tassarolo">"Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro"</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -34,7 +37,7 @@
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +59,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="008C8C8C"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="6">
@@ -145,8 +153,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -577,274 +586,281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B46"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Modelo financiero · Embudo de webinar pago (evento pago)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Anuncios → página de ventas de la entrada → entrada + bump → grupo de WhatsApp → evento en vivo y replay → oferta → programa superior</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Para qué sirve este modelo</t>
         </is>
       </c>
     </row>
     <row r="6" ht="75" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Es el modelo financiero de un embudo de webinar pago: anuncios que venden una entrada barata a un evento, un grupo de WhatsApp, el evento en vivo (con replay) donde se presenta la oferta principal, y un programa superior que se vende después. Con tus números (o con el ejemplo cargado) te dice cuánto vale cada entrada que comprás con publicidad, hasta cuánto podés pagar por entrada y por cada etapa siguiente, cuánto invertir para una meta de ventas, cuánta caja necesitás y qué palanca mejora más la ganancia.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>La unidad que comprás es la entrada vendida: acá los leads ya son compradores de un low ticket, no registros. Lo primero que se mira es qué parte de la pauta recupera la entrada (ROAS del front); después, escalón por escalón: costo por persona en el grupo, costo por asistente en vivo (mucho más alto que en gratuito porque pagaron), costo por solicitud y cierre, cada uno con su cantidad y su porcentaje.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Cómo usarlo en 6 pasos</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>1. Andá a Supuestos y reemplazá el ejemplo por tus números. Si todavía no tenés datos, dejá el escenario en 1 (conservador) y usá Benchmarks como referencia.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>2. Mirá Resumen: ganancia del lanzamiento, ROAS, el techo y el objetivo de costo por entrada, y el semáforo. Después Embudo: todos los pasos en orden con cuántos pasan, qué porcentaje se pierde y cuánto cuesta cada paso.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>3. Abrí Escenarios para ver qué pasa si cambia el precio, la conversión o el costo. Las celdas amarillas de cada tabla se pueden cambiar.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>4. Abrí Sensibilidad para saber qué variable conviene trabajar primero.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>5. Antes de invertir, mirá Proyección 12 meses: la caja necesaria es la plata que tenés que tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>6. Cuando el embudo esté andando, completá una columna de Seguimiento por lanzamiento. El semáforo te dice si estás pagando de más por cada entrada.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Colores y hojas</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Amarillo = celda que editás vos. Azul = resultado calculado: no lo toques, se recalcula solo.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Resumen, Embudo y Modelo leen de Supuestos. Escenarios y Sensibilidad recalculan el modelo entero cambiando una o dos variables. Proyección usa los mismos supuestos mes a mes. Seguimiento es la única hoja, además de Supuestos, donde cargás datos.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Chequeos avisa si un supuesto quedó fuera de rango. Si dice REVISAR, arreglalo antes de leer los resultados.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Cómo elegir escenario: en Supuestos, la celda 'Escenario en uso' (1, 2 o 3) elige la columna conservador, base u optimista de cada fila que tiene tres valores. Las filas con un solo valor se usan tal cual.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>El ejemplo que viene cargado</t>
         </is>
       </c>
     </row>
     <row r="24" ht="45" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Un taller pago con entradas a 9 USD promedio (si escalonás 5, 10 y 15, poné el promedio cobrado). Se invierten 3.000 USD por lanzamiento a 0,35 por visita: 8.571 visitas, el 2,5 % compra la entrada (214 entradas, costo por entrada 14) y el 20 % suma un bump de 27.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>El 85 % entra al grupo (costo por persona en el grupo cerca de 16), el 55 % asiste en vivo (costo por asistente cerca de 25) y el 25 % ve el replay. Cuando se presenta la oferta de 497, el 16 % de los asistentes en vivo solicita y el 4 % de los del replay; la mitad de las solicitudes termina en compra: unas 10 ventas, con un costo por solicitud cerca de 140. El 10 % de los compradores pasa a un programa de 1.997.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Costos: pasarela 8 %, reembolsos 5 %, 0,30 por entrada en WhatsApp y soporte, fijos 800 por lanzamiento. Cobranza 50 / 25 / 25.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Resultado: la entrada y el bump recuperan cerca del 100 % de la pauta en facturado (un 90 % en cash neto) antes del evento; la oferta y el programa son la ganancia. Cambiá los números por los tuyos.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Reglas de decisión (el protocolo corto)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>1. Antes de invertir: cargá tus números en Supuestos (si no tenés datos, escenario 1, conservador) y mirá en Resumen el techo y el objetivo de costo por entrada.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>2. Primeros días: compará tu costo real por entrada con el objetivo. Verde: seguí. Amarillo: no subas la inversión y revisá en este orden: CPM (público y frecuencia), creativo (CTR) y página (conversión). Rojo: bajá un escalón (−25 %) y arreglá antes de volver a subir.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>3. Cada lanzamiento: completá una columna de Seguimiento. El semáforo compara tu costo con el techo móvil (lo que rindieron tus últimas 4 columnas), no con un número fijo.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>4. Subí la inversión de a 25 % y esperá 7 días (o 3 a 4 eventos si vendés por llamada) antes de volver a subir. Un día bueno o malo no decide nada.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>5. Si el costo está en verde y aun así no hay ganancia, el problema no es el tráfico: mirá asistencia, conversión de la oferta y cobranza, en ese orden.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>6. Cambiá una sola cosa por vez. Si cambiás precio, creativo y página la misma semana no vas a saber qué funcionó.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>7. Trabajá siempre con cash neto (lo que entra menos comisiones y reembolsos), nunca con facturado. En Proyección ves cuánta caja necesitás para sostener la pauta mientras cobrás.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="45" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>8. El ROAS del front (entradas + bump ÷ inversión) es el seguro del embudo: si está cerca de 1, el evento se paga solo y todo lo demás es ganancia. Si cae por debajo de 0,5, revisá precio de la entrada y página de ventas antes que nada.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Lo que este modelo no hace</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>No adivina tus conversiones: usa las que cargás. Cuando una conversión cambia, el techo cambia; por eso Seguimiento recalcula el techo móvil con tus últimas 4 columnas.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>No reemplaza la decisión: la informa. Las reglas de arriba dicen qué hacer con cada color.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Los benchmarks son orden de magnitud para tráfico frío en español. Tus datos mandan.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Autor y versión</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro. v1.2 · octubre 2026. Fórmulas compatibles con Excel, Google Sheets y Numbers. Sin macros.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Este modelo se comparte para que lo uses con tus números. Si lo compartís, dejá esta línea: es la forma de saber de dónde salió.</t>
         </is>
@@ -853,10 +869,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -869,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -882,52 +898,59 @@
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Benchmarks: contra qué comparar tus números</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Valores de referencia para tráfico frío en español. Son orden de magnitud, no objetivo: tus propios datos de Seguimiento mandan.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Malo</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Bueno</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Ganador</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Tu valor (Modelo)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Fuente / nota</t>
         </is>
@@ -959,11 +982,11 @@
           <t>&gt;1,2</t>
         </is>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="28">
         <f>'Modelo'!$C$14</f>
         <v/>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Eventos pagos hispanos, 2025 a 2026. Cerca de 1 el evento se paga solo.</t>
         </is>
@@ -995,11 +1018,11 @@
           <t>&gt;3,5 %</t>
         </is>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="18">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Página de ventas de 5 a 15 USD.</t>
         </is>
@@ -1031,11 +1054,11 @@
           <t>&lt;8</t>
         </is>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="20">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Depende del precio: compará contra tu precio de entrada.</t>
         </is>
@@ -1067,11 +1090,11 @@
           <t>&gt;65 %</t>
         </is>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="18">
         <f>'Supuestos'!$C$20</f>
         <v/>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Pagaron: asisten mucho más que en gratuito (10 a 20 %).</t>
         </is>
@@ -1103,11 +1126,11 @@
           <t>&lt;10</t>
         </is>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="20">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Sobre compradores de entrada: casi todos entran.</t>
         </is>
@@ -1139,11 +1162,11 @@
           <t>&gt;22 %</t>
         </is>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="18">
         <f>'Supuestos'!$C$25</f>
         <v/>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Público que pagó por estar: solicita más que en gratuito.</t>
         </is>
@@ -1175,11 +1198,11 @@
           <t>&lt;80</t>
         </is>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="20">
         <f>'Modelo'!$C$26</f>
         <v/>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Oferta de 300 a 1.000.</t>
         </is>
@@ -1211,11 +1234,11 @@
           <t>&gt;65 %</t>
         </is>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="18">
         <f>'Supuestos'!$C$27</f>
         <v/>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Con vendedor: 40 a 60 %. Compra directa en el formulario: más alto.</t>
         </is>
@@ -1247,11 +1270,11 @@
           <t>&gt;10 %</t>
         </is>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="19">
         <f>'Modelo'!$C$28</f>
         <v/>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Vivo + replay.</t>
         </is>
@@ -1283,11 +1306,11 @@
           <t>&gt;3</t>
         </is>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="28">
         <f>'Modelo'!$C$46</f>
         <v/>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Por lanzamiento, cobranza completa.</t>
         </is>
@@ -1296,10 +1319,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -1312,7 +1335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D43"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1321,44 +1344,51 @@
     <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Glosario</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Los términos que usa este modelo, en el orden del embudo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Término</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Qué es</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Dónde aparece</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Costo por mil impresiones: lo que cobra la plataforma de anuncios por mostrar el aviso mil veces.</t>
         </is>
@@ -1370,12 +1400,12 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>CTR</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de impresiones que terminan en clic al enlace.</t>
         </is>
@@ -1387,12 +1417,12 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Clic → visita</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de clics que llegan a cargar la página. Siempre menor a 100 % (cierran antes de que cargue).</t>
         </is>
@@ -1404,12 +1434,12 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Unidad de adquisición</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Lo que compra la publicidad en este embudo (visita, registro o entrada). Todo el modelo se mide por unidad.</t>
         </is>
@@ -1421,12 +1451,12 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Costo por unidad</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Inversión dividida por unidades compradas: costo por visita, CPL (costo por lead o registro) o costo por entrada.</t>
         </is>
@@ -1438,12 +1468,12 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Conversión</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Porcentaje que pasa de una etapa a la siguiente. Las conversiones se multiplican: 15 % × 14 % × 44 % = 0,9 %.</t>
         </is>
@@ -1455,12 +1485,12 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Show rate</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de registrados (o compradores) que asisten en vivo. El replay se cuenta aparte.</t>
         </is>
@@ -1472,12 +1502,12 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Oferta extra en el mismo checkout, con una casilla. Se mide como % de los compradores.</t>
         </is>
@@ -1489,12 +1519,12 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>OTO / upsell</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Oferta que aparece después de pagar (one-time offer). Downsell: la oferta más barata para quien rechaza la OTO.</t>
         </is>
@@ -1506,12 +1536,12 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Producto de mayor valor que se vende después del primero, por ascenso o por llamada.</t>
         </is>
@@ -1523,12 +1553,12 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Facturado promedio por comprador del producto principal, sumando toda la escalera.</t>
         </is>
@@ -1540,12 +1570,12 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>CPA / CAC</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Costo por comprador: inversión dividida por ventas del producto principal.</t>
         </is>
@@ -1557,12 +1587,12 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Facturado</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Lo vendido a precio de lista, aunque todavía no se haya cobrado (cuotas).</t>
         </is>
@@ -1574,12 +1604,12 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Cash cobrado</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Lo que efectivamente entró. Con cuotas, entra en varios meses según la curva de cobranza.</t>
         </is>
@@ -1591,12 +1621,12 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Cash neto</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Cash cobrado menos comisiones de pasarela, comisiones de ventas y reembolsos. Es la base de verdad del modelo.</t>
         </is>
@@ -1608,12 +1638,12 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Retorno sobre la inversión en publicidad. Sobre facturado, sobre cash o sobre cash neto: siempre decí cuál.</t>
         </is>
@@ -1625,12 +1655,12 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Valor neto por unidad (VPU)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Cash neto que deja cada unidad de adquisición, descontando los costos que crecen con el volumen. Es lo que vale un lead, una visita o una entrada.</t>
         </is>
@@ -1642,12 +1672,12 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Techo</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Costo por unidad al que no ganás ni perdés (break-even). Es igual al valor neto por unidad.</t>
         </is>
@@ -1659,12 +1689,12 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Techo dividido por (1 + margen de seguridad). Si pagás eso o menos, estás en verde.</t>
         </is>
@@ -1676,12 +1706,12 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Colchón entre el techo y el objetivo para absorber varianza, reembolsos y costos que no viste. 30 % es el estándar.</t>
         </is>
@@ -1693,12 +1723,12 @@
       </c>
     </row>
     <row r="26" ht="60" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Semáforo</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Rojo: el costo por unidad está por encima del techo (perdés con cada unidad). Verde: el costo está en el objetivo o por debajo y el ROAS sobre cash neto llega al objetivo. Amarillo: todo lo demás (el costo está entre objetivo y techo, o el ROAS no llega).</t>
         </is>
@@ -1710,12 +1740,12 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Techo móvil</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Mediana del valor neto por unidad de tus últimas 4 columnas de Seguimiento. Es el techo que se usa para decidir, porque refleja tu rendimiento reciente.</t>
         </is>
@@ -1727,12 +1757,12 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Conjunto de supuestos conservador, base u optimista. Se elige con una celda en Supuestos.</t>
         </is>
@@ -1744,12 +1774,12 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Sensibilidad</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Cuánto cambia la ganancia si mejorás una sola variable un 10 %. Dice qué palanca trabajar primero.</t>
         </is>
@@ -1761,12 +1791,12 @@
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Ganancia por visita / por lead / por cliente</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>La ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo por paso. La ganancia por visita es la métrica que más vale: resume todo lo que pasa después de la página.</t>
         </is>
@@ -1778,12 +1808,12 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Order value (AOV)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Facturado promedio por comprador del principal sumando toda la escalera. El AOV neto es lo mismo después de comisiones y reembolsos, y su par es el CPA.</t>
         </is>
@@ -1795,12 +1825,12 @@
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Caja necesaria</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>El peor momento de la ganancia acumulada en la proyección, en positivo. Es la plata que necesitás tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
         </is>
@@ -1812,12 +1842,12 @@
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Unit economics</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Los números por unidad: cuánto cuesta y cuánto deja cada visita, registro, entrada o comprador.</t>
         </is>
@@ -1829,12 +1859,12 @@
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Tráfico frío</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Gente que no te conoce y llega desde un anuncio. Convierte menos que tu audiencia propia.</t>
         </is>
@@ -1846,12 +1876,12 @@
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Front / producto principal</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>El primer producto que se vende en el embudo. Todo lo demás (bumps, OTOs, programa) se mide como % de sus compradores.</t>
         </is>
@@ -1863,12 +1893,12 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Pitch</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>La parte del webinar o la llamada donde se presenta la oferta.</t>
         </is>
@@ -1880,12 +1910,12 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>VSL</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Video de ventas: la página de ventas es un video largo que vende el producto.</t>
         </is>
@@ -1897,12 +1927,12 @@
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Negocios que venden a empresas. Sus benchmarks de asistencia son más altos que los de tráfico frío a personas.</t>
         </is>
@@ -1914,12 +1944,12 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Self-serve</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Venta sin llamada: la persona compra sola desde una página de pago.</t>
         </is>
@@ -1931,12 +1961,12 @@
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Entrada</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>El producto barato (5 a 15 USD) que da acceso al evento. Es la unidad de adquisición de este embudo.</t>
         </is>
@@ -1948,12 +1978,12 @@
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>ROAS del front</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Facturado de entradas y bump dividido por la inversión: qué parte de la pauta se recupera antes del evento.</t>
         </is>
@@ -1965,12 +1995,12 @@
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Precio escalonado</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Entrada que sube de precio a medida que se acerca el evento (5 → 10 → 15). En el modelo se usa el promedio cobrado.</t>
         </is>
@@ -1982,12 +2012,12 @@
       </c>
     </row>
     <row r="43" ht="45" customHeight="1">
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Solicitud</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Lo que hace el asistente cuando se presenta la oferta: completa el formulario de compra, la aplicación, o pide hablar con un vendedor. Se mide en cantidad, costo por solicitud y % sobre asistentes en vivo.</t>
         </is>
@@ -2001,10 +2031,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -2017,7 +2047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2026,32 +2056,39 @@
     <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Chequeos: el modelo se revisa solo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Si alguna fila dice REVISAR, hay un supuesto fuera de rango o un dato inconsistente.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Chequeo</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Qué revisar</t>
         </is>
@@ -2063,11 +2100,11 @@
           <t>Ninguna celda con error en Modelo</t>
         </is>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="36">
         <f>IF(ISERROR(SUM('Modelo'!C5:C160)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2079,11 +2116,11 @@
           <t>Ninguna celda con error en Embudo</t>
         </is>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="36">
         <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2095,11 +2132,11 @@
           <t>Ninguna celda con error en Resumen</t>
         </is>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="36">
         <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2111,11 +2148,11 @@
           <t>Ninguna celda con error en Proyección 12 meses</t>
         </is>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="36">
         <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2127,11 +2164,11 @@
           <t>Ninguna celda con error en Escenarios</t>
         </is>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="36">
         <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2143,11 +2180,11 @@
           <t>Ninguna celda con error en Seguimiento</t>
         </is>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2159,11 +2196,11 @@
           <t>Los supuestos de tráfico son mayores a cero</t>
         </is>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="36">
         <f>IF(AND('Supuestos'!$C$10&gt;0,'Supuestos'!$C$13&gt;0),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
         </is>
@@ -2175,11 +2212,11 @@
           <t>La curva de cobranza suma 100 %</t>
         </is>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="36">
         <f>IF(ABS('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41-1)&lt;0.001,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
         </is>
@@ -2191,11 +2228,11 @@
           <t>Comisiones + reembolsos menores al 60 %</t>
         </is>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="36">
         <f>IF(('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)&lt;0.6,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Si suman más, revisá los porcentajes.</t>
         </is>
@@ -2207,11 +2244,11 @@
           <t>El escenario en uso es 1, 2 o 3</t>
         </is>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Supuestos → celda 'Escenario en uso'.</t>
         </is>
@@ -2223,11 +2260,11 @@
           <t>La inversión es mayor a cero</t>
         </is>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="36">
         <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -2235,11 +2272,11 @@
           <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
         </is>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="36">
         <f>IF('Modelo'!$C$28&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
         </is>
@@ -2251,11 +2288,11 @@
           <t>Las conversiones están entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="36">
         <f>IF(AND('Supuestos'!$C$13&gt;=0,'Supuestos'!$C$13&lt;=1,'Supuestos'!$C$16&gt;=0,'Supuestos'!$C$16&lt;=1,'Supuestos'!$C$19&gt;=0,'Supuestos'!$C$19&lt;=1,'Supuestos'!$C$20&gt;=0,'Supuestos'!$C$20&lt;=1,'Supuestos'!$C$21&gt;=0,'Supuestos'!$C$21&lt;=1,'Supuestos'!$C$25&gt;=0,'Supuestos'!$C$25&lt;=1,'Supuestos'!$C$26&gt;=0,'Supuestos'!$C$26&lt;=1,'Supuestos'!$C$27&gt;=0,'Supuestos'!$C$27&lt;=1,'Supuestos'!$C$29&gt;=0,'Supuestos'!$C$29&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
         </is>
@@ -2267,11 +2304,11 @@
           <t>El margen de seguridad está entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="36">
         <f>IF(AND('Supuestos'!$C$45&gt;=0,'Supuestos'!$C$45&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -2279,11 +2316,11 @@
           <t>El crecimiento mensual está entre −50 % y 100 %</t>
         </is>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="36">
         <f>IF(AND('Supuestos'!$C$47&gt;=-0.5,'Supuestos'!$C$47&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Más de 100 % por mes no es realista para una proyección.</t>
         </is>
@@ -2295,11 +2332,11 @@
           <t>La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
         </is>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="36">
         <f>IF(AND('Modelo'!$C$9&lt;='Modelo'!$C$7,'Modelo'!$C$18&lt;='Modelo'!$C$9,'Modelo'!$C$22&lt;='Modelo'!$C$18,'Modelo'!$C$23&lt;='Modelo'!$C$19,'Modelo'!$C$27&lt;='Modelo'!$C$24),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Si falla, alguna conversión está por encima de 100 %.</t>
         </is>
@@ -2311,23 +2348,23 @@
           <t>En vivo + replay no superan el 100 % de los compradores</t>
         </is>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="36">
         <f>IF(('Supuestos'!$C$20+'Supuestos'!$C$21)&lt;=1,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>El replay se cuenta sin los que fueron en vivo.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Estado general del modelo</t>
         </is>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="37">
         <f>IF(COUNTIF(C6:C22,"REVISAR")=0,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -2343,13 +2380,87 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Autoría y licencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Modelo financiero · Embudo de webinar pago (evento pago)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>v1.2 · octubre 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Licencia Creative Commons BY-NC-ND 4.0: podés usar este archivo con tus números y compartirlo tal cual, citando al autor. No podés venderlo, modificar su estructura para redistribuirlo ni quitar la línea de autoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Este archivo, sus fórmulas, sus umbrales y su método son obra de Jesús Tassarolo (TooAudience). Si lo compartís, compartilo entero y con esta hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Canal: youtube.com/@JesusTassaroloSinFiltro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2359,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D42"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2368,45 +2479,52 @@
     <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Resumen: lo que hay que mirar</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Todo sale de Modelo con los supuestos del escenario en uso. Cambiá Supuestos y esto se actualiza.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Qué significa</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Resultado del lanzamiento</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2414,11 +2532,11 @@
           <t>Ganancia del período</t>
         </is>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <f>'Modelo'!$C$44</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Cash neto menos costos y menos inversión.</t>
         </is>
@@ -2430,11 +2548,11 @@
           <t>ROAS del front (qué parte de la pauta recupera la entrada)</t>
         </is>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f>'Modelo'!$C$14</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Qué parte de la pauta recupera la entrada antes del evento. Cerca de 1 = el evento se paga solo.</t>
         </is>
@@ -2446,11 +2564,11 @@
           <t>ROAS sobre cash neto</t>
         </is>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <f>'Modelo'!$C$46</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Total, sobre cash neto.</t>
         </is>
@@ -2462,11 +2580,11 @@
           <t>Entradas vendidas</t>
         </is>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Entradas vendidas.</t>
         </is>
@@ -2478,11 +2596,11 @@
           <t>Asistentes en vivo</t>
         </is>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="11">
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Asistentes en vivo.</t>
         </is>
@@ -2494,24 +2612,24 @@
           <t>Ventas de la oferta</t>
         </is>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="12">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Ventas de la oferta (vivo + replay).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Unit economics</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -2519,11 +2637,11 @@
           <t>Costo por entrada vendida</t>
         </is>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="13">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Costo por entrada vendida.</t>
         </is>
@@ -2535,11 +2653,11 @@
           <t>Valor neto por entrada</t>
         </is>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="13">
         <f>'Modelo'!$C$50</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Lo que vale una entrada en cash neto, con todo lo que viene después.</t>
         </is>
@@ -2551,11 +2669,11 @@
           <t>Costo por persona en el grupo</t>
         </is>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="13">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Lo que te cuesta cada persona que entra al grupo.</t>
         </is>
@@ -2567,11 +2685,11 @@
           <t>Costo por asistente en vivo</t>
         </is>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="13">
         <f>'Modelo'!$C$20</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Lo que te cuesta cada asistente en vivo.</t>
         </is>
@@ -2583,11 +2701,11 @@
           <t>Solicitudes (total)</t>
         </is>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="12">
         <f>'Modelo'!$C$24</f>
         <v/>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Formularios de compra, aplicaciones o pedidos de hablar con un vendedor.</t>
         </is>
@@ -2599,11 +2717,11 @@
           <t>Costo por solicitud</t>
         </is>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="13">
         <f>'Modelo'!$C$26</f>
         <v/>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Lo que te cuesta cada solicitud.</t>
         </is>
@@ -2615,24 +2733,24 @@
           <t>Costo por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="13">
         <f>'Modelo'!$C$29</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Lo que te cuesta cada comprador de la oferta.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Las dos caras de cada número</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -2640,11 +2758,11 @@
           <t>Ganancia por visita</t>
         </is>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="13">
         <f>'Modelo'!$C$64</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada visita a la página de ventas. La métrica más valiosa del embudo.</t>
         </is>
@@ -2656,11 +2774,11 @@
           <t>Ganancia por entrada</t>
         </is>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="13">
         <f>'Modelo'!$C$65</f>
         <v/>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada entrada vendida. Su par es el costo por entrada.</t>
         </is>
@@ -2672,11 +2790,11 @@
           <t>Ganancia por cliente</t>
         </is>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="13">
         <f>'Modelo'!$C$68</f>
         <v/>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada comprador de la oferta. Su par es el costo por comprador.</t>
         </is>
@@ -2688,11 +2806,11 @@
           <t>Order value (AOV)</t>
         </is>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="13">
         <f>'Modelo'!$C$34</f>
         <v/>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Facturado por comprador de la oferta, con todo lo demás.</t>
         </is>
@@ -2704,24 +2822,24 @@
           <t>Order value neto (AOV neto)</t>
         </is>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="13">
         <f>'Modelo'!$C$63</f>
         <v/>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Lo mismo después de comisiones, reembolsos y costos por entrada.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Hasta cuánto pagar</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -2729,11 +2847,11 @@
           <t>Techo de costo por entrada (break-even)</t>
         </is>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="13">
         <f>'Modelo'!$C$51</f>
         <v/>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Costo por entrada donde no ganás ni perdés.</t>
         </is>
@@ -2745,11 +2863,11 @@
           <t>Objetivo de costo por entrada</t>
         </is>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="13">
         <f>'Modelo'!$C$52</f>
         <v/>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>A este costo o menos estás en verde.</t>
         </is>
@@ -2761,11 +2879,11 @@
           <t>Techo de costo por visita a la página</t>
         </is>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="13">
         <f>'Modelo'!$C$53</f>
         <v/>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Costo máximo por visita a la página de ventas.</t>
         </is>
@@ -2777,11 +2895,11 @@
           <t>Techo de costo por solicitud</t>
         </is>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="13">
         <f>'Modelo'!$C$55</f>
         <v/>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Costo máximo por solicitud.</t>
         </is>
@@ -2793,11 +2911,11 @@
           <t>Techo de costo por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="13">
         <f>'Modelo'!$C$56</f>
         <v/>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Costo máximo por comprador de la oferta.</t>
         </is>
@@ -2809,24 +2927,24 @@
           <t>Semáforo del costo por entrada actual</t>
         </is>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="14">
         <f>'Modelo'!$C$59</f>
         <v/>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Tu costo por entrada actual contra techo y objetivo.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Cuánto invertir y cuánta caja</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -2834,11 +2952,11 @@
           <t>Inversión necesaria para la meta de ventas de la oferta (al costo actual)</t>
         </is>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="9">
         <f>'Modelo'!$C$60</f>
         <v/>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Para la meta de ventas de Supuestos, al costo actual.</t>
         </is>
@@ -2850,11 +2968,11 @@
           <t>Caja que hay que tener (peor momento de la proyección)</t>
         </is>
       </c>
-      <c r="C36" s="8">
+      <c r="C36" s="9">
         <f>'Proyección 12 meses'!$C$18</f>
         <v/>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Si da 0, el embudo se autofinancia: cada mes cobra más de lo que invierte.</t>
         </is>
@@ -2866,11 +2984,11 @@
           <t>Saldo mínimo de caja con tu caja inicial</t>
         </is>
       </c>
-      <c r="C37" s="8">
+      <c r="C37" s="9">
         <f>'Proyección 12 meses'!$C$19</f>
         <v/>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Si es negativo, la caja inicial no alcanza.</t>
         </is>
@@ -2882,30 +3000,30 @@
           <t>Ganancia acumulada en 12 meses</t>
         </is>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="9">
         <f>'Proyección 12 meses'!$C$20</f>
         <v/>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Con la inversión creciendo según el supuesto.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Recomendación según el semáforo</t>
         </is>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="15">
         <f>IF('Modelo'!$C$59="VERDE","Sostener o subir un escalón (+25 %) y medir 7 días",IF('Modelo'!$C$59="AMARILLO","No subir. Si el costo está bien, el ROAS no llega al objetivo: mirá Sensibilidad. Si no, revisar en orden: CPM, creativo, página",IF('Modelo'!$C$59="ROJO","Bajar un escalón (−25 %) y arreglar antes de volver a subir","")))</f>
         <v/>
       </c>
-      <c r="D40" s="15" t="n"/>
+      <c r="D40" s="16" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · v1.2 · octubre 2026</t>
         </is>
@@ -2928,10 +3046,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -2944,7 +3062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2958,57 +3076,64 @@
     <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Embudo: todos los pasos, cuántos pasan y, por cada uno, qué pagás, qué te queda y hasta cuánto podrías pagar</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cada fila es un paso del embudo en orden. '% que pasa' compara con el paso anterior (o con el que dice la nota). Tres números por paso: lo que pagás hoy por cada uno (inversión ÷ cantidad), lo que te queda por cada uno (ganancia ÷ cantidad) y lo máximo que podrías pagar (el techo: lo que cada uno genera en cash neto). Techo = costo + ganancia + fijos repartidos.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Paso</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>% que pasa</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>% acumulado</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Costo por paso (pagás hoy)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Ganancia por paso (te queda)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Techo por paso (máximo a pagar)</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Qué se paga acá / cómo se lee</t>
         </is>
@@ -3020,7 +3145,7 @@
           <t>Visitas a la página de ventas de la entrada</t>
         </is>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
@@ -3034,55 +3159,55 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="13">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$44*1/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="13">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Costo por visita.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Compran la entrada</t>
         </is>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$9/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$9/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>IF('Modelo'!$C$9=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$44*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Costo por entrada. La unidad de este embudo: acá los leads ya son compradores.</t>
         </is>
@@ -3094,15 +3219,15 @@
           <t>Toman el bump de la entrada</t>
         </is>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="17">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$11/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$11/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -3121,7 +3246,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Sobre compradores de entrada. Suma al ROAS del front.</t>
         </is>
@@ -3133,67 +3258,67 @@
           <t>Entran al grupo de WhatsApp</t>
         </is>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="17">
         <f>'Modelo'!$C$16</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$16/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$16/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <f>IF('Modelo'!$C$16=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="13">
         <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$44*1/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="13">
         <f>IF('Modelo'!$C$16=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Costo por persona en el grupo.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Asisten en vivo</t>
         </is>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="17">
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$18/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$18/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$44*1/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Costo por asistente en vivo. Sobre compradores de entrada.</t>
         </is>
@@ -3205,31 +3330,31 @@
           <t>Ven el replay</t>
         </is>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="17">
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$19/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$19/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>IF('Modelo'!$C$19=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$19)</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>IF('Modelo'!$C$19=0,0,'Modelo'!$C$44*1/'Modelo'!$C$19)</f>
         <v/>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <f>IF('Modelo'!$C$19=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$19)</f>
         <v/>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Sobre compradores de entrada.</t>
         </is>
@@ -3241,31 +3366,31 @@
           <t>Solicitan, de los que estuvieron en vivo</t>
         </is>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="17">
         <f>'Modelo'!$C$22</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$22/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$22/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>IF('Modelo'!$C$22=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$22)</f>
         <v/>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <f>IF('Modelo'!$C$22=0,0,'Modelo'!$C$44*1/'Modelo'!$C$22)</f>
         <v/>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="13">
         <f>IF('Modelo'!$C$22=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$22)</f>
         <v/>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Formulario de compra, aplicación o vendedor. Sobre asistentes en vivo.</t>
         </is>
@@ -3277,103 +3402,103 @@
           <t>Solicitan, de los que vieron el replay</t>
         </is>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="18">
         <f>IF('Modelo'!$C$19=0,0,'Modelo'!$C$23/'Modelo'!$C$19)</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$23/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>IF('Modelo'!$C$23=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$44*1/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <f>IF('Modelo'!$C$23=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$23)</f>
         <v/>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Sobre los que vieron el replay.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Solicitudes (total)</t>
         </is>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="17">
         <f>'Modelo'!$C$24</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$24/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$24/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>IF('Modelo'!$C$24=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$24)</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$44*1/'Modelo'!$C$24)</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$24)</f>
         <v/>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Costo por solicitud. Sobre compradores de entrada.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Compran la oferta</t>
         </is>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="17">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="18">
         <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$27/'Modelo'!$C$24)</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$27/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>IF('Modelo'!$C$27=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$44*1/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$50*'Modelo'!$C$9*1/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Costo por comprador de la oferta. Sobre solicitudes (cierre).</t>
         </is>
@@ -3385,15 +3510,15 @@
           <t>Pasan al programa superior</t>
         </is>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="17">
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="18">
         <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$31/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$31/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -3412,80 +3537,80 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Sobre compradores de la oferta.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Comprobalo con la fila de la unidad: costo + ganancia + fijos repartidos = techo</t>
         </is>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <f>F7</f>
         <v/>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>G7</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <f>F7+G7+'Supuestos'!$C$36/'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Techo = costo + ganancia + fijos ÷ unidades. Lo que falta entre (costo + ganancia) y el techo son los costos fijos repartidos entre las unidades.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Cómo se lee</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Cantidad: cuántas acciones o personas hubo en ese paso con los supuestos del escenario en uso.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>% que pasa: de los que estaban en el paso anterior (o en el paso que indica la nota), cuántos llegan a este. % acumulado: cuántos llegan a este paso por cada 100 unidades que compra la pauta.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Costo por paso: inversión ÷ cantidad. Es lo que te está costando hoy cada persona que llega a ese paso.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Ganancia por paso: ganancia del período ÷ cantidad. Lo que te queda por cada persona de ese paso después de pagar la pauta, las comisiones, los reembolsos y los fijos. La ganancia por visita es la métrica más valiosa del embudo: resume todo lo que pasa después.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Techo por paso: lo que cada persona de ese paso genera en cash neto (cash neto menos costos por unidad, dividido por la cantidad). Es lo máximo que podrías pagar por ese paso antes de que la ganancia llegue a cero, si lo demás se mantiene. Por eso siempre es mayor que la ganancia: techo = costo + ganancia + fijos repartidos.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Los bumps, las OTOs y la ascensión no tienen costo propio: se pagan con el CPA del comprador principal y se miden por lo que suman al AOV.</t>
         </is>
@@ -3502,10 +3627,10 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -3518,7 +3643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H48"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3531,64 +3656,71 @@
     <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Supuestos</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Celdas amarillas = las editás vos. Celdas azules = se calculan solas. Cada fila dice en qué unidad va y de dónde sale el valor del ejemplo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Supuesto</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Valor en uso</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Optimista</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Nota / fuente del ejemplo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Escenario en uso (1 = conservador · 2 = base · 3 = optimista)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="21" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -3596,24 +3728,24 @@
           <t>1 / 2 / 3</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Cambia todas las filas que tienen tres valores. Si una fila no tiene tres valores, se usa el de 'Valor en uso'.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>1. Inversión y tráfico</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -3621,7 +3753,7 @@
           <t>Inversión en publicidad por lanzamiento</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="22" t="n">
         <v>3000</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -3629,7 +3761,7 @@
           <t>USD / lanzamiento</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Un lanzamiento = una tanda de venta de entradas + evento + oferta.</t>
         </is>
@@ -3641,7 +3773,7 @@
           <t>Lanzamientos por mes (para la proyección)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="21" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -3649,7 +3781,7 @@
           <t>lanzamientos / mes</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Cuántos eventos como este hacés por mes. La proyección multiplica inversión, costos fijos y ventas por este número.</t>
         </is>
@@ -3661,17 +3793,17 @@
           <t>Costo por visita a la página de ventas de la entrada</t>
         </is>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <f>IF('Supuestos'!$C$6=1,D10,IF('Supuestos'!$C$6=2,E10,F10))</f>
         <v/>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <v>0.35</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="23" t="n">
         <v>0.25</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -3679,24 +3811,24 @@
           <t>USD / visita</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Lo que pagás por cada persona que llega a la página.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>2. Entrada y bump</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -3704,17 +3836,17 @@
           <t>% de visitas que compran la entrada</t>
         </is>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="18">
         <f>IF('Supuestos'!$C$6=1,D13,IF('Supuestos'!$C$6=2,E13,F13))</f>
         <v/>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <v>0.015</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="24" t="n">
         <v>0.025</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="24" t="n">
         <v>0.035</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -3722,7 +3854,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Página de ventas de un producto de 5 a 15 USD.</t>
         </is>
@@ -3734,7 +3866,7 @@
           <t>Precio promedio cobrado por entrada</t>
         </is>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -3742,7 +3874,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Si escalonás el precio (5 → 10 → 15), poné el promedio que cobrás.</t>
         </is>
@@ -3754,7 +3886,7 @@
           <t>Bump en el checkout de la entrada: precio</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>27</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -3762,7 +3894,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Grabaciones, plantillas, acceso extendido.</t>
         </is>
@@ -3774,17 +3906,17 @@
           <t>Bump: % de compradores de entrada que lo toman</t>
         </is>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="18">
         <f>IF('Supuestos'!$C$6=1,D16,IF('Supuestos'!$C$6=2,E16,F16))</f>
         <v/>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <v>0.12</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="24" t="n">
         <v>0.3</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -3792,20 +3924,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>3. Grupo y asistencia (sobre compradores de entrada)</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -3813,17 +3945,17 @@
           <t>% que entra al grupo de WhatsApp</t>
         </is>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="18">
         <f>IF('Supuestos'!$C$6=1,D19,IF('Supuestos'!$C$6=2,E19,F19))</f>
         <v/>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="24" t="n">
         <v>0.7</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="24" t="n">
         <v>0.85</v>
       </c>
-      <c r="F19" s="23" t="n">
+      <c r="F19" s="24" t="n">
         <v>0.95</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -3831,7 +3963,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Pagaron: entran casi todos.</t>
         </is>
@@ -3843,17 +3975,17 @@
           <t>% que asiste en vivo</t>
         </is>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="18">
         <f>IF('Supuestos'!$C$6=1,D20,IF('Supuestos'!$C$6=2,E20,F20))</f>
         <v/>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="24" t="n">
         <v>0.4</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="24" t="n">
         <v>0.55</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F20" s="24" t="n">
         <v>0.65</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -3861,7 +3993,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Mucho más alto que en gratuito.</t>
         </is>
@@ -3873,17 +4005,17 @@
           <t>% que ve el replay (sin contar los que fueron en vivo)</t>
         </is>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="18">
         <f>IF('Supuestos'!$C$6=1,D21,IF('Supuestos'!$C$6=2,E21,F21))</f>
         <v/>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="24" t="n">
         <v>0.15</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="24" t="n">
         <v>0.25</v>
       </c>
-      <c r="F21" s="23" t="n">
+      <c r="F21" s="24" t="n">
         <v>0.3</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -3891,20 +4023,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>4. Oferta del evento y programa superior</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -3912,7 +4044,7 @@
           <t>Oferta principal: precio</t>
         </is>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="23" t="n">
         <v>497</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -3920,7 +4052,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Lo que se presenta al final del evento.</t>
         </is>
@@ -3932,17 +4064,17 @@
           <t>% de asistentes en vivo que solicitan (formulario de compra, de aplicación o hablar con un vendedor)</t>
         </is>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="18">
         <f>IF('Supuestos'!$C$6=1,D25,IF('Supuestos'!$C$6=2,E25,F25))</f>
         <v/>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="24" t="n">
         <v>0.16</v>
       </c>
-      <c r="F25" s="23" t="n">
+      <c r="F25" s="24" t="n">
         <v>0.22</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -3950,7 +4082,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Público que pagó por estar: solicita más que en un webinar gratuito.</t>
         </is>
@@ -3962,17 +4094,17 @@
           <t>% de los que ven el replay que solicitan</t>
         </is>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="18">
         <f>IF('Supuestos'!$C$6=1,D26,IF('Supuestos'!$C$6=2,E26,F26))</f>
         <v/>
       </c>
-      <c r="D26" s="23" t="n">
+      <c r="D26" s="24" t="n">
         <v>0.02</v>
       </c>
-      <c r="E26" s="23" t="n">
+      <c r="E26" s="24" t="n">
         <v>0.04</v>
       </c>
-      <c r="F26" s="23" t="n">
+      <c r="F26" s="24" t="n">
         <v>0.06</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -3980,7 +4112,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -3988,17 +4120,17 @@
           <t>% de solicitudes que terminan en compra</t>
         </is>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="18">
         <f>IF('Supuestos'!$C$6=1,D27,IF('Supuestos'!$C$6=2,E27,F27))</f>
         <v/>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="24" t="n">
         <v>0.4</v>
       </c>
-      <c r="E27" s="23" t="n">
+      <c r="E27" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="F27" s="23" t="n">
+      <c r="F27" s="24" t="n">
         <v>0.6</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -4006,7 +4138,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Con compra directa en el formulario suele ser alto; con vendedor, 40 a 60 %.</t>
         </is>
@@ -4018,7 +4150,7 @@
           <t>Programa superior: precio</t>
         </is>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="23" t="n">
         <v>1997</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -4026,7 +4158,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Por llamada o por ascenso.</t>
         </is>
@@ -4038,17 +4170,17 @@
           <t>Programa superior: % de compradores de la oferta que lo toman</t>
         </is>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="18">
         <f>IF('Supuestos'!$C$6=1,D29,IF('Supuestos'!$C$6=2,E29,F29))</f>
         <v/>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="24" t="n">
         <v>0.05</v>
       </c>
-      <c r="E29" s="23" t="n">
+      <c r="E29" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="F29" s="23" t="n">
+      <c r="F29" s="24" t="n">
         <v>0.15</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -4056,20 +4188,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>5. Costos</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
@@ -4077,7 +4209,7 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C32" s="23" t="n">
+      <c r="C32" s="24" t="n">
         <v>0.08</v>
       </c>
       <c r="G32" t="inlineStr">
@@ -4085,7 +4217,7 @@
           <t>% del cash</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Hotmart, Stripe, Mercado Pago: lo que se queda la plataforma.</t>
         </is>
@@ -4097,7 +4229,7 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="24" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -4105,7 +4237,7 @@
           <t>% del cash</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Sobre el cash cobrado. Si el programa superior se vende por llamada, poné acá la comisión del closer.</t>
         </is>
@@ -4117,7 +4249,7 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="24" t="n">
         <v>0.05</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -4125,7 +4257,7 @@
           <t>% del cash</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>5 % es normal en productos digitales. Más de 10 % es un problema de oferta o de expectativa.</t>
         </is>
@@ -4137,7 +4269,7 @@
           <t>Costos por entrada (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="n">
+      <c r="C35" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -4145,7 +4277,7 @@
           <t>USD / entrada</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>WhatsApp, soporte, plataforma del evento: lo que pagás por cada entrada.</t>
         </is>
@@ -4157,7 +4289,7 @@
           <t>Costos fijos por lanzamiento</t>
         </is>
       </c>
-      <c r="C36" s="21" t="n">
+      <c r="C36" s="22" t="n">
         <v>800</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -4165,24 +4297,24 @@
           <t>USD / lanzamiento</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Equipo, herramientas, edición: lo que pagás aunque no vendas.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>6. Cobranza</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
@@ -4190,7 +4322,7 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C39" s="23" t="n">
+      <c r="C39" s="24" t="n">
         <v>0.5</v>
       </c>
       <c r="G39" t="inlineStr">
@@ -4198,7 +4330,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Se aplica a todo el facturado como promedio ponderado: la entrada se cobra al contado, la oferta y el programa en cuotas. El ejemplo usa 50 / 25 / 25.</t>
         </is>
@@ -4210,7 +4342,7 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C40" s="23" t="n">
+      <c r="C40" s="24" t="n">
         <v>0.25</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -4218,7 +4350,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Cuotas o pagos diferidos.</t>
         </is>
@@ -4230,7 +4362,7 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C41" s="23" t="n">
+      <c r="C41" s="24" t="n">
         <v>0.25</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -4238,24 +4370,24 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Los tres deben sumar 100 %.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>7. Objetivos y proyección</t>
         </is>
       </c>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
@@ -4263,7 +4395,7 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C44" s="24" t="n">
+      <c r="C44" s="25" t="n">
         <v>2</v>
       </c>
       <c r="G44" t="inlineStr">
@@ -4271,7 +4403,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>El retorno mínimo que querés por cada dólar invertido, después de comisiones y reembolsos. Entra en el semáforo: sin llegar a este ROAS no hay verde.</t>
         </is>
@@ -4283,7 +4415,7 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C45" s="23" t="n">
+      <c r="C45" s="24" t="n">
         <v>0.3</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -4291,7 +4423,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Colchón entre el techo (donde no ganás ni perdés) y el objetivo. 30 % es el estándar que usamos.</t>
         </is>
@@ -4303,7 +4435,7 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="21" t="n">
         <v>25</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -4311,7 +4443,7 @@
           <t>ventas de la oferta / lanzamiento</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Para calcular cuánto invertir.</t>
         </is>
@@ -4323,7 +4455,7 @@
           <t>Crecimiento de la inversión por mes (proyección)</t>
         </is>
       </c>
-      <c r="C47" s="23" t="n">
+      <c r="C47" s="24" t="n">
         <v>0.1</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -4331,7 +4463,7 @@
           <t>% / mes</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Cuánto sube la inversión cada mes en la proyección. 10 % por mes es un ritmo prudente; más de 25 % suele encarecer el CPM.</t>
         </is>
@@ -4343,7 +4475,7 @@
           <t>Caja inicial</t>
         </is>
       </c>
-      <c r="C48" s="21" t="n">
+      <c r="C48" s="22" t="n">
         <v>4000</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -4351,7 +4483,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Con cuánta plata arrancás. La proyección te dice si alcanza.</t>
         </is>
@@ -4360,10 +4492,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -4376,7 +4508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D68"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4385,45 +4517,52 @@
     <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Modelo: la cadena completa del embudo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cada fila es una etapa o un resultado. No se edita: todo sale de Supuestos. La columna de la derecha dice cómo se calcula.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Etapa / resultado</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Cómo se calcula</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Tráfico y entradas</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -4431,43 +4570,43 @@
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>IF('Supuestos'!$C$10=0,0,'Supuestos'!$C$8/'Supuestos'!$C$10)</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ costo por visita.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Costo por entrada vendida</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13)</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Costo por visita ÷ % que compra la entrada.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Entradas vendidas</t>
         </is>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="11">
         <f>IF('Modelo'!$C$8=0,0,'Supuestos'!$C$8/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ costo por entrada.</t>
         </is>
@@ -4479,11 +4618,11 @@
           <t>Facturado: entradas</t>
         </is>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <f>'Modelo'!$C$9*'Supuestos'!$C$14</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Entradas × precio promedio.</t>
         </is>
@@ -4495,11 +4634,11 @@
           <t>Ventas: bump de la entrada</t>
         </is>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>'Modelo'!$C$9*'Supuestos'!$C$16</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Entradas × % que lo toma.</t>
         </is>
@@ -4511,56 +4650,56 @@
           <t>Facturado: bump de la entrada</t>
         </is>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>'Modelo'!$C$11*'Supuestos'!$C$15</f>
         <v/>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Facturado del front (entradas + bump)</t>
         </is>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="9">
         <f>'Modelo'!$C$10+'Modelo'!$C$12</f>
         <v/>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Lo que entra antes del evento.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>ROAS del front (qué parte de la pauta recupera la entrada)</t>
         </is>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$13/'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Facturado del front ÷ inversión. Cerca de 1 = el evento se paga solo.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Grupo y asistencia</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -4568,43 +4707,43 @@
           <t>Personas en el grupo</t>
         </is>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="17">
         <f>'Modelo'!$C$9*'Supuestos'!$C$19</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Entradas × % que entra.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Costo por persona en el grupo</t>
         </is>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="13">
         <f>IF('Modelo'!$C$16=0,0,'Supuestos'!$C$8/'Modelo'!$C$16)</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ personas en el grupo.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Asistentes en vivo</t>
         </is>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="11">
         <f>'Modelo'!$C$9*'Supuestos'!$C$20</f>
         <v/>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Entradas × asistencia en vivo.</t>
         </is>
@@ -4616,11 +4755,11 @@
           <t>Vieron el replay</t>
         </is>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="17">
         <f>'Modelo'!$C$9*'Supuestos'!$C$21</f>
         <v/>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Entradas × % que ve el replay.</t>
         </is>
@@ -4632,24 +4771,24 @@
           <t>Costo por asistente en vivo</t>
         </is>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <f>IF('Modelo'!$C$18=0,0,'Supuestos'!$C$8/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ asistentes.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Solicitudes (formulario de compra, aplicación o vendedor), oferta, programa y facturación</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -4657,11 +4796,11 @@
           <t>Solicitudes: en vivo</t>
         </is>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>'Modelo'!$C$18*'Supuestos'!$C$25</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Asistentes en vivo × % que solicita.</t>
         </is>
@@ -4673,27 +4812,27 @@
           <t>Solicitudes: replay</t>
         </is>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="27">
         <f>'Modelo'!$C$19*'Supuestos'!$C$26</f>
         <v/>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Replay × % que solicita.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Solicitudes (total)</t>
         </is>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="12">
         <f>'Modelo'!$C$22+'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>En vivo + replay.</t>
         </is>
@@ -4705,43 +4844,43 @@
           <t>% de compradores de entrada que solicitan</t>
         </is>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$24/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Solicitudes ÷ entradas.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Costo por solicitud</t>
         </is>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="13">
         <f>IF('Modelo'!$C$24=0,0,'Supuestos'!$C$8/'Modelo'!$C$24)</f>
         <v/>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ solicitudes.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Ventas de la oferta</t>
         </is>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="12">
         <f>'Modelo'!$C$24*'Supuestos'!$C$27</f>
         <v/>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Solicitudes × % que termina en compra.</t>
         </is>
@@ -4753,27 +4892,27 @@
           <t>% de compradores de entrada que compran la oferta</t>
         </is>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$27/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Ventas ÷ entradas.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Costo por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="13">
         <f>IF('Modelo'!$C$27=0,0,'Supuestos'!$C$8/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ ventas de la oferta.</t>
         </is>
@@ -4785,11 +4924,11 @@
           <t>Facturado: oferta</t>
         </is>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="26">
         <f>'Modelo'!$C$27*'Supuestos'!$C$24</f>
         <v/>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
@@ -4801,11 +4940,11 @@
           <t>Ventas: programa superior</t>
         </is>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="27">
         <f>'Modelo'!$C$27*'Supuestos'!$C$29</f>
         <v/>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Compradores de la oferta × % que asciende.</t>
         </is>
@@ -4817,27 +4956,27 @@
           <t>Facturado: programa superior</t>
         </is>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <f>'Modelo'!$C$31*'Supuestos'!$C$28</f>
         <v/>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Facturado total</t>
         </is>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="9">
         <f>'Modelo'!$C$13+'Modelo'!$C$30+'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Front + oferta + programa.</t>
         </is>
@@ -4849,11 +4988,11 @@
           <t>Facturado por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$33/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Facturado total ÷ ventas de la oferta.</t>
         </is>
@@ -4865,11 +5004,11 @@
           <t>Ventas de la oferta por entrada (para la proyección)</t>
         </is>
       </c>
-      <c r="C35" s="18">
+      <c r="C35" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$27/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Igual a '% que compra la oferta'.</t>
         </is>
@@ -4881,24 +5020,24 @@
           <t>Facturado por entrada</t>
         </is>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="20">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$33/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Facturado total ÷ entradas.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Cash, costos y ganancia del período</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
@@ -4906,11 +5045,11 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="26">
         <f>'Modelo'!$C$33*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41)</f>
         <v/>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Facturado × (mes 1 + mes 2 + mes 3). Si la cobranza suma 100 %, es igual al facturado.</t>
         </is>
@@ -4922,11 +5061,11 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="26">
         <f>'Modelo'!$C$33*'Supuestos'!$C$39</f>
         <v/>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Facturado × % del mes 1.</t>
         </is>
@@ -4938,11 +5077,11 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="26">
         <f>'Modelo'!$C$38*('Supuestos'!$C$32+'Supuestos'!$C$33)</f>
         <v/>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Cash × (pasarela + equipo de ventas).</t>
         </is>
@@ -4954,27 +5093,27 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="26">
         <f>'Modelo'!$C$38*'Supuestos'!$C$34</f>
         <v/>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Cash × % de reembolsos.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Cash neto</t>
         </is>
       </c>
-      <c r="C42" s="8">
+      <c r="C42" s="9">
         <f>'Modelo'!$C$38*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Cash − comisiones − reembolsos. La base de verdad.</t>
         </is>
@@ -4986,27 +5125,27 @@
           <t>Costos por entrada (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="26">
         <f>'Modelo'!$C$9*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Entradas × costo por entrada.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Ganancia del período</t>
         </is>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="9">
         <f>'Modelo'!$C$42-'Modelo'!$C$43-'Supuestos'!$C$36-'Supuestos'!$C$8</f>
         <v/>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Cash neto − costos por unidad − fijos − inversión.</t>
         </is>
@@ -5018,27 +5157,27 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="28">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$33/'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Facturado ÷ inversión. El número que más se infla: no decidas con este.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>ROAS sobre cash neto</t>
         </is>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="10">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$42/'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Cash neto ÷ inversión. Con este se decide.</t>
         </is>
@@ -5050,11 +5189,11 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="18">
         <f>IF('Modelo'!$C$38=0,0,'Modelo'!$C$44/'Modelo'!$C$38)</f>
         <v/>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Ganancia ÷ cash.</t>
         </is>
@@ -5066,68 +5205,68 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="29">
         <f>IF('Modelo'!$C$46&gt;='Supuestos'!$C$44,"SÍ","NO")</f>
         <v/>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>ROAS sobre cash neto contra el objetivo de Supuestos.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Cuánto vale cada entrada y hasta cuánto pagar</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Valor neto por entrada</t>
         </is>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="13">
         <f>IF('Modelo'!$C$9=0,0,('Modelo'!$C$42-'Modelo'!$C$43)/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>(Cash neto − costos por entrada) ÷ entradas.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Techo de costo por entrada (break-even)</t>
         </is>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="13">
         <f>'Modelo'!$C$50</f>
         <v/>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Igual al valor neto por entrada.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Objetivo de costo por entrada</t>
         </is>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="13">
         <f>'Modelo'!$C$51/(1+'Supuestos'!$C$45)</f>
         <v/>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Techo ÷ (1 + margen de seguridad).</t>
         </is>
@@ -5139,11 +5278,11 @@
           <t>Techo de costo por visita a la página</t>
         </is>
       </c>
-      <c r="C53" s="19">
+      <c r="C53" s="20">
         <f>'Modelo'!$C$50*'Supuestos'!$C$13</f>
         <v/>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Valor por entrada × % que compra la entrada.</t>
         </is>
@@ -5155,27 +5294,27 @@
           <t>Techo de costo por asistente en vivo</t>
         </is>
       </c>
-      <c r="C54" s="19">
+      <c r="C54" s="20">
         <f>IF('Supuestos'!$C$20=0,0,'Modelo'!$C$50/'Supuestos'!$C$20)</f>
         <v/>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Valor por entrada ÷ asistencia.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Techo de costo por solicitud</t>
         </is>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="13">
         <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$50*'Modelo'!$C$9/'Modelo'!$C$24)</f>
         <v/>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Valor total ÷ solicitudes.</t>
         </is>
@@ -5187,11 +5326,11 @@
           <t>Techo de costo por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C56" s="19">
+      <c r="C56" s="20">
         <f>IF('Modelo'!$C$28=0,0,'Modelo'!$C$50/'Modelo'!$C$28)</f>
         <v/>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Valor por entrada ÷ % que compra la oferta.</t>
         </is>
@@ -5203,52 +5342,52 @@
           <t>Objetivo de costo por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C57" s="19">
+      <c r="C57" s="20">
         <f>'Modelo'!$C$56/(1+'Supuestos'!$C$45)</f>
         <v/>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Techo ÷ (1 + margen de seguridad).</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Semáforo y cuánto invertir</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Semáforo del costo por entrada actual</t>
         </is>
       </c>
-      <c r="C59" s="13">
+      <c r="C59" s="14">
         <f>IF('Modelo'!$C$8&gt;'Modelo'!$C$51,"ROJO",IF(AND('Modelo'!$C$8&lt;='Modelo'!$C$52,'Modelo'!$C$46&gt;='Supuestos'!$C$44),"VERDE","AMARILLO"))</f>
         <v/>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Rojo: costo &gt; techo. Verde: costo ≤ objetivo y ROAS sobre cash neto ≥ objetivo. Amarillo: el resto.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Inversión necesaria para la meta de ventas de la oferta (al costo actual)</t>
         </is>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="9">
         <f>IF('Modelo'!$C$28=0,"inalcanzable con estos supuestos",'Supuestos'!$C$46/'Modelo'!$C$28*'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Meta ÷ % que compra la oferta × costo por entrada.</t>
         </is>
@@ -5260,68 +5399,68 @@
           <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="26">
         <f>IF('Modelo'!$C$28=0,"inalcanzable con estos supuestos",'Supuestos'!$C$46/'Modelo'!$C$28*'Modelo'!$C$52)</f>
         <v/>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Lo mismo, al costo objetivo.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Ganancia por paso (las dos caras de cada número: costo por X y ganancia por X)</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Cash neto por comprador (AOV neto)</t>
         </is>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="13">
         <f>IF('Modelo'!$C$27=0,0,('Modelo'!$C$42-'Modelo'!$C$43)/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Lo que deja cada comprador del principal después de comisiones, reembolsos y costos por unidad. Su par es el CPA.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Ganancia por visita</t>
         </is>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="13">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$44/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ visitas a la página de ventas. La métrica más valiosa: resume todo lo que pasa después. Su par es el costo por visita.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Ganancia por entrada</t>
         </is>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="13">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$44/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ entradas. Su par es el costo por entrada.</t>
         </is>
@@ -5333,11 +5472,11 @@
           <t>Ganancia por asistente en vivo</t>
         </is>
       </c>
-      <c r="C66" s="19">
+      <c r="C66" s="20">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$44/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ asistente en vivos. Su par es el costo por asistente en vivo.</t>
         </is>
@@ -5349,27 +5488,27 @@
           <t>Ganancia por solicitud</t>
         </is>
       </c>
-      <c r="C67" s="19">
+      <c r="C67" s="20">
         <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$44/'Modelo'!$C$24)</f>
         <v/>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ solicituds. Su par es el costo por solicitud.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Ganancia por cliente</t>
         </is>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="13">
         <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$44/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ compradores de la oferta. Su par es el costo por comprador.</t>
         </is>
@@ -5389,10 +5528,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -5405,7 +5544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5421,15 +5560,22 @@
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Escenarios: qué pasa si cambian el precio, la conversión o el costo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Las celdas amarillas de cada tabla (fila y columna) se pueden cambiar. Verde = ganancia, amarillo = cerca del cero, rojo = pérdida. Todo lo demás queda como en Supuestos.</t>
         </is>
@@ -5441,597 +5587,597 @@
           <t>Umbral de 'cerca del cero' (inversión × margen de seguridad)</t>
         </is>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$45</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Precio de la oferta × % de solicitudes que terminan en compra → ganancia del lanzamiento</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>A más precio, menos cierre: la tabla muestra qué combinación gana.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Precio ↓  /  % solicitud → compra →</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.4</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="30" t="n">
         <v>0.5</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="30" t="n">
         <v>0.6</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="30" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="31" t="n">
         <v>197</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="31" t="n">
         <v>297</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="31" t="n">
         <v>497</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="30" t="n">
+      <c r="B13" s="31" t="n">
         <v>997</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="n">
+      <c r="B14" s="31" t="n">
         <v>1997</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Costo por entrada × % de asistentes en vivo que solicitan → ganancia del lanzamiento</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Hasta cuánto pagar por cada entrada según lo que mueve el evento.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Costo por entrada ↓  /  % en vivo que solicita →</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.08</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.12</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.16</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.2</v>
       </c>
-      <c r="G19" s="29" t="n">
+      <c r="G19" s="30" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*C$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*C$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*D$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*D$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*E$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*E$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*F$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*F$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="26">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*G$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*G$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*C$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*C$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="26">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*D$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*D$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="26">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*E$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*E$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="26">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*F$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*F$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="26">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*G$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*G$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="26">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*C$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*C$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="26">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*D$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*D$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="26">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*E$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*E$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="26">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*F$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*F$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="26">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*G$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*G$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="26">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*C$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*C$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="26">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*D$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*D$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="26">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*E$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*E$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="26">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*F$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*F$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="26">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*G$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*G$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*C$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*C$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="26">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*D$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*D$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="26">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*E$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*E$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="26">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*F$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*F$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="26">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*G$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*G$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="26">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*C$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*C$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="26">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*D$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*D$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="26">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*E$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*E$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="26">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*F$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*F$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="26">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*G$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*G$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Cuánto invertir para una facturación objetivo por lanzamiento, según el ROAS que querés</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Inversión = facturación ÷ ROAS. Debajo: cuántas entradas hacen falta y cuánto podés pagar por cada una.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Facturación objetivo ↓ / ROAS objetivo →</t>
         </is>
       </c>
-      <c r="C30" s="32" t="n">
+      <c r="C30" s="33" t="n">
         <v>1.5</v>
       </c>
-      <c r="D30" s="32" t="n">
+      <c r="D30" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="32" t="n">
+      <c r="E30" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="F30" s="32" t="n">
+      <c r="F30" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="32" t="n">
+      <c r="G30" s="33" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="31" t="n">
         <v>5000</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="26">
         <f>$B31/C$30</f>
         <v/>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="26">
         <f>$B31/D$30</f>
         <v/>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="26">
         <f>$B31/E$30</f>
         <v/>
       </c>
-      <c r="F31" s="25">
+      <c r="F31" s="26">
         <f>$B31/F$30</f>
         <v/>
       </c>
-      <c r="G31" s="25">
+      <c r="G31" s="26">
         <f>$B31/G$30</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <f>$B32/C$30</f>
         <v/>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="26">
         <f>$B32/D$30</f>
         <v/>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="26">
         <f>$B32/E$30</f>
         <v/>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="26">
         <f>$B32/F$30</f>
         <v/>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="26">
         <f>$B32/G$30</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="31" t="n">
         <v>20000</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="26">
         <f>$B33/C$30</f>
         <v/>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="26">
         <f>$B33/D$30</f>
         <v/>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="26">
         <f>$B33/E$30</f>
         <v/>
       </c>
-      <c r="F33" s="25">
+      <c r="F33" s="26">
         <f>$B33/F$30</f>
         <v/>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="26">
         <f>$B33/G$30</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="31" t="n">
         <v>30000</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="26">
         <f>$B34/C$30</f>
         <v/>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="26">
         <f>$B34/D$30</f>
         <v/>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="26">
         <f>$B34/E$30</f>
         <v/>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="26">
         <f>$B34/F$30</f>
         <v/>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="26">
         <f>$B34/G$30</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="31" t="n">
         <v>50000</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <f>$B35/C$30</f>
         <v/>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="26">
         <f>$B35/D$30</f>
         <v/>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="26">
         <f>$B35/E$30</f>
         <v/>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="26">
         <f>$B35/F$30</f>
         <v/>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="26">
         <f>$B35/G$30</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Cantidad de entradas necesaria para esa facturación</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="33">
+      <c r="B37" s="34">
         <f>$B31</f>
         <v/>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="17">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B31/'Modelo'!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="33">
+      <c r="B38" s="34">
         <f>$B32</f>
         <v/>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="17">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B32/'Modelo'!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="33">
+      <c r="B39" s="34">
         <f>$B33</f>
         <v/>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="17">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B33/'Modelo'!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="33">
+      <c r="B40" s="34">
         <f>$B34</f>
         <v/>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="17">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B34/'Modelo'!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="33">
+      <c r="B41" s="34">
         <f>$B35</f>
         <v/>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="17">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B35/'Modelo'!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Costo máximo por entrada para cumplir cada ROAS (sobre facturado)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="34" t="n">
+      <c r="C44" s="35" t="n">
         <v>1.5</v>
       </c>
-      <c r="D44" s="34" t="n">
+      <c r="D44" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E44" s="34" t="n">
+      <c r="E44" s="35" t="n">
         <v>2.5</v>
       </c>
-      <c r="F44" s="34" t="n">
+      <c r="F44" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="34" t="n">
+      <c r="G44" s="35" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6041,65 +6187,65 @@
           <t>Costo máximo (facturado por unidad ÷ ROAS)</t>
         </is>
       </c>
-      <c r="C45" s="19">
+      <c r="C45" s="20">
         <f>IF(C44=0,0,'Modelo'!$C$36/C44)</f>
         <v/>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="20">
         <f>IF(D44=0,0,'Modelo'!$C$36/D44)</f>
         <v/>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="20">
         <f>IF(E44=0,0,'Modelo'!$C$36/E44)</f>
         <v/>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="20">
         <f>IF(F44=0,0,'Modelo'!$C$36/F44)</f>
         <v/>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="20">
         <f>IF(G44=0,0,'Modelo'!$C$36/G44)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Sobre cash neto, el techo real está en Modelo (ya descuenta comisiones y reembolsos).</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Guardarraíl: el ROAS mínimo que tiene que dar cada nivel de inversión para que subir valga la pena</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Parte de tu inversión y tu ROAS actuales. Cada dólar extra tiene que devolver al menos 1,3 neto. Si al subir un escalón el ROAS real queda por debajo del mínimo de esa fila, volvé al escalón anterior.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Nivel de inversión</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>Inversión del período</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>ROAS mínimo (cash neto)</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>Ganancia mínima</t>
         </is>
@@ -6111,15 +6257,15 @@
           <t>actual</t>
         </is>
       </c>
-      <c r="C52" s="25">
+      <c r="C52" s="26">
         <f>'Supuestos'!$C$8*1.0</f>
         <v/>
       </c>
-      <c r="D52" s="27">
+      <c r="D52" s="28">
         <f>IF(C52=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C52-'Supuestos'!$C$8))/C52)</f>
         <v/>
       </c>
-      <c r="E52" s="25">
+      <c r="E52" s="26">
         <f>C52*(D52-1)</f>
         <v/>
       </c>
@@ -6130,15 +6276,15 @@
           <t>× 1.25</t>
         </is>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="26">
         <f>'Supuestos'!$C$8*1.25</f>
         <v/>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="28">
         <f>IF(C53=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C53-'Supuestos'!$C$8))/C53)</f>
         <v/>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="26">
         <f>C53*(D53-1)</f>
         <v/>
       </c>
@@ -6149,15 +6295,15 @@
           <t>× 1.5</t>
         </is>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="26">
         <f>'Supuestos'!$C$8*1.5</f>
         <v/>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="28">
         <f>IF(C54=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C54-'Supuestos'!$C$8))/C54)</f>
         <v/>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="26">
         <f>C54*(D54-1)</f>
         <v/>
       </c>
@@ -6168,15 +6314,15 @@
           <t>× 2</t>
         </is>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="26">
         <f>'Supuestos'!$C$8*2.0</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="28">
         <f>IF(C55=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C55-'Supuestos'!$C$8))/C55)</f>
         <v/>
       </c>
-      <c r="E55" s="25">
+      <c r="E55" s="26">
         <f>C55*(D55-1)</f>
         <v/>
       </c>
@@ -6187,15 +6333,15 @@
           <t>× 3</t>
         </is>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="26">
         <f>'Supuestos'!$C$8*3.0</f>
         <v/>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="28">
         <f>IF(C56=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C56-'Supuestos'!$C$8))/C56)</f>
         <v/>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="26">
         <f>C56*(D56-1)</f>
         <v/>
       </c>
@@ -6227,10 +6373,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -6243,7 +6389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6255,59 +6401,66 @@
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Sensibilidad: qué palanca mueve más la ganancia</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cada fila mejora una sola variable un 10 % (o baja un costo un 10 %) y recalcula la ganancia del período. El ranking dice qué conviene trabajar primero.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Palanca</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Ganancia nueva</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Dif. %</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Ganancia del período con los supuestos actuales</t>
         </is>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <f>'Modelo'!$C$44</f>
         <v/>
       </c>
@@ -6323,19 +6476,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="18">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="17">
         <f>RANK(E7,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -6351,19 +6504,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <f>(((((((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$14)+(((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="17">
         <f>RANK(E8,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -6379,19 +6532,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*('Supuestos'!$C$14*1.1))+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="18">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="17">
         <f>RANK(E9,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -6407,19 +6560,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*('Supuestos'!$C$20*1.1))*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*('Supuestos'!$C$20*1.1))*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="18">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="17">
         <f>RANK(E10,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -6435,19 +6588,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*('Supuestos'!$C$25*1.1))+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*('Supuestos'!$C$25*1.1))+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="18">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="17">
         <f>RANK(E11,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -6463,19 +6616,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*('Supuestos'!$C$27*1.1))*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*('Supuestos'!$C$27*1.1))*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="18">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="17">
         <f>RANK(E12,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -6491,19 +6644,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*('Supuestos'!$C$24*1.1))+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="18">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="17">
         <f>RANK(E13,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -6519,19 +6672,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*('Supuestos'!$C$29*1.1))*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="18">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>RANK(E14,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -6547,19 +6700,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*('Supuestos'!$C$16*1.1))*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <f>D15-$D$6</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="18">
         <f>IF($D$6=0,0,E15/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="17">
         <f>RANK(E15,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -6567,10 +6720,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -6583,7 +6736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6603,87 +6756,94 @@
     <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Proyección a 12 meses y caja</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>La inversión crece cada mes según el supuesto de crecimiento. El cash entra según la curva de cobranza (mes 1 / 2 / 3). La ganancia acumulada muestra cuánto dinero hace falta para sostener la pauta. Cada mes multiplica inversión, costos fijos y ventas por los lanzamientos por mes de Supuestos.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Mes 3</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Mes 4</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Mes 5</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Mes 6</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Mes 7</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Mes 8</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Mes 9</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Mes 10</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Mes 11</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>Mes 12</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -6695,55 +6855,55 @@
           <t>Inversión en publicidad del mes</t>
         </is>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <f>C6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <f>D6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <f>E6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="26">
         <f>F6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="26">
         <f>G6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="26">
         <f>H6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="26">
         <f>I6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="26">
         <f>J6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="26">
         <f>K6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="26">
         <f>L6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="26">
         <f>M6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="9">
         <f>SUM(C6:N6)</f>
         <v/>
       </c>
@@ -6754,55 +6914,55 @@
           <t>Entradas compradas</t>
         </is>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>IF('Modelo'!$C$8=0,0,C6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="17">
         <f>IF('Modelo'!$C$8=0,0,D6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="17">
         <f>IF('Modelo'!$C$8=0,0,E6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="17">
         <f>IF('Modelo'!$C$8=0,0,F6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="17">
         <f>IF('Modelo'!$C$8=0,0,G6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="17">
         <f>IF('Modelo'!$C$8=0,0,H6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="17">
         <f>IF('Modelo'!$C$8=0,0,I6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="17">
         <f>IF('Modelo'!$C$8=0,0,J6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="17">
         <f>IF('Modelo'!$C$8=0,0,K6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="17">
         <f>IF('Modelo'!$C$8=0,0,L6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="17">
         <f>IF('Modelo'!$C$8=0,0,M6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="17">
         <f>IF('Modelo'!$C$8=0,0,N6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="11">
         <f>SUM(C7:N7)</f>
         <v/>
       </c>
@@ -6813,55 +6973,55 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>C7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>D7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>E7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>F7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>G7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <f>H7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <f>I7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="27">
         <f>J7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="27">
         <f>K7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="27">
         <f>L7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="27">
         <f>M7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="27">
         <f>N7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="12">
         <f>SUM(C8:N8)</f>
         <v/>
       </c>
@@ -6872,55 +7032,55 @@
           <t>Facturado (todos los productos)</t>
         </is>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <f>C7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <f>D7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>E7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <f>F7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="26">
         <f>G7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="26">
         <f>H7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="26">
         <f>I7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="26">
         <f>J7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="26">
         <f>K7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="L9" s="25">
+      <c r="L9" s="26">
         <f>L7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="26">
         <f>M7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="26">
         <f>N7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="9">
         <f>SUM(C9:N9)</f>
         <v/>
       </c>
@@ -6931,55 +7091,55 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <f>C9*'Supuestos'!$C$39</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <f>D9*'Supuestos'!$C$39+C9*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <f>E9*'Supuestos'!$C$39+D9*'Supuestos'!$C$40+C9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <f>F9*'Supuestos'!$C$39+E9*'Supuestos'!$C$40+D9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="26">
         <f>G9*'Supuestos'!$C$39+F9*'Supuestos'!$C$40+E9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="26">
         <f>H9*'Supuestos'!$C$39+G9*'Supuestos'!$C$40+F9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="26">
         <f>I9*'Supuestos'!$C$39+H9*'Supuestos'!$C$40+G9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="26">
         <f>J9*'Supuestos'!$C$39+I9*'Supuestos'!$C$40+H9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="26">
         <f>K9*'Supuestos'!$C$39+J9*'Supuestos'!$C$40+I9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="L10" s="25">
+      <c r="L10" s="26">
         <f>L9*'Supuestos'!$C$39+K9*'Supuestos'!$C$40+J9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="26">
         <f>M9*'Supuestos'!$C$39+L9*'Supuestos'!$C$40+K9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="N10" s="25">
+      <c r="N10" s="26">
         <f>N9*'Supuestos'!$C$39+M9*'Supuestos'!$C$40+L9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="9">
         <f>SUM(C10:N10)</f>
         <v/>
       </c>
@@ -6990,55 +7150,55 @@
           <t>Comisiones y reembolsos</t>
         </is>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>C10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>D10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>E10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>F10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="26">
         <f>G10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="26">
         <f>H10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="26">
         <f>I10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="26">
         <f>J10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="26">
         <f>K10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="26">
         <f>L10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="26">
         <f>M10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="26">
         <f>N10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="9">
         <f>SUM(C11:N11)</f>
         <v/>
       </c>
@@ -7049,55 +7209,55 @@
           <t>Costos por unidad (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>C7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>D7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>E7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <f>F7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="26">
         <f>G7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="26">
         <f>H7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="26">
         <f>I7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="26">
         <f>J7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="26">
         <f>K7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="26">
         <f>L7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="26">
         <f>M7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="26">
         <f>N7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="9">
         <f>SUM(C12:N12)</f>
         <v/>
       </c>
@@ -7108,169 +7268,169 @@
           <t>Costos fijos del mes</t>
         </is>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="26">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="9">
         <f>SUM(C13:N13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Ganancia de caja del mes</t>
         </is>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <f>C10-C11-C12-C13-C6</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <f>D10-D11-D12-D13-D6</f>
         <v/>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9">
         <f>E10-E11-E12-E13-E6</f>
         <v/>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <f>F10-F11-F12-F13-F6</f>
         <v/>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <f>G10-G11-G12-G13-G6</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <f>H10-H11-H12-H13-H6</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="9">
         <f>I10-I11-I12-I13-I6</f>
         <v/>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="9">
         <f>J10-J11-J12-J13-J6</f>
         <v/>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="9">
         <f>K10-K11-K12-K13-K6</f>
         <v/>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="9">
         <f>L10-L11-L12-L13-L6</f>
         <v/>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="9">
         <f>M10-M11-M12-M13-M6</f>
         <v/>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="9">
         <f>N10-N11-N12-N13-N6</f>
         <v/>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="9">
         <f>SUM(C14:N14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Ganancia de caja acumulada (desde cero)</t>
         </is>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="9">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f>C15+D14</f>
         <v/>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <f>D15+E14</f>
         <v/>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <f>E15+F14</f>
         <v/>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="9">
         <f>F15+G14</f>
         <v/>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <f>G15+H14</f>
         <v/>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="9">
         <f>H15+I14</f>
         <v/>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="9">
         <f>I15+J14</f>
         <v/>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="9">
         <f>J15+K14</f>
         <v/>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="9">
         <f>K15+L14</f>
         <v/>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="9">
         <f>L15+M14</f>
         <v/>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="9">
         <f>M15+N14</f>
         <v/>
       </c>
@@ -7281,84 +7441,84 @@
           <t>Saldo de caja (caja inicial + ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>'Supuestos'!$C$48+C15</f>
         <v/>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>'Supuestos'!$C$48+D15</f>
         <v/>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>'Supuestos'!$C$48+E15</f>
         <v/>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>'Supuestos'!$C$48+F15</f>
         <v/>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="26">
         <f>'Supuestos'!$C$48+G15</f>
         <v/>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="26">
         <f>'Supuestos'!$C$48+H15</f>
         <v/>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="26">
         <f>'Supuestos'!$C$48+I15</f>
         <v/>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="26">
         <f>'Supuestos'!$C$48+J15</f>
         <v/>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="26">
         <f>'Supuestos'!$C$48+K15</f>
         <v/>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="26">
         <f>'Supuestos'!$C$48+L15</f>
         <v/>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="26">
         <f>'Supuestos'!$C$48+M15</f>
         <v/>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="26">
         <f>'Supuestos'!$C$48+N15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Caja necesaria para no frenar la pauta (el peor momento de la ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <f>MAX(0,-MIN(C15:N15))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Saldo mínimo de caja con tu caja inicial</t>
         </is>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <f>MIN(C16:N16)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Ganancia de caja acumulada en 12 meses</t>
         </is>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="9">
         <f>O14</f>
         <v/>
       </c>
@@ -7378,10 +7538,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -7394,7 +7554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q37"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7416,120 +7576,127 @@
     <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Seguimiento: una columna por lanzamiento</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cargá los datos reales en las celdas amarillas. El semáforo compara tu costo real por entrada con el techo móvil (lo que rindieron tus últimas 4 columnas) y con el techo del modelo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Dato</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 1</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 2</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 3</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 4</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 5</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 6</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 7</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 8</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 9</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 10</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 11</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>Lanzamiento 12</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>Promedio</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>Máximo</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>Mínimo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Datos que cargás</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -7537,33 +7704,33 @@
           <t>Inversión en publicidad</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="22" t="n">
         <v>3200</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="22" t="n">
         <v>3600</v>
       </c>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="25">
+      <c r="F7" s="22" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="22" t="n"/>
+      <c r="L7" s="22" t="n"/>
+      <c r="M7" s="22" t="n"/>
+      <c r="N7" s="22" t="n"/>
+      <c r="O7" s="26">
         <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
         <v/>
       </c>
-      <c r="P7" s="25">
+      <c r="P7" s="26">
         <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
         <v/>
       </c>
-      <c r="Q7" s="25">
+      <c r="Q7" s="26">
         <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
         <v/>
       </c>
@@ -7574,33 +7741,33 @@
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="21" t="n">
         <v>8600</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="21" t="n">
         <v>8900</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="21" t="n">
         <v>9700</v>
       </c>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="16">
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="21" t="n"/>
+      <c r="O8" s="17">
         <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
         <v/>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="17">
         <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
         <v/>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="17">
         <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
         <v/>
       </c>
@@ -7611,33 +7778,33 @@
           <t>Entradas vendidas</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="21" t="n">
         <v>214</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="21" t="n">
         <v>220</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <v>235</v>
       </c>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="20" t="n"/>
-      <c r="O9" s="16">
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="21" t="n"/>
+      <c r="M9" s="21" t="n"/>
+      <c r="N9" s="21" t="n"/>
+      <c r="O9" s="17">
         <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
         <v/>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="17">
         <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
         <v/>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="17">
         <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
         <v/>
       </c>
@@ -7648,33 +7815,33 @@
           <t>Bumps de la entrada</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="21" t="n">
         <v>43</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <v>40</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
-      <c r="K10" s="20" t="n"/>
-      <c r="L10" s="20" t="n"/>
-      <c r="M10" s="20" t="n"/>
-      <c r="N10" s="20" t="n"/>
-      <c r="O10" s="16">
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="21" t="n"/>
+      <c r="M10" s="21" t="n"/>
+      <c r="N10" s="21" t="n"/>
+      <c r="O10" s="17">
         <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
         <v/>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="17">
         <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
         <v/>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="17">
         <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
         <v/>
       </c>
@@ -7685,33 +7852,33 @@
           <t>Entraron al grupo</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>182</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>190</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <v>200</v>
       </c>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="n"/>
-      <c r="O11" s="16">
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
+      <c r="J11" s="21" t="n"/>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="21" t="n"/>
+      <c r="M11" s="21" t="n"/>
+      <c r="N11" s="21" t="n"/>
+      <c r="O11" s="17">
         <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
         <v/>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="17">
         <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
         <v/>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="17">
         <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
         <v/>
       </c>
@@ -7722,33 +7889,33 @@
           <t>Asistentes en vivo</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>118</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>115</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <v>135</v>
       </c>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="20" t="n"/>
-      <c r="O12" s="16">
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
+      <c r="J12" s="21" t="n"/>
+      <c r="K12" s="21" t="n"/>
+      <c r="L12" s="21" t="n"/>
+      <c r="M12" s="21" t="n"/>
+      <c r="N12" s="21" t="n"/>
+      <c r="O12" s="17">
         <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
         <v/>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="17">
         <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
         <v/>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="17">
         <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
         <v/>
       </c>
@@ -7759,33 +7926,33 @@
           <t>Vieron el replay</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="21" t="n">
         <v>54</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>60</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="21" t="n">
         <v>58</v>
       </c>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="20" t="n"/>
-      <c r="N13" s="20" t="n"/>
-      <c r="O13" s="16">
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="21" t="n"/>
+      <c r="J13" s="21" t="n"/>
+      <c r="K13" s="21" t="n"/>
+      <c r="L13" s="21" t="n"/>
+      <c r="M13" s="21" t="n"/>
+      <c r="N13" s="21" t="n"/>
+      <c r="O13" s="17">
         <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
         <v/>
       </c>
-      <c r="P13" s="16">
+      <c r="P13" s="17">
         <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
         <v/>
       </c>
-      <c r="Q13" s="16">
+      <c r="Q13" s="17">
         <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
         <v/>
       </c>
@@ -7796,33 +7963,33 @@
           <t>Solicitudes (formulario de compra, aplicación o vendedor)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="21" t="n">
         <v>26</v>
       </c>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-      <c r="L14" s="20" t="n"/>
-      <c r="M14" s="20" t="n"/>
-      <c r="N14" s="20" t="n"/>
-      <c r="O14" s="16">
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="21" t="n"/>
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="21" t="n"/>
+      <c r="L14" s="21" t="n"/>
+      <c r="M14" s="21" t="n"/>
+      <c r="N14" s="21" t="n"/>
+      <c r="O14" s="17">
         <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
         <v/>
       </c>
-      <c r="P14" s="16">
+      <c r="P14" s="17">
         <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
         <v/>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q14" s="17">
         <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
         <v/>
       </c>
@@ -7833,33 +8000,33 @@
           <t>Ventas de la oferta</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="20" t="n"/>
-      <c r="L15" s="20" t="n"/>
-      <c r="M15" s="20" t="n"/>
-      <c r="N15" s="20" t="n"/>
-      <c r="O15" s="16">
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="21" t="n"/>
+      <c r="M15" s="21" t="n"/>
+      <c r="N15" s="21" t="n"/>
+      <c r="O15" s="17">
         <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
         <v/>
       </c>
-      <c r="P15" s="16">
+      <c r="P15" s="17">
         <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
         <v/>
       </c>
-      <c r="Q15" s="16">
+      <c r="Q15" s="17">
         <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
         <v/>
       </c>
@@ -7870,33 +8037,33 @@
           <t>Ventas del programa superior</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="20" t="n"/>
-      <c r="K16" s="20" t="n"/>
-      <c r="L16" s="20" t="n"/>
-      <c r="M16" s="20" t="n"/>
-      <c r="N16" s="20" t="n"/>
-      <c r="O16" s="16">
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="21" t="n"/>
+      <c r="J16" s="21" t="n"/>
+      <c r="K16" s="21" t="n"/>
+      <c r="L16" s="21" t="n"/>
+      <c r="M16" s="21" t="n"/>
+      <c r="N16" s="21" t="n"/>
+      <c r="O16" s="17">
         <f>IF(COUNT(C16:N16)=0,"",AVERAGE(C16:N16))</f>
         <v/>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="17">
         <f>IF(COUNT(C16:N16)=0,"",MAX(C16:N16))</f>
         <v/>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="17">
         <f>IF(COUNT(C16:N16)=0,"",MIN(C16:N16))</f>
         <v/>
       </c>
@@ -7907,33 +8074,33 @@
           <t>Facturado del lanzamiento (a precio de lista, con cuotas por cobrar)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="22" t="n">
         <v>10400</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="22" t="n">
         <v>9000</v>
       </c>
-      <c r="E17" s="21" t="n">
+      <c r="E17" s="22" t="n">
         <v>12300</v>
       </c>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="25">
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="22" t="n"/>
+      <c r="L17" s="22" t="n"/>
+      <c r="M17" s="22" t="n"/>
+      <c r="N17" s="22" t="n"/>
+      <c r="O17" s="26">
         <f>IF(COUNT(C17:N17)=0,"",AVERAGE(C17:N17))</f>
         <v/>
       </c>
-      <c r="P17" s="25">
+      <c r="P17" s="26">
         <f>IF(COUNT(C17:N17)=0,"",MAX(C17:N17))</f>
         <v/>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="26">
         <f>IF(COUNT(C17:N17)=0,"",MIN(C17:N17))</f>
         <v/>
       </c>
@@ -7944,119 +8111,119 @@
           <t>Cash cobrado hasta ahora de ese lanzamiento</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="22" t="n">
         <v>6900</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="22" t="n">
         <v>6300</v>
       </c>
-      <c r="E18" s="21" t="n">
+      <c r="E18" s="22" t="n">
         <v>8200</v>
       </c>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="25">
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n"/>
+      <c r="M18" s="22" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="O18" s="26">
         <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
         <v/>
       </c>
-      <c r="P18" s="25">
+      <c r="P18" s="26">
         <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
         <v/>
       </c>
-      <c r="Q18" s="25">
+      <c r="Q18" s="26">
         <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Lo que calcula el modelo</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Costo por entrada real</t>
         </is>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="13">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C9=0,0,C7/C9))</f>
         <v/>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="13">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D9=0,0,D7/D9))</f>
         <v/>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="13">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E9=0,0,E7/E9))</f>
         <v/>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F9=0,0,F7/F9))</f>
         <v/>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="13">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G9=0,0,G7/G9))</f>
         <v/>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H9=0,0,H7/H9))</f>
         <v/>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I9=0,0,I7/I9))</f>
         <v/>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="13">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J9=0,0,J7/J9))</f>
         <v/>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="13">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K9=0,0,K7/K9))</f>
         <v/>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="13">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L9=0,0,L7/L9))</f>
         <v/>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="13">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M9=0,0,M7/M9))</f>
         <v/>
       </c>
-      <c r="N20" s="12">
+      <c r="N20" s="13">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N9=0,0,N7/N9))</f>
         <v/>
       </c>
-      <c r="O20" s="19">
+      <c r="O20" s="20">
         <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
         <v/>
       </c>
-      <c r="P20" s="19">
+      <c r="P20" s="20">
         <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
         <v/>
       </c>
-      <c r="Q20" s="19">
+      <c r="Q20" s="20">
         <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
         <v/>
       </c>
@@ -8067,130 +8234,130 @@
           <t>% visita → entrada</t>
         </is>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="18">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C8=0,0,C9/C8))</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D8=0,0,D9/D8))</f>
         <v/>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="18">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E8=0,0,E9/E8))</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="18">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F8=0,0,F9/F8))</f>
         <v/>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="18">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G8=0,0,G9/G8))</f>
         <v/>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="18">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H8=0,0,H9/H8))</f>
         <v/>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="18">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I8=0,0,I9/I8))</f>
         <v/>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="18">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J8=0,0,J9/J8))</f>
         <v/>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="18">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K8=0,0,K9/K8))</f>
         <v/>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="18">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L8=0,0,L9/L8))</f>
         <v/>
       </c>
-      <c r="M21" s="17">
+      <c r="M21" s="18">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M8=0,0,M9/M8))</f>
         <v/>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N8=0,0,N9/N8))</f>
         <v/>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="18">
         <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
         <v/>
       </c>
-      <c r="P21" s="17">
+      <c r="P21" s="18">
         <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
         <v/>
       </c>
-      <c r="Q21" s="17">
+      <c r="Q21" s="18">
         <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>ROAS del front (entradas × precio + bumps × precio ÷ inversión)</t>
         </is>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="10">
         <f>IF(COUNT(C7:C18)&lt;12,"",(C9*'Supuestos'!$C$14+C10*'Supuestos'!$C$15)/C7)</f>
         <v/>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="10">
         <f>IF(COUNT(D7:D18)&lt;12,"",(D9*'Supuestos'!$C$14+D10*'Supuestos'!$C$15)/D7)</f>
         <v/>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="10">
         <f>IF(COUNT(E7:E18)&lt;12,"",(E9*'Supuestos'!$C$14+E10*'Supuestos'!$C$15)/E7)</f>
         <v/>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="10">
         <f>IF(COUNT(F7:F18)&lt;12,"",(F9*'Supuestos'!$C$14+F10*'Supuestos'!$C$15)/F7)</f>
         <v/>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="10">
         <f>IF(COUNT(G7:G18)&lt;12,"",(G9*'Supuestos'!$C$14+G10*'Supuestos'!$C$15)/G7)</f>
         <v/>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="10">
         <f>IF(COUNT(H7:H18)&lt;12,"",(H9*'Supuestos'!$C$14+H10*'Supuestos'!$C$15)/H7)</f>
         <v/>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="10">
         <f>IF(COUNT(I7:I18)&lt;12,"",(I9*'Supuestos'!$C$14+I10*'Supuestos'!$C$15)/I7)</f>
         <v/>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="10">
         <f>IF(COUNT(J7:J18)&lt;12,"",(J9*'Supuestos'!$C$14+J10*'Supuestos'!$C$15)/J7)</f>
         <v/>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="10">
         <f>IF(COUNT(K7:K18)&lt;12,"",(K9*'Supuestos'!$C$14+K10*'Supuestos'!$C$15)/K7)</f>
         <v/>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="10">
         <f>IF(COUNT(L7:L18)&lt;12,"",(L9*'Supuestos'!$C$14+L10*'Supuestos'!$C$15)/L7)</f>
         <v/>
       </c>
-      <c r="M22" s="9">
+      <c r="M22" s="10">
         <f>IF(COUNT(M7:M18)&lt;12,"",(M9*'Supuestos'!$C$14+M10*'Supuestos'!$C$15)/M7)</f>
         <v/>
       </c>
-      <c r="N22" s="9">
+      <c r="N22" s="10">
         <f>IF(COUNT(N7:N18)&lt;12,"",(N9*'Supuestos'!$C$14+N10*'Supuestos'!$C$15)/N7)</f>
         <v/>
       </c>
-      <c r="O22" s="27">
+      <c r="O22" s="28">
         <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
         <v/>
       </c>
-      <c r="P22" s="27">
+      <c r="P22" s="28">
         <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
         <v/>
       </c>
-      <c r="Q22" s="27">
+      <c r="Q22" s="28">
         <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
         <v/>
       </c>
@@ -8201,63 +8368,63 @@
           <t>% entrada → en vivo</t>
         </is>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="18">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C9=0,0,C12/C9))</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="18">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D9=0,0,D12/D9))</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="18">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E9=0,0,E12/E9))</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="18">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F9=0,0,F12/F9))</f>
         <v/>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="18">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G9=0,0,G12/G9))</f>
         <v/>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="18">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H9=0,0,H12/H9))</f>
         <v/>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="18">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I9=0,0,I12/I9))</f>
         <v/>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="18">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J9=0,0,J12/J9))</f>
         <v/>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="18">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K9=0,0,K12/K9))</f>
         <v/>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="18">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L9=0,0,L12/L9))</f>
         <v/>
       </c>
-      <c r="M23" s="17">
+      <c r="M23" s="18">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M9=0,0,M12/M9))</f>
         <v/>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="18">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N9=0,0,N12/N9))</f>
         <v/>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="18">
         <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
         <v/>
       </c>
-      <c r="P23" s="17">
+      <c r="P23" s="18">
         <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
         <v/>
       </c>
-      <c r="Q23" s="17">
+      <c r="Q23" s="18">
         <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
         <v/>
       </c>
@@ -8268,63 +8435,63 @@
           <t>Ventas ÷ asistentes en vivo</t>
         </is>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="18">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C12=0,0,C15/C12))</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="18">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D12=0,0,D15/D12))</f>
         <v/>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="18">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E12=0,0,E15/E12))</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="18">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F12=0,0,F15/F12))</f>
         <v/>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="18">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G12=0,0,G15/G12))</f>
         <v/>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="18">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H12=0,0,H15/H12))</f>
         <v/>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="18">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I12=0,0,I15/I12))</f>
         <v/>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="18">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J12=0,0,J15/J12))</f>
         <v/>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="18">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K12=0,0,K15/K12))</f>
         <v/>
       </c>
-      <c r="L24" s="17">
+      <c r="L24" s="18">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L12=0,0,L15/L12))</f>
         <v/>
       </c>
-      <c r="M24" s="17">
+      <c r="M24" s="18">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M12=0,0,M15/M12))</f>
         <v/>
       </c>
-      <c r="N24" s="17">
+      <c r="N24" s="18">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N12=0,0,N15/N12))</f>
         <v/>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="18">
         <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
         <v/>
       </c>
-      <c r="P24" s="17">
+      <c r="P24" s="18">
         <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
         <v/>
       </c>
-      <c r="Q24" s="17">
+      <c r="Q24" s="18">
         <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
         <v/>
       </c>
@@ -8335,63 +8502,63 @@
           <t>Costo por comprador de la oferta</t>
         </is>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="20">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C15=0,0,C7/C15))</f>
         <v/>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D15=0,0,D7/D15))</f>
         <v/>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="20">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E15=0,0,E7/E15))</f>
         <v/>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="20">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F15=0,0,F7/F15))</f>
         <v/>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="20">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G15=0,0,G7/G15))</f>
         <v/>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="20">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H15=0,0,H7/H15))</f>
         <v/>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="20">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I15=0,0,I7/I15))</f>
         <v/>
       </c>
-      <c r="J25" s="19">
+      <c r="J25" s="20">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J15=0,0,J7/J15))</f>
         <v/>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="20">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K15=0,0,K7/K15))</f>
         <v/>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="20">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L15=0,0,L7/L15))</f>
         <v/>
       </c>
-      <c r="M25" s="19">
+      <c r="M25" s="20">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M15=0,0,M7/M15))</f>
         <v/>
       </c>
-      <c r="N25" s="19">
+      <c r="N25" s="20">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N15=0,0,N7/N15))</f>
         <v/>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="20">
         <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
         <v/>
       </c>
-      <c r="P25" s="19">
+      <c r="P25" s="20">
         <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
         <v/>
       </c>
-      <c r="Q25" s="19">
+      <c r="Q25" s="20">
         <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
         <v/>
       </c>
@@ -8402,63 +8569,63 @@
           <t>Costo por persona en el grupo</t>
         </is>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C11=0,0,C7/C11))</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D11=0,0,D7/D11))</f>
         <v/>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E11=0,0,E7/E11))</f>
         <v/>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F11=0,0,F7/F11))</f>
         <v/>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G11=0,0,G7/G11))</f>
         <v/>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="20">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H11=0,0,H7/H11))</f>
         <v/>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="20">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I11=0,0,I7/I11))</f>
         <v/>
       </c>
-      <c r="J26" s="19">
+      <c r="J26" s="20">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J11=0,0,J7/J11))</f>
         <v/>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="20">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K11=0,0,K7/K11))</f>
         <v/>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="20">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L11=0,0,L7/L11))</f>
         <v/>
       </c>
-      <c r="M26" s="19">
+      <c r="M26" s="20">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M11=0,0,M7/M11))</f>
         <v/>
       </c>
-      <c r="N26" s="19">
+      <c r="N26" s="20">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N11=0,0,N7/N11))</f>
         <v/>
       </c>
-      <c r="O26" s="19">
+      <c r="O26" s="20">
         <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
         <v/>
       </c>
-      <c r="P26" s="19">
+      <c r="P26" s="20">
         <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
         <v/>
       </c>
-      <c r="Q26" s="19">
+      <c r="Q26" s="20">
         <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
         <v/>
       </c>
@@ -8469,130 +8636,130 @@
           <t>% en vivo → solicitud</t>
         </is>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="18">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C12=0,0,C14/C12))</f>
         <v/>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="18">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D12=0,0,D14/D12))</f>
         <v/>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="18">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E12=0,0,E14/E12))</f>
         <v/>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="18">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F12=0,0,F14/F12))</f>
         <v/>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="18">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G12=0,0,G14/G12))</f>
         <v/>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="18">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H12=0,0,H14/H12))</f>
         <v/>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="18">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I12=0,0,I14/I12))</f>
         <v/>
       </c>
-      <c r="J27" s="17">
+      <c r="J27" s="18">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J12=0,0,J14/J12))</f>
         <v/>
       </c>
-      <c r="K27" s="17">
+      <c r="K27" s="18">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K12=0,0,K14/K12))</f>
         <v/>
       </c>
-      <c r="L27" s="17">
+      <c r="L27" s="18">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L12=0,0,L14/L12))</f>
         <v/>
       </c>
-      <c r="M27" s="17">
+      <c r="M27" s="18">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M12=0,0,M14/M12))</f>
         <v/>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="18">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N12=0,0,N14/N12))</f>
         <v/>
       </c>
-      <c r="O27" s="17">
+      <c r="O27" s="18">
         <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
         <v/>
       </c>
-      <c r="P27" s="17">
+      <c r="P27" s="18">
         <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
         <v/>
       </c>
-      <c r="Q27" s="17">
+      <c r="Q27" s="18">
         <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Costo por solicitud</t>
         </is>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="13">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C14=0,0,C7/C14))</f>
         <v/>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="13">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D14=0,0,D7/D14))</f>
         <v/>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="13">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E14=0,0,E7/E14))</f>
         <v/>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="13">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F14=0,0,F7/F14))</f>
         <v/>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="13">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G14=0,0,G7/G14))</f>
         <v/>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="13">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H14=0,0,H7/H14))</f>
         <v/>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="13">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I14=0,0,I7/I14))</f>
         <v/>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="13">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J14=0,0,J7/J14))</f>
         <v/>
       </c>
-      <c r="K28" s="12">
+      <c r="K28" s="13">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K14=0,0,K7/K14))</f>
         <v/>
       </c>
-      <c r="L28" s="12">
+      <c r="L28" s="13">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L14=0,0,L7/L14))</f>
         <v/>
       </c>
-      <c r="M28" s="12">
+      <c r="M28" s="13">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M14=0,0,M7/M14))</f>
         <v/>
       </c>
-      <c r="N28" s="12">
+      <c r="N28" s="13">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N14=0,0,N7/N14))</f>
         <v/>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="20">
         <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
         <v/>
       </c>
-      <c r="P28" s="19">
+      <c r="P28" s="20">
         <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
         <v/>
       </c>
-      <c r="Q28" s="19">
+      <c r="Q28" s="20">
         <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
         <v/>
       </c>
@@ -8603,197 +8770,197 @@
           <t>% solicitud → compra</t>
         </is>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="18">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C14=0,0,C15/C14))</f>
         <v/>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="18">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D14=0,0,D15/D14))</f>
         <v/>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="18">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E14=0,0,E15/E14))</f>
         <v/>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="18">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F14=0,0,F15/F14))</f>
         <v/>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="18">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G14=0,0,G15/G14))</f>
         <v/>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="18">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H14=0,0,H15/H14))</f>
         <v/>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="18">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I14=0,0,I15/I14))</f>
         <v/>
       </c>
-      <c r="J29" s="17">
+      <c r="J29" s="18">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J14=0,0,J15/J14))</f>
         <v/>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="18">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K14=0,0,K15/K14))</f>
         <v/>
       </c>
-      <c r="L29" s="17">
+      <c r="L29" s="18">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L14=0,0,L15/L14))</f>
         <v/>
       </c>
-      <c r="M29" s="17">
+      <c r="M29" s="18">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M14=0,0,M15/M14))</f>
         <v/>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="18">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N14=0,0,N15/N14))</f>
         <v/>
       </c>
-      <c r="O29" s="17">
+      <c r="O29" s="18">
         <f>IF(COUNT(C29:N29)=0,"",AVERAGE(C29:N29))</f>
         <v/>
       </c>
-      <c r="P29" s="17">
+      <c r="P29" s="18">
         <f>IF(COUNT(C29:N29)=0,"",MAX(C29:N29))</f>
         <v/>
       </c>
-      <c r="Q29" s="17">
+      <c r="Q29" s="18">
         <f>IF(COUNT(C29:N29)=0,"",MIN(C29:N29))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Valor neto por unidad real (sobre facturado, cobranza completa)</t>
         </is>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="13">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C9=0,0,(C17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-C9*'Supuestos'!$C$35)/C9))</f>
         <v/>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="13">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D9=0,0,(D17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-D9*'Supuestos'!$C$35)/D9))</f>
         <v/>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="13">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E9=0,0,(E17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-E9*'Supuestos'!$C$35)/E9))</f>
         <v/>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="13">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F9=0,0,(F17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-F9*'Supuestos'!$C$35)/F9))</f>
         <v/>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="13">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G9=0,0,(G17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-G9*'Supuestos'!$C$35)/G9))</f>
         <v/>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="13">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H9=0,0,(H17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-H9*'Supuestos'!$C$35)/H9))</f>
         <v/>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="13">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I9=0,0,(I17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-I9*'Supuestos'!$C$35)/I9))</f>
         <v/>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="13">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J9=0,0,(J17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-J9*'Supuestos'!$C$35)/J9))</f>
         <v/>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="13">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K9=0,0,(K17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-K9*'Supuestos'!$C$35)/K9))</f>
         <v/>
       </c>
-      <c r="L30" s="12">
+      <c r="L30" s="13">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L9=0,0,(L17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-L9*'Supuestos'!$C$35)/L9))</f>
         <v/>
       </c>
-      <c r="M30" s="12">
+      <c r="M30" s="13">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M9=0,0,(M17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-M9*'Supuestos'!$C$35)/M9))</f>
         <v/>
       </c>
-      <c r="N30" s="12">
+      <c r="N30" s="13">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N9=0,0,(N17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-N9*'Supuestos'!$C$35)/N9))</f>
         <v/>
       </c>
-      <c r="O30" s="19">
+      <c r="O30" s="20">
         <f>IF(COUNT(C30:N30)=0,"",AVERAGE(C30:N30))</f>
         <v/>
       </c>
-      <c r="P30" s="19">
+      <c r="P30" s="20">
         <f>IF(COUNT(C30:N30)=0,"",MAX(C30:N30))</f>
         <v/>
       </c>
-      <c r="Q30" s="19">
+      <c r="Q30" s="20">
         <f>IF(COUNT(C30:N30)=0,"",MIN(C30:N30))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Ganancia del período al completar la cobranza</t>
         </is>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="9">
         <f>IF(COUNT(C7:C18)&lt;12,"",C17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-C9*'Supuestos'!$C$35-'Supuestos'!$C$36-C7)</f>
         <v/>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="9">
         <f>IF(COUNT(D7:D18)&lt;12,"",D17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-D9*'Supuestos'!$C$35-'Supuestos'!$C$36-D7)</f>
         <v/>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="9">
         <f>IF(COUNT(E7:E18)&lt;12,"",E17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-E9*'Supuestos'!$C$35-'Supuestos'!$C$36-E7)</f>
         <v/>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="9">
         <f>IF(COUNT(F7:F18)&lt;12,"",F17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-F9*'Supuestos'!$C$35-'Supuestos'!$C$36-F7)</f>
         <v/>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="9">
         <f>IF(COUNT(G7:G18)&lt;12,"",G17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-G9*'Supuestos'!$C$35-'Supuestos'!$C$36-G7)</f>
         <v/>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="9">
         <f>IF(COUNT(H7:H18)&lt;12,"",H17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-H9*'Supuestos'!$C$35-'Supuestos'!$C$36-H7)</f>
         <v/>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="9">
         <f>IF(COUNT(I7:I18)&lt;12,"",I17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-I9*'Supuestos'!$C$35-'Supuestos'!$C$36-I7)</f>
         <v/>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="9">
         <f>IF(COUNT(J7:J18)&lt;12,"",J17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-J9*'Supuestos'!$C$35-'Supuestos'!$C$36-J7)</f>
         <v/>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="9">
         <f>IF(COUNT(K7:K18)&lt;12,"",K17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-K9*'Supuestos'!$C$35-'Supuestos'!$C$36-K7)</f>
         <v/>
       </c>
-      <c r="L31" s="8">
+      <c r="L31" s="9">
         <f>IF(COUNT(L7:L18)&lt;12,"",L17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-L9*'Supuestos'!$C$35-'Supuestos'!$C$36-L7)</f>
         <v/>
       </c>
-      <c r="M31" s="8">
+      <c r="M31" s="9">
         <f>IF(COUNT(M7:M18)&lt;12,"",M17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-M9*'Supuestos'!$C$35-'Supuestos'!$C$36-M7)</f>
         <v/>
       </c>
-      <c r="N31" s="8">
+      <c r="N31" s="9">
         <f>IF(COUNT(N7:N18)&lt;12,"",N17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-N9*'Supuestos'!$C$35-'Supuestos'!$C$36-N7)</f>
         <v/>
       </c>
-      <c r="O31" s="25">
+      <c r="O31" s="26">
         <f>IF(COUNT(C31:N31)=0,"",AVERAGE(C31:N31))</f>
         <v/>
       </c>
-      <c r="P31" s="25">
+      <c r="P31" s="26">
         <f>IF(COUNT(C31:N31)=0,"",MAX(C31:N31))</f>
         <v/>
       </c>
-      <c r="Q31" s="25">
+      <c r="Q31" s="26">
         <f>IF(COUNT(C31:N31)=0,"",MIN(C31:N31))</f>
         <v/>
       </c>
@@ -8804,197 +8971,197 @@
           <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <f>IF(COUNT(C7:C18)&lt;12,"",C18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-C9*'Supuestos'!$C$35-'Supuestos'!$C$36-C7)</f>
         <v/>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="26">
         <f>IF(COUNT(D7:D18)&lt;12,"",D18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-D9*'Supuestos'!$C$35-'Supuestos'!$C$36-D7)</f>
         <v/>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="26">
         <f>IF(COUNT(E7:E18)&lt;12,"",E18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-E9*'Supuestos'!$C$35-'Supuestos'!$C$36-E7)</f>
         <v/>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="26">
         <f>IF(COUNT(F7:F18)&lt;12,"",F18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-F9*'Supuestos'!$C$35-'Supuestos'!$C$36-F7)</f>
         <v/>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="26">
         <f>IF(COUNT(G7:G18)&lt;12,"",G18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-G9*'Supuestos'!$C$35-'Supuestos'!$C$36-G7)</f>
         <v/>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="26">
         <f>IF(COUNT(H7:H18)&lt;12,"",H18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-H9*'Supuestos'!$C$35-'Supuestos'!$C$36-H7)</f>
         <v/>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="26">
         <f>IF(COUNT(I7:I18)&lt;12,"",I18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-I9*'Supuestos'!$C$35-'Supuestos'!$C$36-I7)</f>
         <v/>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="26">
         <f>IF(COUNT(J7:J18)&lt;12,"",J18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-J9*'Supuestos'!$C$35-'Supuestos'!$C$36-J7)</f>
         <v/>
       </c>
-      <c r="K32" s="25">
+      <c r="K32" s="26">
         <f>IF(COUNT(K7:K18)&lt;12,"",K18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-K9*'Supuestos'!$C$35-'Supuestos'!$C$36-K7)</f>
         <v/>
       </c>
-      <c r="L32" s="25">
+      <c r="L32" s="26">
         <f>IF(COUNT(L7:L18)&lt;12,"",L18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-L9*'Supuestos'!$C$35-'Supuestos'!$C$36-L7)</f>
         <v/>
       </c>
-      <c r="M32" s="25">
+      <c r="M32" s="26">
         <f>IF(COUNT(M7:M18)&lt;12,"",M18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-M9*'Supuestos'!$C$35-'Supuestos'!$C$36-M7)</f>
         <v/>
       </c>
-      <c r="N32" s="25">
+      <c r="N32" s="26">
         <f>IF(COUNT(N7:N18)&lt;12,"",N18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-N9*'Supuestos'!$C$35-'Supuestos'!$C$36-N7)</f>
         <v/>
       </c>
-      <c r="O32" s="25">
+      <c r="O32" s="26">
         <f>IF(COUNT(C32:N32)=0,"",AVERAGE(C32:N32))</f>
         <v/>
       </c>
-      <c r="P32" s="25">
+      <c r="P32" s="26">
         <f>IF(COUNT(C32:N32)=0,"",MAX(C32:N32))</f>
         <v/>
       </c>
-      <c r="Q32" s="25">
+      <c r="Q32" s="26">
         <f>IF(COUNT(C32:N32)=0,"",MIN(C32:N32))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Ganancia por unidad real (ganancia ÷ unidades)</t>
         </is>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="13">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C9=0,0,(C17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-C9*'Supuestos'!$C$35-'Supuestos'!$C$36-C7)/C9))</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="13">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D9=0,0,(D17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-D9*'Supuestos'!$C$35-'Supuestos'!$C$36-D7)/D9))</f>
         <v/>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="13">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E9=0,0,(E17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-E9*'Supuestos'!$C$35-'Supuestos'!$C$36-E7)/E9))</f>
         <v/>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="13">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F9=0,0,(F17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-F9*'Supuestos'!$C$35-'Supuestos'!$C$36-F7)/F9))</f>
         <v/>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="13">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G9=0,0,(G17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-G9*'Supuestos'!$C$35-'Supuestos'!$C$36-G7)/G9))</f>
         <v/>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="13">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H9=0,0,(H17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-H9*'Supuestos'!$C$35-'Supuestos'!$C$36-H7)/H9))</f>
         <v/>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="13">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I9=0,0,(I17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-I9*'Supuestos'!$C$35-'Supuestos'!$C$36-I7)/I9))</f>
         <v/>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="13">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J9=0,0,(J17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-J9*'Supuestos'!$C$35-'Supuestos'!$C$36-J7)/J9))</f>
         <v/>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="13">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K9=0,0,(K17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-K9*'Supuestos'!$C$35-'Supuestos'!$C$36-K7)/K9))</f>
         <v/>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="13">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L9=0,0,(L17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-L9*'Supuestos'!$C$35-'Supuestos'!$C$36-L7)/L9))</f>
         <v/>
       </c>
-      <c r="M33" s="12">
+      <c r="M33" s="13">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M9=0,0,(M17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-M9*'Supuestos'!$C$35-'Supuestos'!$C$36-M7)/M9))</f>
         <v/>
       </c>
-      <c r="N33" s="12">
+      <c r="N33" s="13">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N9=0,0,(N17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-N9*'Supuestos'!$C$35-'Supuestos'!$C$36-N7)/N9))</f>
         <v/>
       </c>
-      <c r="O33" s="19">
+      <c r="O33" s="20">
         <f>IF(COUNT(C33:N33)=0,"",AVERAGE(C33:N33))</f>
         <v/>
       </c>
-      <c r="P33" s="19">
+      <c r="P33" s="20">
         <f>IF(COUNT(C33:N33)=0,"",MAX(C33:N33))</f>
         <v/>
       </c>
-      <c r="Q33" s="19">
+      <c r="Q33" s="20">
         <f>IF(COUNT(C33:N33)=0,"",MIN(C33:N33))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>ROAS sobre cash neto (cobranza completa)</t>
         </is>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="10">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C7=0,0,C17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/C7))</f>
         <v/>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="10">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D7=0,0,D17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/D7))</f>
         <v/>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="10">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E7=0,0,E17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/E7))</f>
         <v/>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="10">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F7=0,0,F17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/F7))</f>
         <v/>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="10">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G7=0,0,G17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/G7))</f>
         <v/>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="10">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H7=0,0,H17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/H7))</f>
         <v/>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="10">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I7=0,0,I17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/I7))</f>
         <v/>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="10">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J7=0,0,J17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/J7))</f>
         <v/>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="10">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K7=0,0,K17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/K7))</f>
         <v/>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="10">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L7=0,0,L17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/L7))</f>
         <v/>
       </c>
-      <c r="M34" s="9">
+      <c r="M34" s="10">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M7=0,0,M17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/M7))</f>
         <v/>
       </c>
-      <c r="N34" s="9">
+      <c r="N34" s="10">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N7=0,0,N17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/N7))</f>
         <v/>
       </c>
-      <c r="O34" s="27">
+      <c r="O34" s="28">
         <f>IF(COUNT(C34:N34)=0,"",AVERAGE(C34:N34))</f>
         <v/>
       </c>
-      <c r="P34" s="27">
+      <c r="P34" s="28">
         <f>IF(COUNT(C34:N34)=0,"",MAX(C34:N34))</f>
         <v/>
       </c>
-      <c r="Q34" s="27">
+      <c r="Q34" s="28">
         <f>IF(COUNT(C34:N34)=0,"",MIN(C34:N34))</f>
         <v/>
       </c>
@@ -9005,63 +9172,63 @@
           <t>ROAS de caja (cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="28">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C7=0,0,C18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/C7))</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D7=0,0,D18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/D7))</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E7=0,0,E18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/E7))</f>
         <v/>
       </c>
-      <c r="F35" s="27">
+      <c r="F35" s="28">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F7=0,0,F18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/F7))</f>
         <v/>
       </c>
-      <c r="G35" s="27">
+      <c r="G35" s="28">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G7=0,0,G18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/G7))</f>
         <v/>
       </c>
-      <c r="H35" s="27">
+      <c r="H35" s="28">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H7=0,0,H18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/H7))</f>
         <v/>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="28">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I7=0,0,I18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/I7))</f>
         <v/>
       </c>
-      <c r="J35" s="27">
+      <c r="J35" s="28">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J7=0,0,J18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/J7))</f>
         <v/>
       </c>
-      <c r="K35" s="27">
+      <c r="K35" s="28">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K7=0,0,K18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/K7))</f>
         <v/>
       </c>
-      <c r="L35" s="27">
+      <c r="L35" s="28">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L7=0,0,L18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/L7))</f>
         <v/>
       </c>
-      <c r="M35" s="27">
+      <c r="M35" s="28">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M7=0,0,M18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/M7))</f>
         <v/>
       </c>
-      <c r="N35" s="27">
+      <c r="N35" s="28">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N7=0,0,N18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/N7))</f>
         <v/>
       </c>
-      <c r="O35" s="27">
+      <c r="O35" s="28">
         <f>IF(COUNT(C35:N35)=0,"",AVERAGE(C35:N35))</f>
         <v/>
       </c>
-      <c r="P35" s="27">
+      <c r="P35" s="28">
         <f>IF(COUNT(C35:N35)=0,"",MAX(C35:N35))</f>
         <v/>
       </c>
-      <c r="Q35" s="27">
+      <c r="Q35" s="28">
         <f>IF(COUNT(C35:N35)=0,"",MIN(C35:N35))</f>
         <v/>
       </c>
@@ -9072,118 +9239,118 @@
           <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
         </is>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="20">
         <f>IF(COUNT(C7:C18)&lt;12,"",'Modelo'!$C$51)</f>
         <v/>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="20">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(COUNT(C30:C30)&gt;0,MEDIAN(C30:C30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="20">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(COUNT(C30:D30)&gt;0,MEDIAN(C30:D30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="20">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(COUNT(C30:E30)&gt;0,MEDIAN(C30:E30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="20">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(COUNT(C30:F30)&gt;0,MEDIAN(C30:F30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="20">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(COUNT(D30:G30)&gt;0,MEDIAN(D30:G30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="20">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(COUNT(E30:H30)&gt;0,MEDIAN(E30:H30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="J36" s="19">
+      <c r="J36" s="20">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(COUNT(F30:I30)&gt;0,MEDIAN(F30:I30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="K36" s="19">
+      <c r="K36" s="20">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(COUNT(G30:J30)&gt;0,MEDIAN(G30:J30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="20">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(COUNT(H30:K30)&gt;0,MEDIAN(H30:K30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="M36" s="19">
+      <c r="M36" s="20">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(COUNT(I30:L30)&gt;0,MEDIAN(I30:L30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="N36" s="19">
+      <c r="N36" s="20">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(COUNT(J30:M30)&gt;0,MEDIAN(J30:M30),'Modelo'!$C$51))</f>
         <v/>
       </c>
-      <c r="O36" s="19">
+      <c r="O36" s="20">
         <f>IF(COUNT(C36:N36)=0,"",AVERAGE(C36:N36))</f>
         <v/>
       </c>
-      <c r="P36" s="19">
+      <c r="P36" s="20">
         <f>IF(COUNT(C36:N36)=0,"",MAX(C36:N36))</f>
         <v/>
       </c>
-      <c r="Q36" s="19">
+      <c r="Q36" s="20">
         <f>IF(COUNT(C36:N36)=0,"",MIN(C36:N36))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Semáforo (costo por unidad contra el techo móvil, y ROAS contra el objetivo)</t>
         </is>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="14">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C20&gt;C36,"ROJO",IF(AND(C20&lt;=C36/(1+'Supuestos'!$C$45),C34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="14">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D20&gt;D36,"ROJO",IF(AND(D20&lt;=D36/(1+'Supuestos'!$C$45),D34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="14">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E20&gt;E36,"ROJO",IF(AND(E20&lt;=E36/(1+'Supuestos'!$C$45),E34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="14">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F20&gt;F36,"ROJO",IF(AND(F20&lt;=F36/(1+'Supuestos'!$C$45),F34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="14">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G20&gt;G36,"ROJO",IF(AND(G20&lt;=G36/(1+'Supuestos'!$C$45),G34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="H37" s="13">
+      <c r="H37" s="14">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H20&gt;H36,"ROJO",IF(AND(H20&lt;=H36/(1+'Supuestos'!$C$45),H34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="I37" s="13">
+      <c r="I37" s="14">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I20&gt;I36,"ROJO",IF(AND(I20&lt;=I36/(1+'Supuestos'!$C$45),I34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="J37" s="13">
+      <c r="J37" s="14">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J20&gt;J36,"ROJO",IF(AND(J20&lt;=J36/(1+'Supuestos'!$C$45),J34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="K37" s="13">
+      <c r="K37" s="14">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K20&gt;K36,"ROJO",IF(AND(K20&lt;=K36/(1+'Supuestos'!$C$45),K34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="L37" s="13">
+      <c r="L37" s="14">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L20&gt;L36,"ROJO",IF(AND(L20&lt;=L36/(1+'Supuestos'!$C$45),L34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="M37" s="13">
+      <c r="M37" s="14">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M20&gt;M36,"ROJO",IF(AND(M20&lt;=M36/(1+'Supuestos'!$C$45),M34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="N37" s="13">
+      <c r="N37" s="14">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N20&gt;N36,"ROJO",IF(AND(N20&lt;=N36/(1+'Supuestos'!$C$45),N34&gt;='Supuestos'!$C$44),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
@@ -9202,10 +9369,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>

--- a/excel/04_Modelo_Financiero_Embudo_Webinar_Pago.xlsx
+++ b/excel/04_Modelo_Financiero_Embudo_Webinar_Pago.xlsx
@@ -180,6 +180,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -197,7 +198,6 @@
     <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1050,33 +1050,33 @@
           <t>Inversión en publicidad</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="20" t="n">
         <v>3200</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="20" t="n">
         <v>3600</v>
       </c>
-      <c r="F7" s="19" t="n"/>
-      <c r="G7" s="19" t="n"/>
-      <c r="H7" s="19" t="n"/>
-      <c r="I7" s="19" t="n"/>
-      <c r="J7" s="19" t="n"/>
-      <c r="K7" s="19" t="n"/>
-      <c r="L7" s="19" t="n"/>
-      <c r="M7" s="19" t="n"/>
-      <c r="N7" s="19" t="n"/>
-      <c r="O7" s="20">
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="20" t="n"/>
+      <c r="H7" s="20" t="n"/>
+      <c r="I7" s="20" t="n"/>
+      <c r="J7" s="20" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="L7" s="20" t="n"/>
+      <c r="M7" s="20" t="n"/>
+      <c r="N7" s="20" t="n"/>
+      <c r="O7" s="21">
         <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
         <v/>
       </c>
-      <c r="P7" s="20">
+      <c r="P7" s="21">
         <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
         <v/>
       </c>
-      <c r="Q7" s="20">
+      <c r="Q7" s="21">
         <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
         <v/>
       </c>
@@ -1087,33 +1087,33 @@
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>8600</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>8900</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="30" t="n">
         <v>9700</v>
       </c>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="29" t="n"/>
-      <c r="K8" s="29" t="n"/>
-      <c r="L8" s="29" t="n"/>
-      <c r="M8" s="29" t="n"/>
-      <c r="N8" s="29" t="n"/>
-      <c r="O8" s="21">
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
+      <c r="H8" s="30" t="n"/>
+      <c r="I8" s="30" t="n"/>
+      <c r="J8" s="30" t="n"/>
+      <c r="K8" s="30" t="n"/>
+      <c r="L8" s="30" t="n"/>
+      <c r="M8" s="30" t="n"/>
+      <c r="N8" s="30" t="n"/>
+      <c r="O8" s="22">
         <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
         <v/>
       </c>
-      <c r="P8" s="21">
+      <c r="P8" s="22">
         <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
         <v/>
       </c>
-      <c r="Q8" s="21">
+      <c r="Q8" s="22">
         <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
         <v/>
       </c>
@@ -1124,33 +1124,33 @@
           <t>Entradas vendidas</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>214</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>220</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="30" t="n">
         <v>235</v>
       </c>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="29" t="n"/>
-      <c r="I9" s="29" t="n"/>
-      <c r="J9" s="29" t="n"/>
-      <c r="K9" s="29" t="n"/>
-      <c r="L9" s="29" t="n"/>
-      <c r="M9" s="29" t="n"/>
-      <c r="N9" s="29" t="n"/>
-      <c r="O9" s="21">
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+      <c r="H9" s="30" t="n"/>
+      <c r="I9" s="30" t="n"/>
+      <c r="J9" s="30" t="n"/>
+      <c r="K9" s="30" t="n"/>
+      <c r="L9" s="30" t="n"/>
+      <c r="M9" s="30" t="n"/>
+      <c r="N9" s="30" t="n"/>
+      <c r="O9" s="22">
         <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
         <v/>
       </c>
-      <c r="P9" s="21">
+      <c r="P9" s="22">
         <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
         <v/>
       </c>
-      <c r="Q9" s="21">
+      <c r="Q9" s="22">
         <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
         <v/>
       </c>
@@ -1161,33 +1161,33 @@
           <t>Bumps de la entrada</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>43</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="F10" s="29" t="n"/>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="29" t="n"/>
-      <c r="J10" s="29" t="n"/>
-      <c r="K10" s="29" t="n"/>
-      <c r="L10" s="29" t="n"/>
-      <c r="M10" s="29" t="n"/>
-      <c r="N10" s="29" t="n"/>
-      <c r="O10" s="21">
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+      <c r="H10" s="30" t="n"/>
+      <c r="I10" s="30" t="n"/>
+      <c r="J10" s="30" t="n"/>
+      <c r="K10" s="30" t="n"/>
+      <c r="L10" s="30" t="n"/>
+      <c r="M10" s="30" t="n"/>
+      <c r="N10" s="30" t="n"/>
+      <c r="O10" s="22">
         <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
         <v/>
       </c>
-      <c r="P10" s="21">
+      <c r="P10" s="22">
         <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
         <v/>
       </c>
-      <c r="Q10" s="21">
+      <c r="Q10" s="22">
         <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
         <v/>
       </c>
@@ -1198,33 +1198,33 @@
           <t>Entraron al grupo</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>182</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>190</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="F11" s="29" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="29" t="n"/>
-      <c r="I11" s="29" t="n"/>
-      <c r="J11" s="29" t="n"/>
-      <c r="K11" s="29" t="n"/>
-      <c r="L11" s="29" t="n"/>
-      <c r="M11" s="29" t="n"/>
-      <c r="N11" s="29" t="n"/>
-      <c r="O11" s="21">
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="30" t="n"/>
+      <c r="I11" s="30" t="n"/>
+      <c r="J11" s="30" t="n"/>
+      <c r="K11" s="30" t="n"/>
+      <c r="L11" s="30" t="n"/>
+      <c r="M11" s="30" t="n"/>
+      <c r="N11" s="30" t="n"/>
+      <c r="O11" s="22">
         <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
         <v/>
       </c>
-      <c r="P11" s="21">
+      <c r="P11" s="22">
         <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
         <v/>
       </c>
-      <c r="Q11" s="21">
+      <c r="Q11" s="22">
         <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
         <v/>
       </c>
@@ -1235,33 +1235,33 @@
           <t>Asistentes en vivo</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="30" t="n">
         <v>118</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="30" t="n">
         <v>115</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="30" t="n">
         <v>135</v>
       </c>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="29" t="n"/>
-      <c r="I12" s="29" t="n"/>
-      <c r="J12" s="29" t="n"/>
-      <c r="K12" s="29" t="n"/>
-      <c r="L12" s="29" t="n"/>
-      <c r="M12" s="29" t="n"/>
-      <c r="N12" s="29" t="n"/>
-      <c r="O12" s="21">
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+      <c r="H12" s="30" t="n"/>
+      <c r="I12" s="30" t="n"/>
+      <c r="J12" s="30" t="n"/>
+      <c r="K12" s="30" t="n"/>
+      <c r="L12" s="30" t="n"/>
+      <c r="M12" s="30" t="n"/>
+      <c r="N12" s="30" t="n"/>
+      <c r="O12" s="22">
         <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
         <v/>
       </c>
-      <c r="P12" s="21">
+      <c r="P12" s="22">
         <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
         <v/>
       </c>
-      <c r="Q12" s="21">
+      <c r="Q12" s="22">
         <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
         <v/>
       </c>
@@ -1272,33 +1272,33 @@
           <t>Vieron el replay</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="30" t="n">
         <v>54</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="29" t="n"/>
-      <c r="I13" s="29" t="n"/>
-      <c r="J13" s="29" t="n"/>
-      <c r="K13" s="29" t="n"/>
-      <c r="L13" s="29" t="n"/>
-      <c r="M13" s="29" t="n"/>
-      <c r="N13" s="29" t="n"/>
-      <c r="O13" s="21">
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+      <c r="H13" s="30" t="n"/>
+      <c r="I13" s="30" t="n"/>
+      <c r="J13" s="30" t="n"/>
+      <c r="K13" s="30" t="n"/>
+      <c r="L13" s="30" t="n"/>
+      <c r="M13" s="30" t="n"/>
+      <c r="N13" s="30" t="n"/>
+      <c r="O13" s="22">
         <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
         <v/>
       </c>
-      <c r="P13" s="21">
+      <c r="P13" s="22">
         <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
         <v/>
       </c>
-      <c r="Q13" s="21">
+      <c r="Q13" s="22">
         <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
         <v/>
       </c>
@@ -1309,33 +1309,33 @@
           <t>Solicitudes (formulario de compra, aplicación o vendedor)</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="29" t="n"/>
-      <c r="K14" s="29" t="n"/>
-      <c r="L14" s="29" t="n"/>
-      <c r="M14" s="29" t="n"/>
-      <c r="N14" s="29" t="n"/>
-      <c r="O14" s="21">
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+      <c r="H14" s="30" t="n"/>
+      <c r="I14" s="30" t="n"/>
+      <c r="J14" s="30" t="n"/>
+      <c r="K14" s="30" t="n"/>
+      <c r="L14" s="30" t="n"/>
+      <c r="M14" s="30" t="n"/>
+      <c r="N14" s="30" t="n"/>
+      <c r="O14" s="22">
         <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
         <v/>
       </c>
-      <c r="P14" s="21">
+      <c r="P14" s="22">
         <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
         <v/>
       </c>
-      <c r="Q14" s="21">
+      <c r="Q14" s="22">
         <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
         <v/>
       </c>
@@ -1346,33 +1346,33 @@
           <t>Ventas de la oferta</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="29" t="n"/>
-      <c r="L15" s="29" t="n"/>
-      <c r="M15" s="29" t="n"/>
-      <c r="N15" s="29" t="n"/>
-      <c r="O15" s="21">
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+      <c r="H15" s="30" t="n"/>
+      <c r="I15" s="30" t="n"/>
+      <c r="J15" s="30" t="n"/>
+      <c r="K15" s="30" t="n"/>
+      <c r="L15" s="30" t="n"/>
+      <c r="M15" s="30" t="n"/>
+      <c r="N15" s="30" t="n"/>
+      <c r="O15" s="22">
         <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
         <v/>
       </c>
-      <c r="P15" s="21">
+      <c r="P15" s="22">
         <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
         <v/>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="22">
         <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
         <v/>
       </c>
@@ -1383,33 +1383,33 @@
           <t>Ventas del programa superior</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="29" t="n"/>
-      <c r="K16" s="29" t="n"/>
-      <c r="L16" s="29" t="n"/>
-      <c r="M16" s="29" t="n"/>
-      <c r="N16" s="29" t="n"/>
-      <c r="O16" s="21">
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+      <c r="H16" s="30" t="n"/>
+      <c r="I16" s="30" t="n"/>
+      <c r="J16" s="30" t="n"/>
+      <c r="K16" s="30" t="n"/>
+      <c r="L16" s="30" t="n"/>
+      <c r="M16" s="30" t="n"/>
+      <c r="N16" s="30" t="n"/>
+      <c r="O16" s="22">
         <f>IF(COUNT(C16:N16)=0,"",AVERAGE(C16:N16))</f>
         <v/>
       </c>
-      <c r="P16" s="21">
+      <c r="P16" s="22">
         <f>IF(COUNT(C16:N16)=0,"",MAX(C16:N16))</f>
         <v/>
       </c>
-      <c r="Q16" s="21">
+      <c r="Q16" s="22">
         <f>IF(COUNT(C16:N16)=0,"",MIN(C16:N16))</f>
         <v/>
       </c>
@@ -1420,33 +1420,33 @@
           <t>Facturado del lanzamiento (a precio de lista, con cuotas por cobrar)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="20" t="n">
         <v>10400</v>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="20" t="n">
         <v>9000</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="20" t="n">
         <v>12300</v>
       </c>
-      <c r="F17" s="19" t="n"/>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="19" t="n"/>
-      <c r="I17" s="19" t="n"/>
-      <c r="J17" s="19" t="n"/>
-      <c r="K17" s="19" t="n"/>
-      <c r="L17" s="19" t="n"/>
-      <c r="M17" s="19" t="n"/>
-      <c r="N17" s="19" t="n"/>
-      <c r="O17" s="20">
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="20" t="n"/>
+      <c r="J17" s="20" t="n"/>
+      <c r="K17" s="20" t="n"/>
+      <c r="L17" s="20" t="n"/>
+      <c r="M17" s="20" t="n"/>
+      <c r="N17" s="20" t="n"/>
+      <c r="O17" s="21">
         <f>IF(COUNT(C17:N17)=0,"",AVERAGE(C17:N17))</f>
         <v/>
       </c>
-      <c r="P17" s="20">
+      <c r="P17" s="21">
         <f>IF(COUNT(C17:N17)=0,"",MAX(C17:N17))</f>
         <v/>
       </c>
-      <c r="Q17" s="20">
+      <c r="Q17" s="21">
         <f>IF(COUNT(C17:N17)=0,"",MIN(C17:N17))</f>
         <v/>
       </c>
@@ -1457,33 +1457,33 @@
           <t>Cash cobrado hasta ahora de ese lanzamiento</t>
         </is>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="20" t="n">
         <v>6900</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="20" t="n">
         <v>6300</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="20" t="n">
         <v>8200</v>
       </c>
-      <c r="F18" s="19" t="n"/>
-      <c r="G18" s="19" t="n"/>
-      <c r="H18" s="19" t="n"/>
-      <c r="I18" s="19" t="n"/>
-      <c r="J18" s="19" t="n"/>
-      <c r="K18" s="19" t="n"/>
-      <c r="L18" s="19" t="n"/>
-      <c r="M18" s="19" t="n"/>
-      <c r="N18" s="19" t="n"/>
-      <c r="O18" s="20">
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="20" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="20" t="n"/>
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="20" t="n"/>
+      <c r="O18" s="21">
         <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
         <v/>
       </c>
-      <c r="P18" s="20">
+      <c r="P18" s="21">
         <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
         <v/>
       </c>
-      <c r="Q18" s="20">
+      <c r="Q18" s="21">
         <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
         <v/>
       </c>
@@ -1580,63 +1580,63 @@
           <t>% visita → entrada</t>
         </is>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C8=0,0,C9/C8))</f>
         <v/>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="24">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D8=0,0,D9/D8))</f>
         <v/>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E8=0,0,E9/E8))</f>
         <v/>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="24">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F8=0,0,F9/F8))</f>
         <v/>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="24">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G8=0,0,G9/G8))</f>
         <v/>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="24">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H8=0,0,H9/H8))</f>
         <v/>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="24">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I8=0,0,I9/I8))</f>
         <v/>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="24">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J8=0,0,J9/J8))</f>
         <v/>
       </c>
-      <c r="K21" s="23">
+      <c r="K21" s="24">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K8=0,0,K9/K8))</f>
         <v/>
       </c>
-      <c r="L21" s="23">
+      <c r="L21" s="24">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L8=0,0,L9/L8))</f>
         <v/>
       </c>
-      <c r="M21" s="23">
+      <c r="M21" s="24">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M8=0,0,M9/M8))</f>
         <v/>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="24">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N8=0,0,N9/N8))</f>
         <v/>
       </c>
-      <c r="O21" s="23">
+      <c r="O21" s="24">
         <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
         <v/>
       </c>
-      <c r="P21" s="23">
+      <c r="P21" s="24">
         <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
         <v/>
       </c>
-      <c r="Q21" s="23">
+      <c r="Q21" s="24">
         <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
         <v/>
       </c>
@@ -1695,15 +1695,15 @@
         <f>IF(COUNT(N7:N18)&lt;12,"",(N9*'Supuestos'!$C$14+N10*'Supuestos'!$C$15)/N7)</f>
         <v/>
       </c>
-      <c r="O22" s="25">
+      <c r="O22" s="26">
         <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
         <v/>
       </c>
-      <c r="P22" s="25">
+      <c r="P22" s="26">
         <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
         <v/>
       </c>
-      <c r="Q22" s="25">
+      <c r="Q22" s="26">
         <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
         <v/>
       </c>
@@ -1714,63 +1714,63 @@
           <t>% entrada → en vivo</t>
         </is>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="24">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C9=0,0,C12/C9))</f>
         <v/>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="24">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D9=0,0,D12/D9))</f>
         <v/>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E9=0,0,E12/E9))</f>
         <v/>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="24">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F9=0,0,F12/F9))</f>
         <v/>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="24">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G9=0,0,G12/G9))</f>
         <v/>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="24">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H9=0,0,H12/H9))</f>
         <v/>
       </c>
-      <c r="I23" s="23">
+      <c r="I23" s="24">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I9=0,0,I12/I9))</f>
         <v/>
       </c>
-      <c r="J23" s="23">
+      <c r="J23" s="24">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J9=0,0,J12/J9))</f>
         <v/>
       </c>
-      <c r="K23" s="23">
+      <c r="K23" s="24">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K9=0,0,K12/K9))</f>
         <v/>
       </c>
-      <c r="L23" s="23">
+      <c r="L23" s="24">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L9=0,0,L12/L9))</f>
         <v/>
       </c>
-      <c r="M23" s="23">
+      <c r="M23" s="24">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M9=0,0,M12/M9))</f>
         <v/>
       </c>
-      <c r="N23" s="23">
+      <c r="N23" s="24">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N9=0,0,N12/N9))</f>
         <v/>
       </c>
-      <c r="O23" s="23">
+      <c r="O23" s="24">
         <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
         <v/>
       </c>
-      <c r="P23" s="23">
+      <c r="P23" s="24">
         <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
         <v/>
       </c>
-      <c r="Q23" s="23">
+      <c r="Q23" s="24">
         <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
         <v/>
       </c>
@@ -1781,63 +1781,63 @@
           <t>Ventas ÷ asistentes en vivo</t>
         </is>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="24">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C12=0,0,C15/C12))</f>
         <v/>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="24">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D12=0,0,D15/D12))</f>
         <v/>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="24">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E12=0,0,E15/E12))</f>
         <v/>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="24">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F12=0,0,F15/F12))</f>
         <v/>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="24">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G12=0,0,G15/G12))</f>
         <v/>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="24">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H12=0,0,H15/H12))</f>
         <v/>
       </c>
-      <c r="I24" s="23">
+      <c r="I24" s="24">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I12=0,0,I15/I12))</f>
         <v/>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="24">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J12=0,0,J15/J12))</f>
         <v/>
       </c>
-      <c r="K24" s="23">
+      <c r="K24" s="24">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K12=0,0,K15/K12))</f>
         <v/>
       </c>
-      <c r="L24" s="23">
+      <c r="L24" s="24">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L12=0,0,L15/L12))</f>
         <v/>
       </c>
-      <c r="M24" s="23">
+      <c r="M24" s="24">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M12=0,0,M15/M12))</f>
         <v/>
       </c>
-      <c r="N24" s="23">
+      <c r="N24" s="24">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N12=0,0,N15/N12))</f>
         <v/>
       </c>
-      <c r="O24" s="23">
+      <c r="O24" s="24">
         <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
         <v/>
       </c>
-      <c r="P24" s="23">
+      <c r="P24" s="24">
         <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
         <v/>
       </c>
-      <c r="Q24" s="23">
+      <c r="Q24" s="24">
         <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
         <v/>
       </c>
@@ -1982,63 +1982,63 @@
           <t>% en vivo → solicitud</t>
         </is>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="24">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C12=0,0,C14/C12))</f>
         <v/>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="24">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D12=0,0,D14/D12))</f>
         <v/>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="24">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E12=0,0,E14/E12))</f>
         <v/>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="24">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F12=0,0,F14/F12))</f>
         <v/>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="24">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G12=0,0,G14/G12))</f>
         <v/>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="24">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H12=0,0,H14/H12))</f>
         <v/>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="24">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I12=0,0,I14/I12))</f>
         <v/>
       </c>
-      <c r="J27" s="23">
+      <c r="J27" s="24">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J12=0,0,J14/J12))</f>
         <v/>
       </c>
-      <c r="K27" s="23">
+      <c r="K27" s="24">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K12=0,0,K14/K12))</f>
         <v/>
       </c>
-      <c r="L27" s="23">
+      <c r="L27" s="24">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L12=0,0,L14/L12))</f>
         <v/>
       </c>
-      <c r="M27" s="23">
+      <c r="M27" s="24">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M12=0,0,M14/M12))</f>
         <v/>
       </c>
-      <c r="N27" s="23">
+      <c r="N27" s="24">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N12=0,0,N14/N12))</f>
         <v/>
       </c>
-      <c r="O27" s="23">
+      <c r="O27" s="24">
         <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
         <v/>
       </c>
-      <c r="P27" s="23">
+      <c r="P27" s="24">
         <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
         <v/>
       </c>
-      <c r="Q27" s="23">
+      <c r="Q27" s="24">
         <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
         <v/>
       </c>
@@ -2116,63 +2116,63 @@
           <t>% solicitud → compra</t>
         </is>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="24">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C14=0,0,C15/C14))</f>
         <v/>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="24">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D14=0,0,D15/D14))</f>
         <v/>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="24">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E14=0,0,E15/E14))</f>
         <v/>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="24">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F14=0,0,F15/F14))</f>
         <v/>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="24">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G14=0,0,G15/G14))</f>
         <v/>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="24">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H14=0,0,H15/H14))</f>
         <v/>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="24">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I14=0,0,I15/I14))</f>
         <v/>
       </c>
-      <c r="J29" s="23">
+      <c r="J29" s="24">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J14=0,0,J15/J14))</f>
         <v/>
       </c>
-      <c r="K29" s="23">
+      <c r="K29" s="24">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K14=0,0,K15/K14))</f>
         <v/>
       </c>
-      <c r="L29" s="23">
+      <c r="L29" s="24">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L14=0,0,L15/L14))</f>
         <v/>
       </c>
-      <c r="M29" s="23">
+      <c r="M29" s="24">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M14=0,0,M15/M14))</f>
         <v/>
       </c>
-      <c r="N29" s="23">
+      <c r="N29" s="24">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N14=0,0,N15/N14))</f>
         <v/>
       </c>
-      <c r="O29" s="23">
+      <c r="O29" s="24">
         <f>IF(COUNT(C29:N29)=0,"",AVERAGE(C29:N29))</f>
         <v/>
       </c>
-      <c r="P29" s="23">
+      <c r="P29" s="24">
         <f>IF(COUNT(C29:N29)=0,"",MAX(C29:N29))</f>
         <v/>
       </c>
-      <c r="Q29" s="23">
+      <c r="Q29" s="24">
         <f>IF(COUNT(C29:N29)=0,"",MIN(C29:N29))</f>
         <v/>
       </c>
@@ -2298,15 +2298,15 @@
         <f>IF(COUNT(N7:N18)&lt;12,"",N17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-N9*'Supuestos'!$C$35-'Supuestos'!$C$36-N7)</f>
         <v/>
       </c>
-      <c r="O31" s="20">
+      <c r="O31" s="21">
         <f>IF(COUNT(C31:N31)=0,"",AVERAGE(C31:N31))</f>
         <v/>
       </c>
-      <c r="P31" s="20">
+      <c r="P31" s="21">
         <f>IF(COUNT(C31:N31)=0,"",MAX(C31:N31))</f>
         <v/>
       </c>
-      <c r="Q31" s="20">
+      <c r="Q31" s="21">
         <f>IF(COUNT(C31:N31)=0,"",MIN(C31:N31))</f>
         <v/>
       </c>
@@ -2317,63 +2317,63 @@
           <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="21">
         <f>IF(COUNT(C7:C18)&lt;12,"",C18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-C9*'Supuestos'!$C$35-'Supuestos'!$C$36-C7)</f>
         <v/>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="21">
         <f>IF(COUNT(D7:D18)&lt;12,"",D18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-D9*'Supuestos'!$C$35-'Supuestos'!$C$36-D7)</f>
         <v/>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="21">
         <f>IF(COUNT(E7:E18)&lt;12,"",E18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-E9*'Supuestos'!$C$35-'Supuestos'!$C$36-E7)</f>
         <v/>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="21">
         <f>IF(COUNT(F7:F18)&lt;12,"",F18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-F9*'Supuestos'!$C$35-'Supuestos'!$C$36-F7)</f>
         <v/>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="21">
         <f>IF(COUNT(G7:G18)&lt;12,"",G18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-G9*'Supuestos'!$C$35-'Supuestos'!$C$36-G7)</f>
         <v/>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="21">
         <f>IF(COUNT(H7:H18)&lt;12,"",H18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-H9*'Supuestos'!$C$35-'Supuestos'!$C$36-H7)</f>
         <v/>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="21">
         <f>IF(COUNT(I7:I18)&lt;12,"",I18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-I9*'Supuestos'!$C$35-'Supuestos'!$C$36-I7)</f>
         <v/>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="21">
         <f>IF(COUNT(J7:J18)&lt;12,"",J18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-J9*'Supuestos'!$C$35-'Supuestos'!$C$36-J7)</f>
         <v/>
       </c>
-      <c r="K32" s="20">
+      <c r="K32" s="21">
         <f>IF(COUNT(K7:K18)&lt;12,"",K18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-K9*'Supuestos'!$C$35-'Supuestos'!$C$36-K7)</f>
         <v/>
       </c>
-      <c r="L32" s="20">
+      <c r="L32" s="21">
         <f>IF(COUNT(L7:L18)&lt;12,"",L18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-L9*'Supuestos'!$C$35-'Supuestos'!$C$36-L7)</f>
         <v/>
       </c>
-      <c r="M32" s="20">
+      <c r="M32" s="21">
         <f>IF(COUNT(M7:M18)&lt;12,"",M18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-M9*'Supuestos'!$C$35-'Supuestos'!$C$36-M7)</f>
         <v/>
       </c>
-      <c r="N32" s="20">
+      <c r="N32" s="21">
         <f>IF(COUNT(N7:N18)&lt;12,"",N18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)-N9*'Supuestos'!$C$35-'Supuestos'!$C$36-N7)</f>
         <v/>
       </c>
-      <c r="O32" s="20">
+      <c r="O32" s="21">
         <f>IF(COUNT(C32:N32)=0,"",AVERAGE(C32:N32))</f>
         <v/>
       </c>
-      <c r="P32" s="20">
+      <c r="P32" s="21">
         <f>IF(COUNT(C32:N32)=0,"",MAX(C32:N32))</f>
         <v/>
       </c>
-      <c r="Q32" s="20">
+      <c r="Q32" s="21">
         <f>IF(COUNT(C32:N32)=0,"",MIN(C32:N32))</f>
         <v/>
       </c>
@@ -2499,15 +2499,15 @@
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N7=0,0,N17*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/N7))</f>
         <v/>
       </c>
-      <c r="O34" s="25">
+      <c r="O34" s="26">
         <f>IF(COUNT(C34:N34)=0,"",AVERAGE(C34:N34))</f>
         <v/>
       </c>
-      <c r="P34" s="25">
+      <c r="P34" s="26">
         <f>IF(COUNT(C34:N34)=0,"",MAX(C34:N34))</f>
         <v/>
       </c>
-      <c r="Q34" s="25">
+      <c r="Q34" s="26">
         <f>IF(COUNT(C34:N34)=0,"",MIN(C34:N34))</f>
         <v/>
       </c>
@@ -2518,63 +2518,63 @@
           <t>ROAS de caja (cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <f>IF(COUNT(C7:C18)&lt;12,"",IF(C7=0,0,C18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/C7))</f>
         <v/>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="26">
         <f>IF(COUNT(D7:D18)&lt;12,"",IF(D7=0,0,D18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/D7))</f>
         <v/>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="26">
         <f>IF(COUNT(E7:E18)&lt;12,"",IF(E7=0,0,E18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/E7))</f>
         <v/>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="26">
         <f>IF(COUNT(F7:F18)&lt;12,"",IF(F7=0,0,F18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/F7))</f>
         <v/>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="26">
         <f>IF(COUNT(G7:G18)&lt;12,"",IF(G7=0,0,G18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/G7))</f>
         <v/>
       </c>
-      <c r="H35" s="25">
+      <c r="H35" s="26">
         <f>IF(COUNT(H7:H18)&lt;12,"",IF(H7=0,0,H18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/H7))</f>
         <v/>
       </c>
-      <c r="I35" s="25">
+      <c r="I35" s="26">
         <f>IF(COUNT(I7:I18)&lt;12,"",IF(I7=0,0,I18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/I7))</f>
         <v/>
       </c>
-      <c r="J35" s="25">
+      <c r="J35" s="26">
         <f>IF(COUNT(J7:J18)&lt;12,"",IF(J7=0,0,J18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/J7))</f>
         <v/>
       </c>
-      <c r="K35" s="25">
+      <c r="K35" s="26">
         <f>IF(COUNT(K7:K18)&lt;12,"",IF(K7=0,0,K18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/K7))</f>
         <v/>
       </c>
-      <c r="L35" s="25">
+      <c r="L35" s="26">
         <f>IF(COUNT(L7:L18)&lt;12,"",IF(L7=0,0,L18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/L7))</f>
         <v/>
       </c>
-      <c r="M35" s="25">
+      <c r="M35" s="26">
         <f>IF(COUNT(M7:M18)&lt;12,"",IF(M7=0,0,M18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/M7))</f>
         <v/>
       </c>
-      <c r="N35" s="25">
+      <c r="N35" s="26">
         <f>IF(COUNT(N7:N18)&lt;12,"",IF(N7=0,0,N18*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34)/N7))</f>
         <v/>
       </c>
-      <c r="O35" s="25">
+      <c r="O35" s="26">
         <f>IF(COUNT(C35:N35)=0,"",AVERAGE(C35:N35))</f>
         <v/>
       </c>
-      <c r="P35" s="25">
+      <c r="P35" s="26">
         <f>IF(COUNT(C35:N35)=0,"",MAX(C35:N35))</f>
         <v/>
       </c>
-      <c r="Q35" s="25">
+      <c r="Q35" s="26">
         <f>IF(COUNT(C35:N35)=0,"",MIN(C35:N35))</f>
         <v/>
       </c>
@@ -2828,7 +2828,7 @@
           <t>&gt;1,2</t>
         </is>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="26">
         <f>'Modelo'!$C$14</f>
         <v/>
       </c>
@@ -2864,7 +2864,7 @@
           <t>&gt;3,5 %</t>
         </is>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="24">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
@@ -2936,7 +2936,7 @@
           <t>&gt;65 %</t>
         </is>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="24">
         <f>'Supuestos'!$C$20</f>
         <v/>
       </c>
@@ -3008,7 +3008,7 @@
           <t>&gt;22 %</t>
         </is>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="24">
         <f>'Supuestos'!$C$25</f>
         <v/>
       </c>
@@ -3080,7 +3080,7 @@
           <t>&gt;65 %</t>
         </is>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="24">
         <f>'Supuestos'!$C$27</f>
         <v/>
       </c>
@@ -3116,7 +3116,7 @@
           <t>&gt;10 %</t>
         </is>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <f>'Modelo'!$C$28</f>
         <v/>
       </c>
@@ -3152,7 +3152,7 @@
           <t>&gt;3</t>
         </is>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="26">
         <f>'Modelo'!$C$46</f>
         <v/>
       </c>
@@ -3893,7 +3893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3946,7 +3946,7 @@
           <t>Ninguna celda con error en Modelo</t>
         </is>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="19">
         <f>IF(ISERROR(SUM('Modelo'!C5:C160)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3962,7 +3962,7 @@
           <t>Ninguna celda con error en Simulador</t>
         </is>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="19">
         <f>IF(ISERROR(SUM('Simulador'!C5:G220)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3978,7 +3978,7 @@
           <t>Ninguna celda con error en Embudo</t>
         </is>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="19">
         <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3994,7 +3994,7 @@
           <t>Ninguna celda con error en Resumen</t>
         </is>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="19">
         <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -4010,7 +4010,7 @@
           <t>Ninguna celda con error en Proyección 12 meses</t>
         </is>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="19">
         <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -4026,7 +4026,7 @@
           <t>Ninguna celda con error en Escenarios</t>
         </is>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="19">
         <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -4042,7 +4042,7 @@
           <t>Ninguna celda con error en Seguimiento</t>
         </is>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="19">
         <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -4058,7 +4058,7 @@
           <t>Los supuestos de tráfico son mayores a cero</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="19">
         <f>IF(AND('Supuestos'!$C$10&gt;0,'Supuestos'!$C$13&gt;0),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4074,7 +4074,7 @@
           <t>La curva de cobranza suma 100 %</t>
         </is>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="19">
         <f>IF(ABS('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41-1)&lt;0.001,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4090,7 +4090,7 @@
           <t>Comisiones + reembolsos menores al 60 %</t>
         </is>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="19">
         <f>IF(('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)&lt;0.6,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4106,7 +4106,7 @@
           <t>El escenario en uso es 1, 2 o 3</t>
         </is>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="19">
         <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4122,7 +4122,7 @@
           <t>La inversión es mayor a cero</t>
         </is>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="19">
         <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4134,7 +4134,7 @@
           <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
         </is>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="19">
         <f>IF('Modelo'!$C$28&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4150,7 +4150,7 @@
           <t>Las conversiones están entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="19">
         <f>IF(AND('Supuestos'!$C$13&gt;=0,'Supuestos'!$C$13&lt;=1,'Supuestos'!$C$16&gt;=0,'Supuestos'!$C$16&lt;=1,'Supuestos'!$C$19&gt;=0,'Supuestos'!$C$19&lt;=1,'Supuestos'!$C$20&gt;=0,'Supuestos'!$C$20&lt;=1,'Supuestos'!$C$21&gt;=0,'Supuestos'!$C$21&lt;=1,'Supuestos'!$C$25&gt;=0,'Supuestos'!$C$25&lt;=1,'Supuestos'!$C$26&gt;=0,'Supuestos'!$C$26&lt;=1,'Supuestos'!$C$27&gt;=0,'Supuestos'!$C$27&lt;=1,'Supuestos'!$C$29&gt;=0,'Supuestos'!$C$29&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4166,7 +4166,7 @@
           <t>El margen de seguridad está entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="19">
         <f>IF(AND('Supuestos'!$C$45&gt;=0,'Supuestos'!$C$45&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4178,7 +4178,7 @@
           <t>El crecimiento mensual está entre −50 % y 100 %</t>
         </is>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="19">
         <f>IF(AND('Supuestos'!$C$47&gt;=-0.5,'Supuestos'!$C$47&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4194,7 +4194,7 @@
           <t>La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
         </is>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="19">
         <f>IF(AND('Modelo'!$C$9&lt;='Modelo'!$C$7,'Modelo'!$C$18&lt;='Modelo'!$C$9,'Modelo'!$C$22&lt;='Modelo'!$C$18,'Modelo'!$C$23&lt;='Modelo'!$C$19,'Modelo'!$C$27&lt;='Modelo'!$C$24),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4210,7 +4210,7 @@
           <t>En vivo + replay no superan el 100 % de los compradores</t>
         </is>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="19">
         <f>IF(('Supuestos'!$C$20+'Supuestos'!$C$21)&lt;=1,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -4220,19 +4220,212 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Simulador: lo que escribiste en las celdas amarillas</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+    </row>
     <row r="25">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ningún supuesto del Simulador fuera de rango (porcentajes entre 0 y 1, números no negativos)</t>
+        </is>
+      </c>
+      <c r="C25" s="19">
+        <f>IF(COUNTIF('Simulador'!$I$6:$I$94,"REVISAR")=0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>La columna Rango del Simulador marca la fila con el problema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Simulador: Los supuestos de tráfico son mayores a cero</t>
+        </is>
+      </c>
+      <c r="C26" s="19">
+        <f>IF(AND('Simulador'!$C$7&gt;0,'Simulador'!$C$10&gt;0),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Simulador: La curva de cobranza suma 100 %</t>
+        </is>
+      </c>
+      <c r="C27" s="19">
+        <f>IF(ABS('Simulador'!$C$53+'Simulador'!$C$54+'Simulador'!$C$55-1)&lt;0.001,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Simulador: Comisiones + reembolsos menores al 60 %</t>
+        </is>
+      </c>
+      <c r="C28" s="19">
+        <f>IF(('Simulador'!$C$58+'Simulador'!$C$59+'Simulador'!$C$61)&lt;0.6,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Si suman más, revisá los porcentajes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Simulador: El escenario en uso es 1, 2 o 3</t>
+        </is>
+      </c>
+      <c r="C29" s="19">
+        <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Supuestos → celda 'Escenario en uso'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Simulador: La inversión es mayor a cero</t>
+        </is>
+      </c>
+      <c r="C30" s="19">
+        <f>IF('Simulador'!$C$8&gt;0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Simulador: La meta de ventas es alcanzable (hay conversión a venta)</t>
+        </is>
+      </c>
+      <c r="C31" s="19">
+        <f>IF('Simulador'!$E$40&gt;0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Simulador: Las conversiones están entre 0 y 100 %</t>
+        </is>
+      </c>
+      <c r="C32" s="19">
+        <f>IF(AND('Simulador'!$C$10&gt;=0,'Simulador'!$C$10&lt;=1,'Simulador'!$C$15&gt;=0,'Simulador'!$C$15&lt;=1,'Simulador'!$C$22&gt;=0,'Simulador'!$C$22&lt;=1,'Simulador'!$C$25&gt;=0,'Simulador'!$C$25&lt;=1,'Simulador'!$C$27&gt;=0,'Simulador'!$C$27&lt;=1,'Simulador'!$C$31&gt;=0,'Simulador'!$C$31&lt;=1,'Simulador'!$C$33&gt;=0,'Simulador'!$C$33&lt;=1,'Simulador'!$C$38&gt;=0,'Simulador'!$C$38&lt;=1,'Simulador'!$C$44&gt;=0,'Simulador'!$C$44&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Simulador: El margen de seguridad está entre 0 y 100 %</t>
+        </is>
+      </c>
+      <c r="C33" s="19">
+        <f>IF(AND('Simulador'!$C$76&gt;=0,'Simulador'!$C$76&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Simulador: El crecimiento mensual está entre −50 % y 100 %</t>
+        </is>
+      </c>
+      <c r="C34" s="19">
+        <f>IF(AND('Supuestos'!$C$47&gt;=-0.5,'Supuestos'!$C$47&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Más de 100 % por mes no es realista para una proyección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Simulador: La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
+        </is>
+      </c>
+      <c r="C35" s="19">
+        <f>IF(AND('Simulador'!$E$12&lt;='Simulador'!$E$9,'Simulador'!$E$26&lt;='Simulador'!$E$12,'Simulador'!$E$32&lt;='Simulador'!$E$26,'Simulador'!$E$34&lt;='Simulador'!$E$28,'Simulador'!$E$39&lt;='Simulador'!$E$35),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Si falla, alguna conversión está por encima de 100 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Simulador: En vivo + replay no superan el 100 % de los compradores</t>
+        </is>
+      </c>
+      <c r="C36" s="19">
+        <f>IF(('Simulador'!$C$25+'Simulador'!$C$27)&lt;=1,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>El replay se cuenta sin los que fueron en vivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Estado general del modelo</t>
         </is>
       </c>
-      <c r="C25" s="37">
-        <f>IF(COUNTIF(C6:C23,"REVISAR")=0,"OK","REVISAR")</f>
+      <c r="C38" s="37">
+        <f>IF(COUNTIF(C6:C36,"REVISAR")=0,"OK","REVISAR")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:C25">
+  <conditionalFormatting sqref="C6:C38">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -4924,7 +5117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4935,6 +5128,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4992,6 +5186,11 @@
       <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Rango</t>
         </is>
       </c>
     </row>
@@ -5031,6 +5230,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I7" s="19">
+        <f>IF(AND(ISNUMBER(C7),C7&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -5038,11 +5241,11 @@
           <t>Inversión en publicidad por lanzamiento</t>
         </is>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <f>'Supuestos'!$C$8</f>
         <v/>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <f>'Supuestos'!$C$8</f>
         <v/>
       </c>
@@ -5055,6 +5258,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I8" s="19">
+        <f>IF(AND(ISNUMBER(C8),C8&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -5062,15 +5269,15 @@
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="22">
         <f>IF($C$7=0,0,$C$8/$C$7)</f>
         <v/>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="22">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="22">
         <f>IF(AND(ISNUMBER(E9),ISNUMBER(F9)),E9-F9,"")</f>
         <v/>
       </c>
@@ -5086,11 +5293,11 @@
           <t>% de visitas que compran la entrada</t>
         </is>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="24">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
@@ -5103,6 +5310,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I10" s="19">
+        <f>IF(AND(ISNUMBER(C10),C10&gt;=0,C10&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
@@ -5138,11 +5349,11 @@
         <f>IF($E$11=0,0,$C$8/$E$11)</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="22">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="22">
         <f>IF(AND(ISNUMBER(E12),ISNUMBER(F12)),E12-F12,"")</f>
         <v/>
       </c>
@@ -5175,6 +5386,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I13" s="19">
+        <f>IF(AND(ISNUMBER(C13),C13&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -5182,15 +5397,15 @@
           <t>Facturado: entradas</t>
         </is>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <f>$E$12*$C$13</f>
         <v/>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <f>IF(AND(ISNUMBER(E14),ISNUMBER(F14)),E14-F14,"")</f>
         <v/>
       </c>
@@ -5206,11 +5421,11 @@
           <t>Bump: % de compradores de entrada que lo toman</t>
         </is>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="23">
         <f>'Supuestos'!$C$16</f>
         <v/>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
         <f>'Supuestos'!$C$16</f>
         <v/>
       </c>
@@ -5223,6 +5438,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I15" s="19">
+        <f>IF(AND(ISNUMBER(C15),C15&gt;=0,C15&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -5230,15 +5449,15 @@
           <t>Ventas: bump de la entrada</t>
         </is>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <f>$E$12*$C$15</f>
         <v/>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="25">
         <f>IF(AND(ISNUMBER(E16),ISNUMBER(F16)),E16-F16,"")</f>
         <v/>
       </c>
@@ -5271,6 +5490,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I17" s="19">
+        <f>IF(AND(ISNUMBER(C17),C17&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -5278,15 +5501,15 @@
           <t>Facturado: bump de la entrada</t>
         </is>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <f>$E$16*$C$17</f>
         <v/>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="21">
         <f>'Modelo'!$C$12</f>
         <v/>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <f>IF(AND(ISNUMBER(E18),ISNUMBER(F18)),E18-F18,"")</f>
         <v/>
       </c>
@@ -5306,11 +5529,11 @@
         <f>$E$14+$E$18</f>
         <v/>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="21">
         <f>'Modelo'!$C$13</f>
         <v/>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="21">
         <f>IF(AND(ISNUMBER(E19),ISNUMBER(F19)),E19-F19,"")</f>
         <v/>
       </c>
@@ -5330,11 +5553,11 @@
         <f>IF($C$8=0,0,$E$19/$C$8)</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <f>'Modelo'!$C$14</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="26">
         <f>IF(AND(ISNUMBER(E20),ISNUMBER(F20)),E20-F20,"")</f>
         <v/>
       </c>
@@ -5363,11 +5586,11 @@
           <t>% que entra al grupo de WhatsApp</t>
         </is>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="23">
         <f>'Supuestos'!$C$19</f>
         <v/>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="24">
         <f>'Supuestos'!$C$19</f>
         <v/>
       </c>
@@ -5380,6 +5603,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I22" s="19">
+        <f>IF(AND(ISNUMBER(C22),C22&gt;=0,C22&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -5387,15 +5614,15 @@
           <t>Personas en el grupo</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="22">
         <f>$E$12*$C$22</f>
         <v/>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="22">
         <f>'Modelo'!$C$16</f>
         <v/>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="22">
         <f>IF(AND(ISNUMBER(E23),ISNUMBER(F23)),E23-F23,"")</f>
         <v/>
       </c>
@@ -5435,11 +5662,11 @@
           <t>% que asiste en vivo</t>
         </is>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <f>'Supuestos'!$C$20</f>
         <v/>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="24">
         <f>'Supuestos'!$C$20</f>
         <v/>
       </c>
@@ -5452,6 +5679,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I25" s="19">
+        <f>IF(AND(ISNUMBER(C25),C25&gt;=0,C25&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
@@ -5463,11 +5694,11 @@
         <f>$E$12*$C$25</f>
         <v/>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="22">
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="22">
         <f>IF(AND(ISNUMBER(E26),ISNUMBER(F26)),E26-F26,"")</f>
         <v/>
       </c>
@@ -5483,11 +5714,11 @@
           <t>% que ve el replay (sin contar los que fueron en vivo)</t>
         </is>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="23">
         <f>'Supuestos'!$C$21</f>
         <v/>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="24">
         <f>'Supuestos'!$C$21</f>
         <v/>
       </c>
@@ -5500,6 +5731,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I27" s="19">
+        <f>IF(AND(ISNUMBER(C27),C27&gt;=0,C27&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
@@ -5507,15 +5742,15 @@
           <t>Vieron el replay</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="22">
         <f>$E$12*$C$27</f>
         <v/>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="22">
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="22">
         <f>IF(AND(ISNUMBER(E28),ISNUMBER(F28)),E28-F28,"")</f>
         <v/>
       </c>
@@ -5568,11 +5803,11 @@
           <t>% de asistentes en vivo que solicitan (formulario de compra, de aplicación o hablar con un vendedor)</t>
         </is>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <f>'Supuestos'!$C$25</f>
         <v/>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="24">
         <f>'Supuestos'!$C$25</f>
         <v/>
       </c>
@@ -5585,6 +5820,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I31" s="19">
+        <f>IF(AND(ISNUMBER(C31),C31&gt;=0,C31&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
@@ -5592,15 +5831,15 @@
           <t>Solicitudes: en vivo</t>
         </is>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="25">
         <f>$E$26*$C$31</f>
         <v/>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="25">
         <f>'Modelo'!$C$22</f>
         <v/>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="25">
         <f>IF(AND(ISNUMBER(E32),ISNUMBER(F32)),E32-F32,"")</f>
         <v/>
       </c>
@@ -5616,11 +5855,11 @@
           <t>% de los que ven el replay que solicitan</t>
         </is>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="23">
         <f>'Supuestos'!$C$26</f>
         <v/>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="24">
         <f>'Supuestos'!$C$26</f>
         <v/>
       </c>
@@ -5633,6 +5872,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I33" s="19">
+        <f>IF(AND(ISNUMBER(C33),C33&gt;=0,C33&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
@@ -5640,15 +5883,15 @@
           <t>Solicitudes: replay</t>
         </is>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="25">
         <f>$E$28*$C$33</f>
         <v/>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="25">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="25">
         <f>IF(AND(ISNUMBER(E34),ISNUMBER(F34)),E34-F34,"")</f>
         <v/>
       </c>
@@ -5668,11 +5911,11 @@
         <f>$E$32+$E$34</f>
         <v/>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="25">
         <f>'Modelo'!$C$24</f>
         <v/>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="25">
         <f>IF(AND(ISNUMBER(E35),ISNUMBER(F35)),E35-F35,"")</f>
         <v/>
       </c>
@@ -5688,15 +5931,15 @@
           <t>% de compradores de entrada que solicitan</t>
         </is>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="27">
         <f>IF($E$12=0,0,$E$35/$E$12)</f>
         <v/>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="27">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
-      <c r="G36" s="26">
+      <c r="G36" s="27">
         <f>IF(AND(ISNUMBER(E36),ISNUMBER(F36)),E36-F36,"")</f>
         <v/>
       </c>
@@ -5736,11 +5979,11 @@
           <t>% de solicitudes que terminan en compra</t>
         </is>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="23">
         <f>'Supuestos'!$C$27</f>
         <v/>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="24">
         <f>'Supuestos'!$C$27</f>
         <v/>
       </c>
@@ -5753,6 +5996,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I38" s="19">
+        <f>IF(AND(ISNUMBER(C38),C38&gt;=0,C38&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
@@ -5764,11 +6011,11 @@
         <f>$E$35*$C$38</f>
         <v/>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="25">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="G39" s="24">
+      <c r="G39" s="25">
         <f>IF(AND(ISNUMBER(E39),ISNUMBER(F39)),E39-F39,"")</f>
         <v/>
       </c>
@@ -5784,15 +6031,15 @@
           <t>% de compradores de entrada que compran la oferta</t>
         </is>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="27">
         <f>IF($E$12=0,0,$E$39/$E$12)</f>
         <v/>
       </c>
-      <c r="F40" s="26">
+      <c r="F40" s="27">
         <f>'Modelo'!$C$28</f>
         <v/>
       </c>
-      <c r="G40" s="26">
+      <c r="G40" s="27">
         <f>IF(AND(ISNUMBER(E40),ISNUMBER(F40)),E40-F40,"")</f>
         <v/>
       </c>
@@ -5849,6 +6096,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I42" s="19">
+        <f>IF(AND(ISNUMBER(C42),C42&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -5856,15 +6107,15 @@
           <t>Facturado: oferta</t>
         </is>
       </c>
-      <c r="E43" s="20">
+      <c r="E43" s="21">
         <f>$E$39*$C$42</f>
         <v/>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="21">
         <f>'Modelo'!$C$30</f>
         <v/>
       </c>
-      <c r="G43" s="20">
+      <c r="G43" s="21">
         <f>IF(AND(ISNUMBER(E43),ISNUMBER(F43)),E43-F43,"")</f>
         <v/>
       </c>
@@ -5880,11 +6131,11 @@
           <t>Programa superior: % de compradores de la oferta que lo toman</t>
         </is>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="23">
         <f>'Supuestos'!$C$29</f>
         <v/>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="24">
         <f>'Supuestos'!$C$29</f>
         <v/>
       </c>
@@ -5897,6 +6148,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I44" s="19">
+        <f>IF(AND(ISNUMBER(C44),C44&gt;=0,C44&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -5904,15 +6159,15 @@
           <t>Ventas: programa superior</t>
         </is>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="25">
         <f>$E$39*$C$44</f>
         <v/>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="25">
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="25">
         <f>IF(AND(ISNUMBER(E45),ISNUMBER(F45)),E45-F45,"")</f>
         <v/>
       </c>
@@ -5945,6 +6200,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I46" s="19">
+        <f>IF(AND(ISNUMBER(C46),C46&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
@@ -5952,15 +6211,15 @@
           <t>Facturado: programa superior</t>
         </is>
       </c>
-      <c r="E47" s="20">
+      <c r="E47" s="21">
         <f>$E$45*$C$46</f>
         <v/>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="21">
         <f>'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="G47" s="20">
+      <c r="G47" s="21">
         <f>IF(AND(ISNUMBER(E47),ISNUMBER(F47)),E47-F47,"")</f>
         <v/>
       </c>
@@ -5980,11 +6239,11 @@
         <f>$E$19+$E$43+$E$47</f>
         <v/>
       </c>
-      <c r="F48" s="20">
+      <c r="F48" s="21">
         <f>'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="G48" s="20">
+      <c r="G48" s="21">
         <f>IF(AND(ISNUMBER(E48),ISNUMBER(F48)),E48-F48,"")</f>
         <v/>
       </c>
@@ -6024,15 +6283,15 @@
           <t>Ventas de la oferta por entrada (para la proyección)</t>
         </is>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="27">
         <f>IF($E$12=0,0,$E$39/$E$12)</f>
         <v/>
       </c>
-      <c r="F50" s="26">
+      <c r="F50" s="27">
         <f>'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="G50" s="26">
+      <c r="G50" s="27">
         <f>IF(AND(ISNUMBER(E50),ISNUMBER(F50)),E50-F50,"")</f>
         <v/>
       </c>
@@ -6085,11 +6344,11 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="23">
         <f>'Supuestos'!$C$39</f>
         <v/>
       </c>
-      <c r="D53" s="23">
+      <c r="D53" s="24">
         <f>'Supuestos'!$C$39</f>
         <v/>
       </c>
@@ -6102,6 +6361,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I53" s="19">
+        <f>IF(AND(ISNUMBER(C53),C53&gt;=0,C53&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
@@ -6109,11 +6372,11 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="23">
         <f>'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="24">
         <f>'Supuestos'!$C$40</f>
         <v/>
       </c>
@@ -6126,6 +6389,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I54" s="19">
+        <f>IF(AND(ISNUMBER(C54),C54&gt;=0,C54&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -6133,11 +6400,11 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="23">
         <f>'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="D55" s="23">
+      <c r="D55" s="24">
         <f>'Supuestos'!$C$41</f>
         <v/>
       </c>
@@ -6150,6 +6417,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I55" s="19">
+        <f>IF(AND(ISNUMBER(C55),C55&gt;=0,C55&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -6157,15 +6428,15 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="21">
         <f>$E$48*($C$53+$C$54+$C$55)</f>
         <v/>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="21">
         <f>'Modelo'!$C$38</f>
         <v/>
       </c>
-      <c r="G56" s="20">
+      <c r="G56" s="21">
         <f>IF(AND(ISNUMBER(E56),ISNUMBER(F56)),E56-F56,"")</f>
         <v/>
       </c>
@@ -6181,15 +6452,15 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="21">
         <f>$E$48*$C$53</f>
         <v/>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="21">
         <f>'Modelo'!$C$39</f>
         <v/>
       </c>
-      <c r="G57" s="20">
+      <c r="G57" s="21">
         <f>IF(AND(ISNUMBER(E57),ISNUMBER(F57)),E57-F57,"")</f>
         <v/>
       </c>
@@ -6205,11 +6476,11 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C58" s="22">
+      <c r="C58" s="23">
         <f>'Supuestos'!$C$32</f>
         <v/>
       </c>
-      <c r="D58" s="23">
+      <c r="D58" s="24">
         <f>'Supuestos'!$C$32</f>
         <v/>
       </c>
@@ -6222,6 +6493,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I58" s="19">
+        <f>IF(AND(ISNUMBER(C58),C58&gt;=0,C58&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
@@ -6229,11 +6504,11 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="23">
         <f>'Supuestos'!$C$33</f>
         <v/>
       </c>
-      <c r="D59" s="23">
+      <c r="D59" s="24">
         <f>'Supuestos'!$C$33</f>
         <v/>
       </c>
@@ -6246,6 +6521,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I59" s="19">
+        <f>IF(AND(ISNUMBER(C59),C59&gt;=0,C59&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
@@ -6253,15 +6532,15 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="E60" s="20">
+      <c r="E60" s="21">
         <f>$E$56*($C$58+$C$59)</f>
         <v/>
       </c>
-      <c r="F60" s="20">
+      <c r="F60" s="21">
         <f>'Modelo'!$C$40</f>
         <v/>
       </c>
-      <c r="G60" s="20">
+      <c r="G60" s="21">
         <f>IF(AND(ISNUMBER(E60),ISNUMBER(F60)),E60-F60,"")</f>
         <v/>
       </c>
@@ -6277,11 +6556,11 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C61" s="22">
+      <c r="C61" s="23">
         <f>'Supuestos'!$C$34</f>
         <v/>
       </c>
-      <c r="D61" s="23">
+      <c r="D61" s="24">
         <f>'Supuestos'!$C$34</f>
         <v/>
       </c>
@@ -6294,6 +6573,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I61" s="19">
+        <f>IF(AND(ISNUMBER(C61),C61&gt;=0,C61&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
@@ -6301,15 +6584,15 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="E62" s="20">
+      <c r="E62" s="21">
         <f>$E$56*$C$61</f>
         <v/>
       </c>
-      <c r="F62" s="20">
+      <c r="F62" s="21">
         <f>'Modelo'!$C$41</f>
         <v/>
       </c>
-      <c r="G62" s="20">
+      <c r="G62" s="21">
         <f>IF(AND(ISNUMBER(E62),ISNUMBER(F62)),E62-F62,"")</f>
         <v/>
       </c>
@@ -6329,11 +6612,11 @@
         <f>$E$56*(1-$C$58-$C$59-$C$61)</f>
         <v/>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="21">
         <f>'Modelo'!$C$42</f>
         <v/>
       </c>
-      <c r="G63" s="20">
+      <c r="G63" s="21">
         <f>IF(AND(ISNUMBER(E63),ISNUMBER(F63)),E63-F63,"")</f>
         <v/>
       </c>
@@ -6366,6 +6649,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I64" s="19">
+        <f>IF(AND(ISNUMBER(C64),C64&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
@@ -6373,15 +6660,15 @@
           <t>Costos por entrada (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="E65" s="20">
+      <c r="E65" s="21">
         <f>$E$12*$C$64</f>
         <v/>
       </c>
-      <c r="F65" s="20">
+      <c r="F65" s="21">
         <f>'Modelo'!$C$43</f>
         <v/>
       </c>
-      <c r="G65" s="20">
+      <c r="G65" s="21">
         <f>IF(AND(ISNUMBER(E65),ISNUMBER(F65)),E65-F65,"")</f>
         <v/>
       </c>
@@ -6397,11 +6684,11 @@
           <t>Costos fijos por lanzamiento</t>
         </is>
       </c>
-      <c r="C66" s="19">
+      <c r="C66" s="20">
         <f>'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="D66" s="20">
+      <c r="D66" s="21">
         <f>'Supuestos'!$C$36</f>
         <v/>
       </c>
@@ -6414,6 +6701,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I66" s="19">
+        <f>IF(AND(ISNUMBER(C66),C66&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
@@ -6425,11 +6716,11 @@
         <f>$E$63-$E$65-$C$66-$C$8</f>
         <v/>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="21">
         <f>'Modelo'!$C$44</f>
         <v/>
       </c>
-      <c r="G67" s="20">
+      <c r="G67" s="21">
         <f>IF(AND(ISNUMBER(E67),ISNUMBER(F67)),E67-F67,"")</f>
         <v/>
       </c>
@@ -6445,15 +6736,15 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="E68" s="25">
+      <c r="E68" s="26">
         <f>IF($C$8=0,0,$E$48/$C$8)</f>
         <v/>
       </c>
-      <c r="F68" s="25">
+      <c r="F68" s="26">
         <f>'Modelo'!$C$45</f>
         <v/>
       </c>
-      <c r="G68" s="25">
+      <c r="G68" s="26">
         <f>IF(AND(ISNUMBER(E68),ISNUMBER(F68)),E68-F68,"")</f>
         <v/>
       </c>
@@ -6473,11 +6764,11 @@
         <f>IF($C$8=0,0,$E$63/$C$8)</f>
         <v/>
       </c>
-      <c r="F69" s="25">
+      <c r="F69" s="26">
         <f>'Modelo'!$C$46</f>
         <v/>
       </c>
-      <c r="G69" s="25">
+      <c r="G69" s="26">
         <f>IF(AND(ISNUMBER(E69),ISNUMBER(F69)),E69-F69,"")</f>
         <v/>
       </c>
@@ -6493,15 +6784,15 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="E70" s="23">
+      <c r="E70" s="24">
         <f>IF($E$56=0,0,$E$67/$E$56)</f>
         <v/>
       </c>
-      <c r="F70" s="23">
+      <c r="F70" s="24">
         <f>'Modelo'!$C$47</f>
         <v/>
       </c>
-      <c r="G70" s="23">
+      <c r="G70" s="24">
         <f>IF(AND(ISNUMBER(E70),ISNUMBER(F70)),E70-F70,"")</f>
         <v/>
       </c>
@@ -6517,11 +6808,11 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="28">
         <f>'Supuestos'!$C$44</f>
         <v/>
       </c>
-      <c r="D71" s="25">
+      <c r="D71" s="26">
         <f>'Supuestos'!$C$44</f>
         <v/>
       </c>
@@ -6534,6 +6825,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I71" s="19">
+        <f>IF(AND(ISNUMBER(C71),C71&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
@@ -6541,11 +6836,11 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="E72" s="28">
+      <c r="E72" s="29">
         <f>IF($E$69&gt;=$C$71,"SÍ","NO")</f>
         <v/>
       </c>
-      <c r="F72" s="28">
+      <c r="F72" s="29">
         <f>'Modelo'!$C$48</f>
         <v/>
       </c>
@@ -6626,11 +6921,11 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C76" s="22">
+      <c r="C76" s="23">
         <f>'Supuestos'!$C$45</f>
         <v/>
       </c>
-      <c r="D76" s="23">
+      <c r="D76" s="24">
         <f>'Supuestos'!$C$45</f>
         <v/>
       </c>
@@ -6642,6 +6937,10 @@
         <is>
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
+      </c>
+      <c r="I76" s="19">
+        <f>IF(AND(ISNUMBER(C76),C76&gt;=0,C76&lt;=1),"OK","REVISAR")</f>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -6811,7 +7110,7 @@
         <f>IF($E$11&gt;$E$75,"ROJO",IF(AND($E$11&lt;=$E$77,$E$69&gt;=$C$71),"VERDE","AMARILLO"))</f>
         <v/>
       </c>
-      <c r="F84" s="28">
+      <c r="F84" s="29">
         <f>'Modelo'!$C$59</f>
         <v/>
       </c>
@@ -6831,11 +7130,11 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C85" s="29">
+      <c r="C85" s="30">
         <f>'Supuestos'!$C$46</f>
         <v/>
       </c>
-      <c r="D85" s="21">
+      <c r="D85" s="22">
         <f>'Supuestos'!$C$46</f>
         <v/>
       </c>
@@ -6848,6 +7147,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I85" s="19">
+        <f>IF(AND(ISNUMBER(C85),C85&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="4" t="inlineStr">
@@ -6859,11 +7162,11 @@
         <f>IF($E$40=0,"inalcanzable con estos supuestos",$C$85/$E$40*$E$11)</f>
         <v/>
       </c>
-      <c r="F86" s="20">
+      <c r="F86" s="21">
         <f>'Modelo'!$C$60</f>
         <v/>
       </c>
-      <c r="G86" s="20">
+      <c r="G86" s="21">
         <f>IF(AND(ISNUMBER(E86),ISNUMBER(F86)),E86-F86,"")</f>
         <v/>
       </c>
@@ -6879,15 +7182,15 @@
           <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="E87" s="20">
+      <c r="E87" s="21">
         <f>IF($E$40=0,"inalcanzable con estos supuestos",$C$85/$E$40*$E$77)</f>
         <v/>
       </c>
-      <c r="F87" s="20">
+      <c r="F87" s="21">
         <f>'Modelo'!$C$61</f>
         <v/>
       </c>
-      <c r="G87" s="20">
+      <c r="G87" s="21">
         <f>IF(AND(ISNUMBER(E87),ISNUMBER(F87)),E87-F87,"")</f>
         <v/>
       </c>
@@ -7075,39 +7378,61 @@
         </is>
       </c>
     </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>La columna Rango avisa si escribiste algo imposible (un porcentaje fuera de 0 a 1, un negativo, texto) y Chequeos repite los chequeos del modelo con tus números del Simulador.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B99:H99"/>
     <mergeCell ref="B98:H98"/>
     <mergeCell ref="B96:H96"/>
   </mergeCells>
+  <conditionalFormatting sqref="I6:I94">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+      <formula>"REVISAR"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C6:C94">
-    <cfRule type="expression" priority="1" dxfId="3">
+    <cfRule type="expression" priority="2" dxfId="3">
       <formula>AND(ISNUMBER(C6),C6&lt;&gt;D6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E72:F72">
-    <cfRule type="expression" priority="2" dxfId="0">
+    <cfRule type="expression" priority="3" dxfId="0">
       <formula>LEFT(E72,5)="VERDE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>LEFT(E72,8)="AMARILLO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
+    <cfRule type="expression" priority="5" dxfId="2">
       <formula>LEFT(E72,4)="ROJO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E84:F84">
-    <cfRule type="expression" priority="5" dxfId="0">
+    <cfRule type="expression" priority="6" dxfId="0">
       <formula>LEFT(E84,5)="VERDE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="1">
       <formula>LEFT(E84,8)="AMARILLO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="2">
       <formula>LEFT(E84,4)="ROJO"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C10 C15 C22 C25 C27 C31 C33 C38 C44 C53 C54 C55 C58 C59 C61 C76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Porcentaje fuera de rango" error="Escribí el porcentaje como fracción entre 0 y 1 (15 % = 0,15)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C7 C8 C13 C17 C42 C46 C64 C66 C71 C85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Tiene que ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
@@ -7209,7 +7534,7 @@
           <t>Visitas a la página de ventas de la entrada</t>
         </is>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="22">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
@@ -7247,15 +7572,15 @@
           <t>Compran la entrada</t>
         </is>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="24">
         <f>IF('Modelo'!$C$7=0,0,'Modelo'!$C$9/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$9/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7283,15 +7608,15 @@
           <t>Toman el bump de la entrada</t>
         </is>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="22">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="24">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$11/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$11/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7322,15 +7647,15 @@
           <t>Entran al grupo de WhatsApp</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="22">
         <f>'Modelo'!$C$16</f>
         <v/>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="24">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$16/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$16/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7358,15 +7683,15 @@
           <t>Asisten en vivo</t>
         </is>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="22">
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="24">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$18/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$18/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7394,15 +7719,15 @@
           <t>Ven el replay</t>
         </is>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="24">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$19/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$19/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7430,15 +7755,15 @@
           <t>Solicitan, de los que estuvieron en vivo</t>
         </is>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="22">
         <f>'Modelo'!$C$22</f>
         <v/>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="24">
         <f>IF('Modelo'!$C$18=0,0,'Modelo'!$C$22/'Modelo'!$C$18)</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$22/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7466,15 +7791,15 @@
           <t>Solicitan, de los que vieron el replay</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="22">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="24">
         <f>IF('Modelo'!$C$19=0,0,'Modelo'!$C$23/'Modelo'!$C$19)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$23/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7502,15 +7827,15 @@
           <t>Solicitudes (total)</t>
         </is>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="22">
         <f>'Modelo'!$C$24</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="24">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$24/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$24/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7538,15 +7863,15 @@
           <t>Compran la oferta</t>
         </is>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
         <f>IF('Modelo'!$C$24=0,0,'Modelo'!$C$27/'Modelo'!$C$24)</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$27/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7574,15 +7899,15 @@
           <t>Pasan al programa superior</t>
         </is>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="24">
         <f>IF('Modelo'!$C$27=0,0,'Modelo'!$C$31/'Modelo'!$C$27)</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$31/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -7784,7 +8109,7 @@
           <t>Escenario en uso (1 = conservador · 2 = base · 3 = optimista)</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -7817,7 +8142,7 @@
           <t>Inversión en publicidad por lanzamiento</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <v>3000</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -7837,7 +8162,7 @@
           <t>Lanzamientos por mes (para la proyección)</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -7900,17 +8225,17 @@
           <t>% de visitas que compran la entrada</t>
         </is>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="24">
         <f>IF('Supuestos'!$C$6=1,D13,IF('Supuestos'!$C$6=2,E13,F13))</f>
         <v/>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>0.015</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="23" t="n">
         <v>0.025</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>0.035</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -7970,17 +8295,17 @@
           <t>Bump: % de compradores de entrada que lo toman</t>
         </is>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="24">
         <f>IF('Supuestos'!$C$6=1,D16,IF('Supuestos'!$C$6=2,E16,F16))</f>
         <v/>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>0.12</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -8009,17 +8334,17 @@
           <t>% que entra al grupo de WhatsApp</t>
         </is>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="24">
         <f>IF('Supuestos'!$C$6=1,D19,IF('Supuestos'!$C$6=2,E19,F19))</f>
         <v/>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="23" t="n">
         <v>0.7</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="E19" s="23" t="n">
         <v>0.85</v>
       </c>
-      <c r="F19" s="22" t="n">
+      <c r="F19" s="23" t="n">
         <v>0.95</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -8039,17 +8364,17 @@
           <t>% que asiste en vivo</t>
         </is>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="24">
         <f>IF('Supuestos'!$C$6=1,D20,IF('Supuestos'!$C$6=2,E20,F20))</f>
         <v/>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="23" t="n">
         <v>0.4</v>
       </c>
-      <c r="E20" s="22" t="n">
+      <c r="E20" s="23" t="n">
         <v>0.55</v>
       </c>
-      <c r="F20" s="22" t="n">
+      <c r="F20" s="23" t="n">
         <v>0.65</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -8069,17 +8394,17 @@
           <t>% que ve el replay (sin contar los que fueron en vivo)</t>
         </is>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <f>IF('Supuestos'!$C$6=1,D21,IF('Supuestos'!$C$6=2,E21,F21))</f>
         <v/>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="23" t="n">
         <v>0.15</v>
       </c>
-      <c r="E21" s="22" t="n">
+      <c r="E21" s="23" t="n">
         <v>0.25</v>
       </c>
-      <c r="F21" s="22" t="n">
+      <c r="F21" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -8128,17 +8453,17 @@
           <t>% de asistentes en vivo que solicitan (formulario de compra, de aplicación o hablar con un vendedor)</t>
         </is>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="24">
         <f>IF('Supuestos'!$C$6=1,D25,IF('Supuestos'!$C$6=2,E25,F25))</f>
         <v/>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="E25" s="22" t="n">
+      <c r="E25" s="23" t="n">
         <v>0.16</v>
       </c>
-      <c r="F25" s="22" t="n">
+      <c r="F25" s="23" t="n">
         <v>0.22</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -8158,17 +8483,17 @@
           <t>% de los que ven el replay que solicitan</t>
         </is>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="24">
         <f>IF('Supuestos'!$C$6=1,D26,IF('Supuestos'!$C$6=2,E26,F26))</f>
         <v/>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="23" t="n">
         <v>0.02</v>
       </c>
-      <c r="E26" s="22" t="n">
+      <c r="E26" s="23" t="n">
         <v>0.04</v>
       </c>
-      <c r="F26" s="22" t="n">
+      <c r="F26" s="23" t="n">
         <v>0.06</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -8184,17 +8509,17 @@
           <t>% de solicitudes que terminan en compra</t>
         </is>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="24">
         <f>IF('Supuestos'!$C$6=1,D27,IF('Supuestos'!$C$6=2,E27,F27))</f>
         <v/>
       </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="23" t="n">
         <v>0.4</v>
       </c>
-      <c r="E27" s="22" t="n">
+      <c r="E27" s="23" t="n">
         <v>0.5</v>
       </c>
-      <c r="F27" s="22" t="n">
+      <c r="F27" s="23" t="n">
         <v>0.6</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -8234,17 +8559,17 @@
           <t>Programa superior: % de compradores de la oferta que lo toman</t>
         </is>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="24">
         <f>IF('Supuestos'!$C$6=1,D29,IF('Supuestos'!$C$6=2,E29,F29))</f>
         <v/>
       </c>
-      <c r="D29" s="22" t="n">
+      <c r="D29" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="E29" s="22" t="n">
+      <c r="E29" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="F29" s="22" t="n">
+      <c r="F29" s="23" t="n">
         <v>0.15</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -8273,7 +8598,7 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C32" s="22" t="n">
+      <c r="C32" s="23" t="n">
         <v>0.08</v>
       </c>
       <c r="G32" t="inlineStr">
@@ -8293,7 +8618,7 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -8313,7 +8638,7 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -8353,7 +8678,7 @@
           <t>Costos fijos por lanzamiento</t>
         </is>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="20" t="n">
         <v>800</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -8386,7 +8711,7 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C39" s="22" t="n">
+      <c r="C39" s="23" t="n">
         <v>0.5</v>
       </c>
       <c r="G39" t="inlineStr">
@@ -8406,7 +8731,7 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C40" s="22" t="n">
+      <c r="C40" s="23" t="n">
         <v>0.25</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -8426,7 +8751,7 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C41" s="22" t="n">
+      <c r="C41" s="23" t="n">
         <v>0.25</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -8459,7 +8784,7 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C44" s="27" t="n">
+      <c r="C44" s="28" t="n">
         <v>2</v>
       </c>
       <c r="G44" t="inlineStr">
@@ -8479,7 +8804,7 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C45" s="22" t="n">
+      <c r="C45" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -8499,7 +8824,7 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="30" t="n">
         <v>25</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -8519,7 +8844,7 @@
           <t>Crecimiento de la inversión por mes (proyección)</t>
         </is>
       </c>
-      <c r="C47" s="22" t="n">
+      <c r="C47" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -8539,7 +8864,7 @@
           <t>Caja inicial</t>
         </is>
       </c>
-      <c r="C48" s="19" t="n">
+      <c r="C48" s="20" t="n">
         <v>4000</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -8634,7 +8959,7 @@
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f>IF('Supuestos'!$C$10=0,0,'Supuestos'!$C$8/'Supuestos'!$C$10)</f>
         <v/>
       </c>
@@ -8682,7 +9007,7 @@
           <t>Facturado: entradas</t>
         </is>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <f>'Modelo'!$C$9*'Supuestos'!$C$14</f>
         <v/>
       </c>
@@ -8698,7 +9023,7 @@
           <t>Ventas: bump de la entrada</t>
         </is>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <f>'Modelo'!$C$9*'Supuestos'!$C$16</f>
         <v/>
       </c>
@@ -8714,7 +9039,7 @@
           <t>Facturado: bump de la entrada</t>
         </is>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>'Modelo'!$C$11*'Supuestos'!$C$15</f>
         <v/>
       </c>
@@ -8771,7 +9096,7 @@
           <t>Personas en el grupo</t>
         </is>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <f>'Modelo'!$C$9*'Supuestos'!$C$19</f>
         <v/>
       </c>
@@ -8819,7 +9144,7 @@
           <t>Vieron el replay</t>
         </is>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="22">
         <f>'Modelo'!$C$9*'Supuestos'!$C$21</f>
         <v/>
       </c>
@@ -8860,7 +9185,7 @@
           <t>Solicitudes: en vivo</t>
         </is>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="25">
         <f>'Modelo'!$C$18*'Supuestos'!$C$25</f>
         <v/>
       </c>
@@ -8876,7 +9201,7 @@
           <t>Solicitudes: replay</t>
         </is>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="25">
         <f>'Modelo'!$C$19*'Supuestos'!$C$26</f>
         <v/>
       </c>
@@ -8908,7 +9233,7 @@
           <t>% de compradores de entrada que solicitan</t>
         </is>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$24/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -8956,7 +9281,7 @@
           <t>% de compradores de entrada que compran la oferta</t>
         </is>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$27/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -8988,7 +9313,7 @@
           <t>Facturado: oferta</t>
         </is>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="21">
         <f>'Modelo'!$C$27*'Supuestos'!$C$24</f>
         <v/>
       </c>
@@ -9004,7 +9329,7 @@
           <t>Ventas: programa superior</t>
         </is>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="25">
         <f>'Modelo'!$C$27*'Supuestos'!$C$29</f>
         <v/>
       </c>
@@ -9020,7 +9345,7 @@
           <t>Facturado: programa superior</t>
         </is>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="21">
         <f>'Modelo'!$C$31*'Supuestos'!$C$28</f>
         <v/>
       </c>
@@ -9068,7 +9393,7 @@
           <t>Ventas de la oferta por entrada (para la proyección)</t>
         </is>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="27">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$27/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -9109,7 +9434,7 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="21">
         <f>'Modelo'!$C$33*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41)</f>
         <v/>
       </c>
@@ -9125,7 +9450,7 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="C39" s="20">
+      <c r="C39" s="21">
         <f>'Modelo'!$C$33*'Supuestos'!$C$39</f>
         <v/>
       </c>
@@ -9141,7 +9466,7 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="21">
         <f>'Modelo'!$C$38*('Supuestos'!$C$32+'Supuestos'!$C$33)</f>
         <v/>
       </c>
@@ -9157,7 +9482,7 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="21">
         <f>'Modelo'!$C$38*'Supuestos'!$C$34</f>
         <v/>
       </c>
@@ -9189,7 +9514,7 @@
           <t>Costos por entrada (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C43" s="20">
+      <c r="C43" s="21">
         <f>'Modelo'!$C$9*'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -9221,7 +9546,7 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="26">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$33/'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -9253,7 +9578,7 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="24">
         <f>IF('Modelo'!$C$38=0,0,'Modelo'!$C$44/'Modelo'!$C$38)</f>
         <v/>
       </c>
@@ -9269,7 +9594,7 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="29">
         <f>IF('Modelo'!$C$46&gt;='Supuestos'!$C$44,"SÍ","NO")</f>
         <v/>
       </c>
@@ -9463,7 +9788,7 @@
           <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="C61" s="20">
+      <c r="C61" s="21">
         <f>IF('Modelo'!$C$28=0,"inalcanzable con estos supuestos",'Supuestos'!$C$46/'Modelo'!$C$28*'Modelo'!$C$52)</f>
         <v/>
       </c>
@@ -9651,7 +9976,7 @@
           <t>Umbral de 'cerca del cero' (inversión × margen de seguridad)</t>
         </is>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="21">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$45</f>
         <v/>
       </c>
@@ -9676,143 +10001,143 @@
           <t>Precio ↓  /  % solicitud → compra →</t>
         </is>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="31" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <v>197</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B10)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <v>297</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B11)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="32" t="n">
         <v>497</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B12)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="32" t="n">
         <v>997</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B13)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <v>1997</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*C$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*D$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*E$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*F$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*$B14)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*G$9)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -9837,168 +10162,168 @@
           <t>Costo por entrada ↓  /  % en vivo que solicita →</t>
         </is>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="31" t="n">
         <v>0.08</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="31" t="n">
         <v>0.12</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="E19" s="31" t="n">
         <v>0.16</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="G19" s="30" t="n">
+      <c r="G19" s="31" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="32" t="n">
+      <c r="B20" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="21">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*C$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*C$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="21">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*D$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*D$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="21">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*E$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*E$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="21">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*F$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*F$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="21">
         <f>(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$14)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*G$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$20)*G$19)+(((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="32" t="n">
+      <c r="B21" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="21">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*C$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*C$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="21">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*D$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*D$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="21">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*E$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*E$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="21">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*F$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*F$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="21">
         <f>(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$14)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*G$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$20)*G$19)+(((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="32" t="n">
+      <c r="B22" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="21">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*C$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*C$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="21">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*D$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*D$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="21">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*E$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*E$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="21">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*F$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*F$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="21">
         <f>(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$14)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*G$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$20)*G$19)+(((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="32" t="n">
+      <c r="B23" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="21">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*C$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*C$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="21">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*D$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*D$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="21">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*E$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*E$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="21">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*F$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*F$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="21">
         <f>(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$14)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*G$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$20)*G$19)+(((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="32" t="n">
+      <c r="B24" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="21">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*C$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*C$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="21">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*D$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*D$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="21">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*E$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*E$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="21">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*F$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*F$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="21">
         <f>(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$14)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*G$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$20)*G$19)+(((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="32" t="n">
+      <c r="B25" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="21">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*C$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*C$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="21">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*D$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*D$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="21">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*E$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*E$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="21">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*F$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*F$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="21">
         <f>(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$14)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*G$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$20)*G$19)+(((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -10023,143 +10348,143 @@
           <t>Facturación objetivo ↓ / ROAS objetivo →</t>
         </is>
       </c>
-      <c r="C30" s="33" t="n">
+      <c r="C30" s="34" t="n">
         <v>1.5</v>
       </c>
-      <c r="D30" s="33" t="n">
+      <c r="D30" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="33" t="n">
+      <c r="E30" s="34" t="n">
         <v>2.5</v>
       </c>
-      <c r="F30" s="33" t="n">
+      <c r="F30" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="33" t="n">
+      <c r="G30" s="34" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="31" t="n">
+      <c r="B31" s="32" t="n">
         <v>5000</v>
       </c>
-      <c r="C31" s="20">
+      <c r="C31" s="21">
         <f>$B31/C$30</f>
         <v/>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="21">
         <f>$B31/D$30</f>
         <v/>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="21">
         <f>$B31/E$30</f>
         <v/>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="21">
         <f>$B31/F$30</f>
         <v/>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="21">
         <f>$B31/G$30</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="31" t="n">
+      <c r="B32" s="32" t="n">
         <v>10000</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="21">
         <f>$B32/C$30</f>
         <v/>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="21">
         <f>$B32/D$30</f>
         <v/>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="21">
         <f>$B32/E$30</f>
         <v/>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="21">
         <f>$B32/F$30</f>
         <v/>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="21">
         <f>$B32/G$30</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="32" t="n">
         <v>20000</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="21">
         <f>$B33/C$30</f>
         <v/>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="21">
         <f>$B33/D$30</f>
         <v/>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="21">
         <f>$B33/E$30</f>
         <v/>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="21">
         <f>$B33/F$30</f>
         <v/>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="21">
         <f>$B33/G$30</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="32" t="n">
         <v>30000</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="21">
         <f>$B34/C$30</f>
         <v/>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="21">
         <f>$B34/D$30</f>
         <v/>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="21">
         <f>$B34/E$30</f>
         <v/>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="21">
         <f>$B34/F$30</f>
         <v/>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="21">
         <f>$B34/G$30</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="32" t="n">
         <v>50000</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="21">
         <f>$B35/C$30</f>
         <v/>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="21">
         <f>$B35/D$30</f>
         <v/>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="21">
         <f>$B35/E$30</f>
         <v/>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="21">
         <f>$B35/F$30</f>
         <v/>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="21">
         <f>$B35/G$30</f>
         <v/>
       </c>
@@ -10172,51 +10497,51 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="34">
+      <c r="B37" s="35">
         <f>$B31</f>
         <v/>
       </c>
-      <c r="C37" s="21">
+      <c r="C37" s="22">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B31/'Modelo'!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="34">
+      <c r="B38" s="35">
         <f>$B32</f>
         <v/>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="22">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B32/'Modelo'!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="34">
+      <c r="B39" s="35">
         <f>$B33</f>
         <v/>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="22">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B33/'Modelo'!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="34">
+      <c r="B40" s="35">
         <f>$B34</f>
         <v/>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="22">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B34/'Modelo'!$C$36)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="34">
+      <c r="B41" s="35">
         <f>$B35</f>
         <v/>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="22">
         <f>IF('Modelo'!$C$36=0,"inalcanzable",$B35/'Modelo'!$C$36)</f>
         <v/>
       </c>
@@ -10229,19 +10554,19 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="35" t="n">
+      <c r="C44" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="D44" s="35" t="n">
+      <c r="D44" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="E44" s="35" t="n">
+      <c r="E44" s="36" t="n">
         <v>2.5</v>
       </c>
-      <c r="F44" s="35" t="n">
+      <c r="F44" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="35" t="n">
+      <c r="G44" s="36" t="n">
         <v>4</v>
       </c>
     </row>
@@ -10321,15 +10646,15 @@
           <t>actual</t>
         </is>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="21">
         <f>'Supuestos'!$C$8*1.0</f>
         <v/>
       </c>
-      <c r="D52" s="25">
+      <c r="D52" s="26">
         <f>IF(C52=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C52-'Supuestos'!$C$8))/C52)</f>
         <v/>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="21">
         <f>C52*(D52-1)</f>
         <v/>
       </c>
@@ -10340,15 +10665,15 @@
           <t>× 1.25</t>
         </is>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="21">
         <f>'Supuestos'!$C$8*1.25</f>
         <v/>
       </c>
-      <c r="D53" s="25">
+      <c r="D53" s="26">
         <f>IF(C53=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C53-'Supuestos'!$C$8))/C53)</f>
         <v/>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="21">
         <f>C53*(D53-1)</f>
         <v/>
       </c>
@@ -10359,15 +10684,15 @@
           <t>× 1.5</t>
         </is>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="21">
         <f>'Supuestos'!$C$8*1.5</f>
         <v/>
       </c>
-      <c r="D54" s="25">
+      <c r="D54" s="26">
         <f>IF(C54=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C54-'Supuestos'!$C$8))/C54)</f>
         <v/>
       </c>
-      <c r="E54" s="20">
+      <c r="E54" s="21">
         <f>C54*(D54-1)</f>
         <v/>
       </c>
@@ -10378,15 +10703,15 @@
           <t>× 2</t>
         </is>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="21">
         <f>'Supuestos'!$C$8*2.0</f>
         <v/>
       </c>
-      <c r="D55" s="25">
+      <c r="D55" s="26">
         <f>IF(C55=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C55-'Supuestos'!$C$8))/C55)</f>
         <v/>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="21">
         <f>C55*(D55-1)</f>
         <v/>
       </c>
@@ -10397,15 +10722,15 @@
           <t>× 3</t>
         </is>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="21">
         <f>'Supuestos'!$C$8*3.0</f>
         <v/>
       </c>
-      <c r="D56" s="25">
+      <c r="D56" s="26">
         <f>IF(C56=0,0,('Supuestos'!$C$8*'Modelo'!$C$46+1.3*(C56-'Supuestos'!$C$8))/C56)</f>
         <v/>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="21">
         <f>C56*(D56-1)</f>
         <v/>
       </c>
@@ -10540,19 +10865,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,('Supuestos'!$C$10*0.9)/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <f>RANK(E7,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -10568,19 +10893,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <f>(((((((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$14)+(((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))=0,0,'Supuestos'!$C$8/(IF(('Supuestos'!$C$13*1.1)=0,0,'Supuestos'!$C$10/('Supuestos'!$C$13*1.1)))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="22">
         <f>RANK(E8,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -10596,19 +10921,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*('Supuestos'!$C$14*1.1))+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="24">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="22">
         <f>RANK(E9,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -10624,19 +10949,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*('Supuestos'!$C$20*1.1))*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*('Supuestos'!$C$20*1.1))*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="24">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="22">
         <f>RANK(E10,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -10652,19 +10977,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*('Supuestos'!$C$25*1.1))+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*('Supuestos'!$C$25*1.1))+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="22">
         <f>RANK(E11,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -10680,19 +11005,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*('Supuestos'!$C$27*1.1))*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*('Supuestos'!$C$27*1.1))*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="22">
         <f>RANK(E12,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -10708,19 +11033,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*('Supuestos'!$C$24*1.1))+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="24">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="22">
         <f>RANK(E13,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -10736,19 +11061,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$16)*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*('Supuestos'!$C$29*1.1))*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="22">
         <f>RANK(E14,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -10764,19 +11089,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <f>(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$14)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*('Supuestos'!$C$16*1.1))*'Supuestos'!$C$15))+((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$24)+(((((((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$20)*'Supuestos'!$C$25)+(((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$21)*'Supuestos'!$C$26))*'Supuestos'!$C$27)*'Supuestos'!$C$29)*'Supuestos'!$C$28))*('Supuestos'!$C$39+'Supuestos'!$C$40+'Supuestos'!$C$41))*(1-'Supuestos'!$C$32-'Supuestos'!$C$33-'Supuestos'!$C$34))-((IF((IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))=0,0,'Supuestos'!$C$8/(IF('Supuestos'!$C$13=0,0,'Supuestos'!$C$10/'Supuestos'!$C$13))))*'Supuestos'!$C$35)-'Supuestos'!$C$36-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <f>D15-$D$6</f>
         <v/>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="24">
         <f>IF($D$6=0,0,E15/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="22">
         <f>RANK(E15,$E$7:$E$15)</f>
         <v/>
       </c>
@@ -10919,51 +11244,51 @@
           <t>Inversión en publicidad del mes</t>
         </is>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <f>C6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <f>D6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <f>E6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <f>F6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="21">
         <f>G6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="21">
         <f>H6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="21">
         <f>I6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="21">
         <f>J6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="21">
         <f>K6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="21">
         <f>L6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="21">
         <f>M6*(1+'Supuestos'!$C$47)</f>
         <v/>
       </c>
@@ -10978,51 +11303,51 @@
           <t>Entradas compradas</t>
         </is>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f>IF('Modelo'!$C$8=0,0,C6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="22">
         <f>IF('Modelo'!$C$8=0,0,D6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="22">
         <f>IF('Modelo'!$C$8=0,0,E6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <f>IF('Modelo'!$C$8=0,0,F6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <f>IF('Modelo'!$C$8=0,0,G6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <f>IF('Modelo'!$C$8=0,0,H6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="22">
         <f>IF('Modelo'!$C$8=0,0,I6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="22">
         <f>IF('Modelo'!$C$8=0,0,J6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="22">
         <f>IF('Modelo'!$C$8=0,0,K6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="22">
         <f>IF('Modelo'!$C$8=0,0,L6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="22">
         <f>IF('Modelo'!$C$8=0,0,M6/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="22">
         <f>IF('Modelo'!$C$8=0,0,N6/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -11037,51 +11362,51 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <f>C7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <f>D7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <f>E7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <f>F7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="25">
         <f>G7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="25">
         <f>H7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="25">
         <f>I7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="25">
         <f>J7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="25">
         <f>K7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="25">
         <f>L7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="25">
         <f>M7*'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="25">
         <f>N7*'Modelo'!$C$35</f>
         <v/>
       </c>
@@ -11096,51 +11421,51 @@
           <t>Facturado (todos los productos)</t>
         </is>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <f>C7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <f>D7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <f>E7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <f>F7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="21">
         <f>G7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="21">
         <f>H7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="21">
         <f>I7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="21">
         <f>J7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="21">
         <f>K7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="21">
         <f>L7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="M9" s="20">
+      <c r="M9" s="21">
         <f>M7*'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="21">
         <f>N7*'Modelo'!$C$36</f>
         <v/>
       </c>
@@ -11155,51 +11480,51 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <f>C9*'Supuestos'!$C$39</f>
         <v/>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <f>D9*'Supuestos'!$C$39+C9*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <f>E9*'Supuestos'!$C$39+D9*'Supuestos'!$C$40+C9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <f>F9*'Supuestos'!$C$39+E9*'Supuestos'!$C$40+D9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="21">
         <f>G9*'Supuestos'!$C$39+F9*'Supuestos'!$C$40+E9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="21">
         <f>H9*'Supuestos'!$C$39+G9*'Supuestos'!$C$40+F9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="21">
         <f>I9*'Supuestos'!$C$39+H9*'Supuestos'!$C$40+G9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="21">
         <f>J9*'Supuestos'!$C$39+I9*'Supuestos'!$C$40+H9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="21">
         <f>K9*'Supuestos'!$C$39+J9*'Supuestos'!$C$40+I9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="21">
         <f>L9*'Supuestos'!$C$39+K9*'Supuestos'!$C$40+J9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="M10" s="20">
+      <c r="M10" s="21">
         <f>M9*'Supuestos'!$C$39+L9*'Supuestos'!$C$40+K9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="21">
         <f>N9*'Supuestos'!$C$39+M9*'Supuestos'!$C$40+L9*'Supuestos'!$C$41</f>
         <v/>
       </c>
@@ -11214,51 +11539,51 @@
           <t>Comisiones y reembolsos</t>
         </is>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="21">
         <f>C10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <f>D10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <f>E10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="21">
         <f>F10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="21">
         <f>G10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="21">
         <f>H10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="21">
         <f>I10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="21">
         <f>J10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="21">
         <f>K10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="21">
         <f>L10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="M11" s="20">
+      <c r="M11" s="21">
         <f>M10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="21">
         <f>N10*('Supuestos'!$C$32+'Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
@@ -11273,51 +11598,51 @@
           <t>Costos por unidad (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>C7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>D7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>E7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <f>F7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <f>G7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="21">
         <f>H7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="21">
         <f>I7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="21">
         <f>J7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="K12" s="20">
+      <c r="K12" s="21">
         <f>K7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="L12" s="20">
+      <c r="L12" s="21">
         <f>L7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="M12" s="20">
+      <c r="M12" s="21">
         <f>M7*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="21">
         <f>N7*'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -11332,51 +11657,51 @@
           <t>Costos fijos del mes</t>
         </is>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="K13" s="20">
+      <c r="K13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="L13" s="20">
+      <c r="L13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="M13" s="20">
+      <c r="M13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="N13" s="20">
+      <c r="N13" s="21">
         <f>'Supuestos'!$C$36*'Supuestos'!$C$9</f>
         <v/>
       </c>
@@ -11505,51 +11830,51 @@
           <t>Saldo de caja (caja inicial + ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <f>'Supuestos'!$C$48+C15</f>
         <v/>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <f>'Supuestos'!$C$48+D15</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>'Supuestos'!$C$48+E15</f>
         <v/>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <f>'Supuestos'!$C$48+F15</f>
         <v/>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="21">
         <f>'Supuestos'!$C$48+G15</f>
         <v/>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="21">
         <f>'Supuestos'!$C$48+H15</f>
         <v/>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="21">
         <f>'Supuestos'!$C$48+I15</f>
         <v/>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="21">
         <f>'Supuestos'!$C$48+J15</f>
         <v/>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="21">
         <f>'Supuestos'!$C$48+K15</f>
         <v/>
       </c>
-      <c r="L16" s="20">
+      <c r="L16" s="21">
         <f>'Supuestos'!$C$48+L15</f>
         <v/>
       </c>
-      <c r="M16" s="20">
+      <c r="M16" s="21">
         <f>'Supuestos'!$C$48+M15</f>
         <v/>
       </c>
-      <c r="N16" s="20">
+      <c r="N16" s="21">
         <f>'Supuestos'!$C$48+N15</f>
         <v/>
       </c>
